--- a/NN/reports/feature_importance_white_invert.xlsx
+++ b/NN/reports/feature_importance_white_invert.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,31 +501,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6501605942060463</v>
+        <v>0.2392785615738154</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8450281121562027</v>
+        <v>0.7020986585130535</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03151037493105605</v>
+        <v>0.4995727851397694</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.212173756026052</v>
+        <v>3.494570036984816</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -538,31 +538,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04545366324078495</v>
+        <v>0.04822482659425891</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02461861185401604</v>
+        <v>0.03150354708145633</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08512977177444428</v>
+        <v>0.01109876378887378</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7542731971311465</v>
+        <v>0.8096637815779482</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
@@ -571,35 +571,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03867821997572523</v>
+        <v>0.07626919443993266</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0160403165305471</v>
+        <v>0.02585223668624248</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05703335699796618</v>
+        <v>0.03187028379250897</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6396065787575287</v>
+        <v>0.7206125907865633</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
@@ -608,35 +608,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.02972220972562753</v>
+        <v>0.04517764016305515</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01707783967228338</v>
+        <v>0.0268120915623819</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02579477762284776</v>
+        <v>0.006611205109028462</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6515954121834011</v>
+        <v>0.8278717553569916</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="6">
@@ -645,35 +645,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02871419289502236</v>
+        <v>0.04354714772811538</v>
       </c>
       <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01898519156507235</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.00805747393289582</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.692930115106654</v>
+      </c>
+      <c r="J6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.01572927199291591</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.02887838229334536</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.7375076242816028</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="7">
@@ -682,35 +682,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02779402940574771</v>
+        <v>0.03750440698185665</v>
       </c>
       <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02372824530537914</v>
+      </c>
+      <c r="F7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.03202482966261833</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
       <c r="G7" t="n">
-        <v>0.02405228838461036</v>
+        <v>0.006696035472563022</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5195526016396697</v>
+        <v>0.6835552164975804</v>
       </c>
       <c r="J7" t="n">
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -719,35 +719,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01941416353680005</v>
+        <v>0.03656710558333551</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003578828502408032</v>
+        <v>0.04749754356039777</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0312078758294526</v>
+        <v>0.00625049212052472</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07984587565996115</v>
+        <v>0.5379885324465508</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -756,35 +756,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01514014121377332</v>
+        <v>0.01122596803523677</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003978331719061633</v>
+        <v>0.004788354009875164</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01637313103652362</v>
+        <v>0.001521671257992752</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1212993169885603</v>
+        <v>0.379242517438104</v>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>8.75</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="10">
@@ -793,35 +793,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02051504580805164</v>
+        <v>0.0100511404669856</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005310481161799445</v>
+        <v>0.00268917621439448</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03838228633529363</v>
+        <v>0.0008747056634513028</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02855948983542422</v>
+        <v>0.1317323699311772</v>
       </c>
       <c r="J10" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>9.25</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01567019983800492</v>
+        <v>0.006033194988754455</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>0.009113469710817659</v>
+        <v>0.02199497678977943</v>
       </c>
       <c r="F11" t="n">
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004086444523113397</v>
+        <v>0.0005616933527610391</v>
       </c>
       <c r="H11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I11" t="n">
-        <v>0.113700174686393</v>
+        <v>0.3359020433126672</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
-        <v>9.75</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.01406142297104181</v>
+        <v>0.009748713791755263</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>0.003585441652585084</v>
+        <v>0.002376658975893509</v>
       </c>
       <c r="F12" t="n">
+        <v>22</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.001688412376054249</v>
+      </c>
+      <c r="H12" t="n">
         <v>10</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.001258370923873708</v>
-      </c>
-      <c r="H12" t="n">
-        <v>17</v>
-      </c>
       <c r="I12" t="n">
-        <v>0.05788806699944393</v>
+        <v>0.07631384256049234</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K12" t="n">
-        <v>12.5</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="13">
@@ -904,35 +904,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.009647952335048919</v>
+        <v>0.01933099434164613</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002469473047140079</v>
+        <v>0.003598491630996464</v>
       </c>
       <c r="F13" t="n">
         <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004288328365881566</v>
+        <v>0.00134922590741986</v>
       </c>
       <c r="H13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04077465670107427</v>
+        <v>0.05533991156553952</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="K13" t="n">
-        <v>13.75</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="14">
@@ -941,35 +941,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.01150337710655282</v>
+        <v>0.009318921880566915</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002991046161264166</v>
+        <v>0.003302288829380732</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.01052200717441567</v>
+        <v>-0.0006264921433683068</v>
       </c>
       <c r="H14" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06575116056268948</v>
+        <v>0.1435422164601232</v>
       </c>
       <c r="J14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>14.75</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -978,35 +978,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.01155629893440493</v>
+        <v>0.002627038859039394</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002148742506065918</v>
+        <v>0.00755226422145774</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.008362686901043814</v>
+        <v>0.001878851563722894</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01668648957024255</v>
+        <v>0.07919767859878446</v>
       </c>
       <c r="J15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K15" t="n">
-        <v>14.75</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="16">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.009617232145809829</v>
+        <v>0.007499976221640881</v>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001965316055727048</v>
+        <v>0.001830038906218063</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
-        <v>0.008933155248196623</v>
+        <v>0.0003438099849484844</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I16" t="n">
-        <v>0.03987430440062978</v>
+        <v>0.1153905285354511</v>
       </c>
       <c r="J16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K16" t="n">
-        <v>15</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.009090799351627305</v>
+        <v>0.008998429978499685</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002542634371562479</v>
+        <v>0.001381383685993206</v>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00740198173398593</v>
+        <v>0.0005825194984571235</v>
       </c>
       <c r="H17" t="n">
+        <v>17</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1270074286839145</v>
+      </c>
+      <c r="J17" t="n">
         <v>12</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>22</v>
-      </c>
       <c r="K17" t="n">
-        <v>15.75</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.00901811516713954</v>
+        <v>0.00310941172531338</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002105624334325469</v>
+        <v>0.007299630567400027</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>0.006163480871744653</v>
+        <v>0.002067810914767354</v>
       </c>
       <c r="H18" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03414653424672087</v>
+        <v>0.06857522721585374</v>
       </c>
       <c r="J18" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K18" t="n">
-        <v>16.25</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.008440425919721382</v>
+        <v>0.1873988696456341</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001800295909005443</v>
+        <v>0.004297102478633507</v>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.002974200876968913</v>
+        <v>-0.02194819670442113</v>
       </c>
       <c r="H19" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0815786599915107</v>
+        <v>0.06851967201496523</v>
       </c>
       <c r="J19" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="K19" t="n">
-        <v>17.5</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.008113345387977883</v>
+        <v>0.01096156082556342</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002133129469784251</v>
+        <v>0.002766614765557432</v>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0001180161300002869</v>
+        <v>-0.000150599280333874</v>
       </c>
       <c r="H20" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03380436337285975</v>
+        <v>0.05715507498948114</v>
       </c>
       <c r="J20" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="K20" t="n">
-        <v>18.25</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.00859252703040402</v>
+        <v>0.006737243445710204</v>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E21" t="n">
-        <v>0.002103727839216454</v>
+        <v>0.003086007355575549</v>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.005320301525803484</v>
+        <v>-0.0005387010116341684</v>
       </c>
       <c r="H21" t="n">
+        <v>41</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.0847919741349199</v>
+      </c>
+      <c r="J21" t="n">
         <v>22</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.03993354619787093</v>
-      </c>
-      <c r="J21" t="n">
-        <v>14</v>
-      </c>
       <c r="K21" t="n">
-        <v>18.25</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="22">
@@ -1241,31 +1241,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.007865353753230817</v>
+        <v>0.008413229029541468</v>
       </c>
       <c r="D22" t="n">
         <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>0.002394513709260966</v>
+        <v>0.00242472011931414</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G22" t="n">
-        <v>0.002427038219831312</v>
+        <v>-0.0002857415488159099</v>
       </c>
       <c r="H22" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0005879810303510702</v>
+        <v>0.07016872245278982</v>
       </c>
       <c r="J22" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K22" t="n">
-        <v>18.25</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0003550095945719826</v>
+        <v>0.005886969378862915</v>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0004933567905551761</v>
+        <v>0.001894858111643036</v>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.316683218667182e-05</v>
+        <v>0.0001645951792163758</v>
       </c>
       <c r="H23" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03722798557969842</v>
+        <v>0.07578163492785395</v>
       </c>
       <c r="J23" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K23" t="n">
-        <v>20.25</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,1145 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.00719535894968134</v>
+      </c>
+      <c r="D24" t="n">
+        <v>25</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.002032766054721776</v>
+      </c>
+      <c r="F24" t="n">
+        <v>27</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0001186463784928926</v>
+      </c>
+      <c r="H24" t="n">
+        <v>26</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.06049050796130562</v>
+      </c>
+      <c r="J24" t="n">
+        <v>35</v>
+      </c>
+      <c r="K24" t="n">
+        <v>28.25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.008421856859704643</v>
+      </c>
+      <c r="D25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.00211370215016681</v>
+      </c>
+      <c r="F25" t="n">
+        <v>25</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.00164232973952384</v>
+      </c>
+      <c r="H25" t="n">
+        <v>50</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.08626015139544796</v>
+      </c>
+      <c r="J25" t="n">
+        <v>20</v>
+      </c>
+      <c r="K25" t="n">
+        <v>28.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.01224841297601068</v>
+      </c>
+      <c r="D26" t="n">
+        <v>11</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.005984435520218248</v>
+      </c>
+      <c r="F26" t="n">
+        <v>11</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.00142048526763473</v>
+      </c>
+      <c r="H26" t="n">
+        <v>48</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.01820777581569377</v>
+      </c>
+      <c r="J26" t="n">
+        <v>47</v>
+      </c>
+      <c r="K26" t="n">
+        <v>29.25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.01001883877945995</v>
+      </c>
+      <c r="D27" t="n">
+        <v>15</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.002063085015217124</v>
+      </c>
+      <c r="F27" t="n">
+        <v>26</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.00147404199285428</v>
+      </c>
+      <c r="H27" t="n">
+        <v>49</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.07258453014363386</v>
+      </c>
+      <c r="J27" t="n">
+        <v>27</v>
+      </c>
+      <c r="K27" t="n">
+        <v>29.25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.01413753573266014</v>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.002002564792444114</v>
+      </c>
+      <c r="F28" t="n">
+        <v>28</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.001715218802246488</v>
+      </c>
+      <c r="H28" t="n">
+        <v>51</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.07165645316039404</v>
+      </c>
+      <c r="J28" t="n">
+        <v>28</v>
+      </c>
+      <c r="K28" t="n">
+        <v>29.25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0002624802007073004</v>
+      </c>
+      <c r="D29" t="n">
+        <v>52</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.002696027020492809</v>
+      </c>
+      <c r="F29" t="n">
+        <v>19</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-4.000226660227924e-06</v>
+      </c>
+      <c r="H29" t="n">
+        <v>32</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1053126868845498</v>
+      </c>
+      <c r="J29" t="n">
+        <v>14</v>
+      </c>
+      <c r="K29" t="n">
+        <v>29.25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.008441719886500443</v>
+      </c>
+      <c r="D30" t="n">
+        <v>19</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.00315498963606712</v>
+      </c>
+      <c r="F30" t="n">
+        <v>16</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.002235304855133002</v>
+      </c>
+      <c r="H30" t="n">
+        <v>52</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.06235080822428163</v>
+      </c>
+      <c r="J30" t="n">
+        <v>33</v>
+      </c>
+      <c r="K30" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.005585420911260726</v>
+      </c>
+      <c r="D31" t="n">
+        <v>33</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.001960520668127841</v>
+      </c>
+      <c r="F31" t="n">
+        <v>29</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.0002185553499171378</v>
+      </c>
+      <c r="H31" t="n">
+        <v>37</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.0851360275683648</v>
+      </c>
+      <c r="J31" t="n">
+        <v>21</v>
+      </c>
+      <c r="K31" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.006283205113379683</v>
+      </c>
+      <c r="D32" t="n">
+        <v>28</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.001548638105296112</v>
+      </c>
+      <c r="F32" t="n">
+        <v>36</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0007631619335715545</v>
+      </c>
+      <c r="H32" t="n">
+        <v>15</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.0479470393911634</v>
+      </c>
+      <c r="J32" t="n">
+        <v>42</v>
+      </c>
+      <c r="K32" t="n">
+        <v>30.25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.003585041625533856</v>
+      </c>
+      <c r="D33" t="n">
+        <v>43</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.001145237844529358</v>
+      </c>
+      <c r="F33" t="n">
+        <v>47</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0005977563814497211</v>
+      </c>
+      <c r="H33" t="n">
+        <v>16</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.1005354258648734</v>
+      </c>
+      <c r="J33" t="n">
+        <v>15</v>
+      </c>
+      <c r="K33" t="n">
+        <v>30.25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.007913312452445673</v>
+      </c>
+      <c r="D34" t="n">
+        <v>22</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.001828120984901879</v>
+      </c>
+      <c r="F34" t="n">
+        <v>32</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-3.411137786994978e-05</v>
+      </c>
+      <c r="H34" t="n">
+        <v>33</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.05594284296521712</v>
+      </c>
+      <c r="J34" t="n">
+        <v>38</v>
+      </c>
+      <c r="K34" t="n">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.006484374560023289</v>
+      </c>
+      <c r="D35" t="n">
+        <v>27</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.001624730669403799</v>
+      </c>
+      <c r="F35" t="n">
+        <v>34</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0001786858351194631</v>
+      </c>
+      <c r="H35" t="n">
+        <v>24</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.04168210238512593</v>
+      </c>
+      <c r="J35" t="n">
+        <v>44</v>
+      </c>
+      <c r="K35" t="n">
+        <v>32.25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.005388925526459861</v>
+      </c>
+      <c r="D36" t="n">
+        <v>36</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.00141860717341115</v>
+      </c>
+      <c r="F36" t="n">
+        <v>42</v>
+      </c>
+      <c r="G36" t="n">
+        <v>7.389424923087695e-05</v>
+      </c>
+      <c r="H36" t="n">
+        <v>28</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.08428896967463562</v>
+      </c>
+      <c r="J36" t="n">
+        <v>23</v>
+      </c>
+      <c r="K36" t="n">
+        <v>32.25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.003929903466314806</v>
+      </c>
+      <c r="D37" t="n">
+        <v>42</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.001166344695713981</v>
+      </c>
+      <c r="F37" t="n">
+        <v>45</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8.937264546736712e-05</v>
+      </c>
+      <c r="H37" t="n">
+        <v>27</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09638604513066973</v>
+      </c>
+      <c r="J37" t="n">
+        <v>16</v>
+      </c>
+      <c r="K37" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.006130200583785508</v>
+      </c>
+      <c r="D38" t="n">
+        <v>30</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.001508301193739607</v>
+      </c>
+      <c r="F38" t="n">
+        <v>38</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0003666531390621785</v>
+      </c>
+      <c r="H38" t="n">
+        <v>21</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.04947098822750107</v>
+      </c>
+      <c r="J38" t="n">
+        <v>41</v>
+      </c>
+      <c r="K38" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.00351009649134086</v>
+      </c>
+      <c r="D39" t="n">
+        <v>45</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.002308898723905178</v>
+      </c>
+      <c r="F39" t="n">
+        <v>23</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0008768741801767454</v>
+      </c>
+      <c r="H39" t="n">
+        <v>13</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>51</v>
+      </c>
+      <c r="K39" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.003582832798197596</v>
+      </c>
+      <c r="D40" t="n">
+        <v>44</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.00112987366556819</v>
+      </c>
+      <c r="F40" t="n">
+        <v>49</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.0002408118842709972</v>
+      </c>
+      <c r="H40" t="n">
+        <v>23</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09626847402319516</v>
+      </c>
+      <c r="J40" t="n">
+        <v>17</v>
+      </c>
+      <c r="K40" t="n">
+        <v>33.25</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.005251037937169436</v>
+      </c>
+      <c r="D41" t="n">
+        <v>38</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.001534295373496901</v>
+      </c>
+      <c r="F41" t="n">
+        <v>37</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.0003430546552071423</v>
+      </c>
+      <c r="H41" t="n">
+        <v>40</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.09116504893459432</v>
+      </c>
+      <c r="J41" t="n">
+        <v>19</v>
+      </c>
+      <c r="K41" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.005398859642255072</v>
+      </c>
+      <c r="D42" t="n">
+        <v>35</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.001486162317343822</v>
+      </c>
+      <c r="F42" t="n">
+        <v>40</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.0004073960740187954</v>
+      </c>
+      <c r="H42" t="n">
+        <v>20</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.05407251610368879</v>
+      </c>
+      <c r="J42" t="n">
+        <v>40</v>
+      </c>
+      <c r="K42" t="n">
+        <v>33.75</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.004569159793192584</v>
+      </c>
+      <c r="D43" t="n">
+        <v>41</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.001352934041462639</v>
+      </c>
+      <c r="F43" t="n">
+        <v>44</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-5.17778356995513e-05</v>
+      </c>
+      <c r="H43" t="n">
+        <v>34</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.09325412685993539</v>
+      </c>
+      <c r="J43" t="n">
+        <v>18</v>
+      </c>
+      <c r="K43" t="n">
+        <v>34.25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>white_quality_ash_1</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.007247496005988886</v>
+      </c>
+      <c r="D44" t="n">
+        <v>24</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.002238429857352846</v>
+      </c>
+      <c r="F44" t="n">
+        <v>24</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.001391353341655666</v>
+      </c>
+      <c r="H44" t="n">
+        <v>47</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.03999331145754903</v>
+      </c>
+      <c r="J44" t="n">
+        <v>45</v>
+      </c>
+      <c r="K44" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_1</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.004957844870211341</v>
+      </c>
+      <c r="D45" t="n">
+        <v>39</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.001424224768173518</v>
+      </c>
+      <c r="F45" t="n">
+        <v>41</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.0004460295429333461</v>
+      </c>
+      <c r="H45" t="n">
+        <v>19</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.04417439044620686</v>
+      </c>
+      <c r="J45" t="n">
+        <v>43</v>
+      </c>
+      <c r="K45" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.005570404394293522</v>
+      </c>
+      <c r="D46" t="n">
+        <v>34</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.00149890594579983</v>
+      </c>
+      <c r="F46" t="n">
+        <v>39</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0.0007137982229562412</v>
+      </c>
+      <c r="H46" t="n">
+        <v>44</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.06405963718412444</v>
+      </c>
+      <c r="J46" t="n">
+        <v>32</v>
+      </c>
+      <c r="K46" t="n">
+        <v>37.25</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.006218100461482147</v>
+      </c>
+      <c r="D47" t="n">
+        <v>29</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.001593668657358322</v>
+      </c>
+      <c r="F47" t="n">
+        <v>35</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-0.0007357061907502071</v>
+      </c>
+      <c r="H47" t="n">
+        <v>45</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.005673998930172619</v>
+      </c>
+      <c r="J47" t="n">
+        <v>49</v>
+      </c>
+      <c r="K47" t="n">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.001663360782748484</v>
+      </c>
+      <c r="D48" t="n">
+        <v>48</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.001757441345586086</v>
+      </c>
+      <c r="F48" t="n">
+        <v>33</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4.52069388739873e-05</v>
+      </c>
+      <c r="H48" t="n">
+        <v>29</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>51</v>
+      </c>
+      <c r="K48" t="n">
+        <v>40.25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.005366524830917239</v>
+      </c>
+      <c r="D49" t="n">
+        <v>37</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.001147542919868919</v>
+      </c>
+      <c r="F49" t="n">
+        <v>46</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.0006793108609644549</v>
+      </c>
+      <c r="H49" t="n">
+        <v>43</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.05634842949855523</v>
+      </c>
+      <c r="J49" t="n">
+        <v>37</v>
+      </c>
+      <c r="K49" t="n">
+        <v>40.75</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.004784381846940302</v>
+      </c>
+      <c r="D50" t="n">
+        <v>40</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.001129882934385539</v>
+      </c>
+      <c r="F50" t="n">
+        <v>48</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-0.0007792542138363778</v>
+      </c>
+      <c r="H50" t="n">
+        <v>46</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.06094154532836749</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34</v>
+      </c>
+      <c r="K50" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0009385338490848201</v>
+      </c>
+      <c r="D51" t="n">
+        <v>49</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.0003852495780667005</v>
+      </c>
+      <c r="F51" t="n">
+        <v>51</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-0.0002125872452711342</v>
+      </c>
+      <c r="H51" t="n">
+        <v>36</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.02715593727123222</v>
+      </c>
+      <c r="J51" t="n">
+        <v>46</v>
+      </c>
+      <c r="K51" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.000409422954063243</v>
+      </c>
+      <c r="D52" t="n">
+        <v>51</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.0003466637184265833</v>
+      </c>
+      <c r="F52" t="n">
+        <v>52</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3.42480824476743e-06</v>
+      </c>
+      <c r="H52" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.0008470847830079897</v>
+      </c>
+      <c r="J52" t="n">
+        <v>50</v>
+      </c>
+      <c r="K52" t="n">
+        <v>45.75</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.0001275446562220433</v>
+      </c>
+      <c r="D53" t="n">
+        <v>53</v>
+      </c>
+      <c r="E53" t="n">
+        <v>9.828944389033009e-05</v>
+      </c>
+      <c r="F53" t="n">
+        <v>53</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8.260306988083776e-07</v>
+      </c>
+      <c r="H53" t="n">
+        <v>31</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.008267973532043449</v>
+      </c>
+      <c r="J53" t="n">
+        <v>48</v>
+      </c>
+      <c r="K53" t="n">
+        <v>46.25</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>0.0008756804568849533</v>
-      </c>
-      <c r="D24" t="n">
-        <v>22</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.0007666051908373479</v>
-      </c>
-      <c r="F24" t="n">
-        <v>22</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-0.001797485393857956</v>
-      </c>
-      <c r="H24" t="n">
-        <v>20</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="C54" t="n">
+        <v>0.0004672653828441226</v>
+      </c>
+      <c r="D54" t="n">
+        <v>50</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.0005593842487669528</v>
+      </c>
+      <c r="F54" t="n">
+        <v>50</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-0.0003352761374145863</v>
+      </c>
+      <c r="H54" t="n">
+        <v>39</v>
+      </c>
+      <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
-        <v>22</v>
-      </c>
-      <c r="K24" t="n">
-        <v>21.5</v>
+      <c r="J54" t="n">
+        <v>51</v>
+      </c>
+      <c r="K54" t="n">
+        <v>47.5</v>
       </c>
     </row>
   </sheetData>
@@ -1423,31 +2533,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6501605942060463</v>
+        <v>0.2392785615738154</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8450281121562027</v>
+        <v>0.7020986585130535</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03151037493105605</v>
+        <v>0.4995727851397694</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.212173756026052</v>
+        <v>3.494570036984816</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1460,31 +2570,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04545366324078495</v>
+        <v>0.04822482659425891</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02461861185401604</v>
+        <v>0.03150354708145633</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08512977177444428</v>
+        <v>0.01109876378887378</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7542731971311465</v>
+        <v>0.8096637815779482</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
@@ -1493,35 +2603,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03867821997572523</v>
+        <v>0.07626919443993266</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0160403165305471</v>
+        <v>0.02585223668624248</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05703335699796618</v>
+        <v>0.03187028379250897</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6396065787575287</v>
+        <v>0.7206125907865633</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
@@ -1530,35 +2640,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.02972220972562753</v>
+        <v>0.04517764016305515</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01707783967228338</v>
+        <v>0.0268120915623819</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02579477762284776</v>
+        <v>0.006611205109028462</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6515954121834011</v>
+        <v>0.8278717553569916</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="6">
@@ -1567,35 +2677,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02871419289502236</v>
+        <v>0.04354714772811538</v>
       </c>
       <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01898519156507235</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.00805747393289582</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.692930115106654</v>
+      </c>
+      <c r="J6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.01572927199291591</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.02887838229334536</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.7375076242816028</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="7">
@@ -1604,35 +2714,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02779402940574771</v>
+        <v>0.03750440698185665</v>
       </c>
       <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02372824530537914</v>
+      </c>
+      <c r="F7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.03202482966261833</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
       <c r="G7" t="n">
-        <v>0.02405228838461036</v>
+        <v>0.006696035472563022</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5195526016396697</v>
+        <v>0.6835552164975804</v>
       </c>
       <c r="J7" t="n">
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1641,35 +2751,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01941416353680005</v>
+        <v>0.03656710558333551</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003578828502408032</v>
+        <v>0.04749754356039777</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0312078758294526</v>
+        <v>0.00625049212052472</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07984587565996115</v>
+        <v>0.5379885324465508</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -1678,35 +2788,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01514014121377332</v>
+        <v>0.01122596803523677</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003978331719061633</v>
+        <v>0.004788354009875164</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01637313103652362</v>
+        <v>0.001521671257992752</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1212993169885603</v>
+        <v>0.379242517438104</v>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>8.75</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="10">
@@ -1715,35 +2825,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02051504580805164</v>
+        <v>0.0100511404669856</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005310481161799445</v>
+        <v>0.00268917621439448</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03838228633529363</v>
+        <v>0.0008747056634513028</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02855948983542422</v>
+        <v>0.1317323699311772</v>
       </c>
       <c r="J10" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>9.25</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="11">
@@ -1752,35 +2862,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01567019983800492</v>
+        <v>0.006033194988754455</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>0.009113469710817659</v>
+        <v>0.02199497678977943</v>
       </c>
       <c r="F11" t="n">
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004086444523113397</v>
+        <v>0.0005616933527610391</v>
       </c>
       <c r="H11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I11" t="n">
-        <v>0.113700174686393</v>
+        <v>0.3359020433126672</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
-        <v>9.75</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="12">
@@ -1789,35 +2899,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.01406142297104181</v>
+        <v>0.009748713791755263</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>0.003585441652585084</v>
+        <v>0.002376658975893509</v>
       </c>
       <c r="F12" t="n">
+        <v>22</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.001688412376054249</v>
+      </c>
+      <c r="H12" t="n">
         <v>10</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.001258370923873708</v>
-      </c>
-      <c r="H12" t="n">
-        <v>17</v>
-      </c>
       <c r="I12" t="n">
-        <v>0.05788806699944393</v>
+        <v>0.07631384256049234</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K12" t="n">
-        <v>12.5</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="13">
@@ -1826,35 +2936,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.009647952335048919</v>
+        <v>0.01933099434164613</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002469473047140079</v>
+        <v>0.003598491630996464</v>
       </c>
       <c r="F13" t="n">
         <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004288328365881566</v>
+        <v>0.00134922590741986</v>
       </c>
       <c r="H13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04077465670107427</v>
+        <v>0.05533991156553952</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="K13" t="n">
-        <v>13.75</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="14">
@@ -1863,35 +2973,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.01150337710655282</v>
+        <v>0.009318921880566915</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002991046161264166</v>
+        <v>0.003302288829380732</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.01052200717441567</v>
+        <v>-0.0006264921433683068</v>
       </c>
       <c r="H14" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06575116056268948</v>
+        <v>0.1435422164601232</v>
       </c>
       <c r="J14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>14.75</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -1900,35 +3010,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.01155629893440493</v>
+        <v>0.002627038859039394</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002148742506065918</v>
+        <v>0.00755226422145774</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.008362686901043814</v>
+        <v>0.001878851563722894</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01668648957024255</v>
+        <v>0.07919767859878446</v>
       </c>
       <c r="J15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K15" t="n">
-        <v>14.75</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="16">
@@ -1937,35 +3047,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.009617232145809829</v>
+        <v>0.007499976221640881</v>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001965316055727048</v>
+        <v>0.001830038906218063</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
-        <v>0.008933155248196623</v>
+        <v>0.0003438099849484844</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I16" t="n">
-        <v>0.03987430440062978</v>
+        <v>0.1153905285354511</v>
       </c>
       <c r="J16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K16" t="n">
-        <v>15</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="17">
@@ -1974,35 +3084,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.009090799351627305</v>
+        <v>0.008998429978499685</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002542634371562479</v>
+        <v>0.001381383685993206</v>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00740198173398593</v>
+        <v>0.0005825194984571235</v>
       </c>
       <c r="H17" t="n">
+        <v>17</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1270074286839145</v>
+      </c>
+      <c r="J17" t="n">
         <v>12</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>22</v>
-      </c>
       <c r="K17" t="n">
-        <v>15.75</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="18">
@@ -2011,35 +3121,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.00901811516713954</v>
+        <v>0.00310941172531338</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002105624334325469</v>
+        <v>0.007299630567400027</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>0.006163480871744653</v>
+        <v>0.002067810914767354</v>
       </c>
       <c r="H18" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03414653424672087</v>
+        <v>0.06857522721585374</v>
       </c>
       <c r="J18" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K18" t="n">
-        <v>16.25</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="19">
@@ -2048,35 +3158,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.008440425919721382</v>
+        <v>0.1873988696456341</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001800295909005443</v>
+        <v>0.004297102478633507</v>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.002974200876968913</v>
+        <v>-0.02194819670442113</v>
       </c>
       <c r="H19" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0815786599915107</v>
+        <v>0.06851967201496523</v>
       </c>
       <c r="J19" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="K19" t="n">
-        <v>17.5</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="20">
@@ -2085,35 +3195,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.008113345387977883</v>
+        <v>0.01096156082556342</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002133129469784251</v>
+        <v>0.002766614765557432</v>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0001180161300002869</v>
+        <v>-0.000150599280333874</v>
       </c>
       <c r="H20" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03380436337285975</v>
+        <v>0.05715507498948114</v>
       </c>
       <c r="J20" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="K20" t="n">
-        <v>18.25</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="21">
@@ -2122,35 +3232,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.00859252703040402</v>
+        <v>0.006737243445710204</v>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E21" t="n">
-        <v>0.002103727839216454</v>
+        <v>0.003086007355575549</v>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.005320301525803484</v>
+        <v>-0.0005387010116341684</v>
       </c>
       <c r="H21" t="n">
+        <v>41</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.0847919741349199</v>
+      </c>
+      <c r="J21" t="n">
         <v>22</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.03993354619787093</v>
-      </c>
-      <c r="J21" t="n">
-        <v>14</v>
-      </c>
       <c r="K21" t="n">
-        <v>18.25</v>
+        <v>26.5</v>
       </c>
     </row>
   </sheetData>
@@ -2164,7 +3274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2194,7 +3304,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6501605942060463</v>
+        <v>0.2392785615738154</v>
       </c>
     </row>
     <row r="3">
@@ -2203,11 +3313,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04545366324078495</v>
+        <v>0.1873988696456341</v>
       </c>
     </row>
     <row r="4">
@@ -2216,11 +3326,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03867821997572523</v>
+        <v>0.07626919443993266</v>
       </c>
     </row>
     <row r="5">
@@ -2229,11 +3339,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.02972220972562753</v>
+        <v>0.04822482659425891</v>
       </c>
     </row>
     <row r="6">
@@ -2246,7 +3356,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02871419289502236</v>
+        <v>0.04517764016305515</v>
       </c>
     </row>
     <row r="7">
@@ -2255,11 +3365,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02779402940574771</v>
+        <v>0.04354714772811538</v>
       </c>
     </row>
     <row r="8">
@@ -2268,11 +3378,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02051504580805164</v>
+        <v>0.03750440698185665</v>
       </c>
     </row>
     <row r="9">
@@ -2281,11 +3391,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01941416353680005</v>
+        <v>0.03656710558333551</v>
       </c>
     </row>
     <row r="10">
@@ -2294,11 +3404,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.01567019983800492</v>
+        <v>0.01933099434164613</v>
       </c>
     </row>
     <row r="11">
@@ -2307,11 +3417,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01514014121377332</v>
+        <v>0.01413753573266014</v>
       </c>
     </row>
     <row r="12">
@@ -2320,11 +3430,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.01406142297104181</v>
+        <v>0.01224841297601068</v>
       </c>
     </row>
     <row r="13">
@@ -2333,11 +3443,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.01155629893440493</v>
+        <v>0.01122596803523677</v>
       </c>
     </row>
     <row r="14">
@@ -2346,11 +3456,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.01150337710655282</v>
+        <v>0.01096156082556342</v>
       </c>
     </row>
     <row r="15">
@@ -2359,11 +3469,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.009647952335048919</v>
+        <v>0.0100511404669856</v>
       </c>
     </row>
     <row r="16">
@@ -2372,11 +3482,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.009617232145809829</v>
+        <v>0.01001883877945995</v>
       </c>
     </row>
     <row r="17">
@@ -2385,11 +3495,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.009090799351627305</v>
+        <v>0.009748713791755263</v>
       </c>
     </row>
     <row r="18">
@@ -2398,11 +3508,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.00901811516713954</v>
+        <v>0.009318921880566915</v>
       </c>
     </row>
     <row r="19">
@@ -2411,11 +3521,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.00859252703040402</v>
+        <v>0.008998429978499685</v>
       </c>
     </row>
     <row r="20">
@@ -2424,11 +3534,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.008440425919721382</v>
+        <v>0.008441719886500443</v>
       </c>
     </row>
     <row r="21">
@@ -2437,11 +3547,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.008113345387977883</v>
+        <v>0.008421856859704643</v>
       </c>
     </row>
     <row r="22">
@@ -2454,7 +3564,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.007865353753230817</v>
+        <v>0.008413229029541468</v>
       </c>
     </row>
     <row r="23">
@@ -2463,11 +3573,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0008756804568849533</v>
+        <v>0.007913312452445673</v>
       </c>
     </row>
     <row r="24">
@@ -2476,11 +3586,401 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>sulphited_color</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.007499976221640881</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>white_quality_ash_1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.007247496005988886</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.00719535894968134</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>raw_syrup_color</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.006737243445710204</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.006484374560023289</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.006283205113379683</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.006218100461482147</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.006130200583785508</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>report_date_month</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.006033194988754455</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.005886969378862915</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.005585420911260726</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.005570404394293522</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.005398859642255072</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.005388925526459861</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.005366524830917239</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.005251037937169436</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_1</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.004957844870211341</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.004784381846940302</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.004569159793192584</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.003929903466314806</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.003585041625533856</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.003582832798197596</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.00351009649134086</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.00310941172531338</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.002627038859039394</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.001663360782748484</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0009385338490848201</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0004672653828441226</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.000409422954063243</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.0002624802007073004</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>carbonated_alkalinity</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>0.0003550095945719826</v>
+      <c r="C54" t="n">
+        <v>0.0001275446562220433</v>
       </c>
     </row>
   </sheetData>
@@ -2494,7 +3994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2524,7 +4024,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8450281121562027</v>
+        <v>0.7020986585130535</v>
       </c>
     </row>
     <row r="3">
@@ -2537,7 +4037,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03202482966261833</v>
+        <v>0.04749754356039777</v>
       </c>
     </row>
     <row r="4">
@@ -2550,7 +4050,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.02461861185401604</v>
+        <v>0.03150354708145633</v>
       </c>
     </row>
     <row r="5">
@@ -2559,11 +4059,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.01707783967228338</v>
+        <v>0.0268120915623819</v>
       </c>
     </row>
     <row r="6">
@@ -2572,11 +4072,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0160403165305471</v>
+        <v>0.02585223668624248</v>
       </c>
     </row>
     <row r="7">
@@ -2585,11 +4085,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01572927199291591</v>
+        <v>0.02372824530537914</v>
       </c>
     </row>
     <row r="8">
@@ -2598,11 +4098,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.009113469710817659</v>
+        <v>0.02199497678977943</v>
       </c>
     </row>
     <row r="9">
@@ -2611,11 +4111,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005310481161799445</v>
+        <v>0.01898519156507235</v>
       </c>
     </row>
     <row r="10">
@@ -2624,11 +4124,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.003978331719061633</v>
+        <v>0.00755226422145774</v>
       </c>
     </row>
     <row r="11">
@@ -2637,11 +4137,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.003585441652585084</v>
+        <v>0.007299630567400027</v>
       </c>
     </row>
     <row r="12">
@@ -2650,11 +4150,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.003578828502408032</v>
+        <v>0.005984435520218248</v>
       </c>
     </row>
     <row r="13">
@@ -2663,11 +4163,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002991046161264166</v>
+        <v>0.004788354009875164</v>
       </c>
     </row>
     <row r="14">
@@ -2676,11 +4176,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002542634371562479</v>
+        <v>0.004297102478633507</v>
       </c>
     </row>
     <row r="15">
@@ -2689,11 +4189,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002469473047140079</v>
+        <v>0.003598491630996464</v>
       </c>
     </row>
     <row r="16">
@@ -2702,11 +4202,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002394513709260966</v>
+        <v>0.003302288829380732</v>
       </c>
     </row>
     <row r="17">
@@ -2715,11 +4215,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.002148742506065918</v>
+        <v>0.00315498963606712</v>
       </c>
     </row>
     <row r="18">
@@ -2728,11 +4228,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002133129469784251</v>
+        <v>0.003086007355575549</v>
       </c>
     </row>
     <row r="19">
@@ -2741,11 +4241,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002105624334325469</v>
+        <v>0.002766614765557432</v>
       </c>
     </row>
     <row r="20">
@@ -2754,11 +4254,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002103727839216454</v>
+        <v>0.002696027020492809</v>
       </c>
     </row>
     <row r="21">
@@ -2767,11 +4267,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001965316055727048</v>
+        <v>0.00268917621439448</v>
       </c>
     </row>
     <row r="22">
@@ -2780,11 +4280,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001800295909005443</v>
+        <v>0.00242472011931414</v>
       </c>
     </row>
     <row r="23">
@@ -2793,11 +4293,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0007666051908373479</v>
+        <v>0.002376658975893509</v>
       </c>
     </row>
     <row r="24">
@@ -2806,11 +4306,401 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.002308898723905178</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>white_quality_ash_1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.002238429857352846</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.00211370215016681</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.002063085015217124</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.002032766054721776</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.002002564792444114</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.001960520668127841</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.001894858111643036</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>sulphited_color</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.001830038906218063</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.001828120984901879</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.001757441345586086</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.001624730669403799</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.001593668657358322</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.001548638105296112</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.001534295373496901</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.001508301193739607</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.00149890594579983</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.001486162317343822</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.001424224768173518</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.00141860717341115</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.001381383685993206</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.001352934041462639</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.001166344695713981</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.001147542919868919</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.001145237844529358</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.001129882934385539</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.00112987366556819</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0005593842487669528</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.0003852495780667005</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.0003466637184265833</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>carbonated_alkalinity</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>0.0004933567905551761</v>
+      <c r="C54" t="n">
+        <v>9.828944389033009e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +4714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2855,14 +4745,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.08512977177444428</v>
+        <v>0.4995727851397694</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03582911113382192</v>
+        <v>0.01857695332894564</v>
       </c>
     </row>
     <row r="3">
@@ -2871,14 +4761,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05703335699796618</v>
+        <v>0.03187028379250897</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0109537252968094</v>
+        <v>0.008589619572648633</v>
       </c>
     </row>
     <row r="4">
@@ -2887,14 +4777,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03838228633529363</v>
+        <v>0.01109876378887378</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01166634682009353</v>
+        <v>0.008308217314278074</v>
       </c>
     </row>
     <row r="5">
@@ -2903,14 +4793,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03151037493105605</v>
+        <v>0.00805747393289582</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006616109614556968</v>
+        <v>0.005979374089886852</v>
       </c>
     </row>
     <row r="6">
@@ -2919,14 +4809,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0312078758294526</v>
+        <v>0.006696035472563022</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01031472728922348</v>
+        <v>0.007032935668823118</v>
       </c>
     </row>
     <row r="7">
@@ -2939,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02887838229334536</v>
+        <v>0.006611205109028462</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01107940911930256</v>
+        <v>0.007768903585070768</v>
       </c>
     </row>
     <row r="8">
@@ -2951,14 +4841,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02579477762284776</v>
+        <v>0.00625049212052472</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01174417269059322</v>
+        <v>0.007272452258322136</v>
       </c>
     </row>
     <row r="9">
@@ -2967,14 +4857,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02405228838461036</v>
+        <v>0.002067810914767354</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01114382430632502</v>
+        <v>0.0009010450608744553</v>
       </c>
     </row>
     <row r="10">
@@ -2983,14 +4873,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.01637313103652362</v>
+        <v>0.001878851563722894</v>
       </c>
       <c r="D10" t="n">
-        <v>0.005899977380401523</v>
+        <v>0.0009052369613553881</v>
       </c>
     </row>
     <row r="11">
@@ -2999,14 +4889,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.008933155248196623</v>
+        <v>0.001688412376054249</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002262705706651605</v>
+        <v>0.001357517417666689</v>
       </c>
     </row>
     <row r="12">
@@ -3015,14 +4905,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.008362686901043814</v>
+        <v>0.001521671257992752</v>
       </c>
       <c r="D12" t="n">
-        <v>0.005607050529684163</v>
+        <v>0.0006774631949469078</v>
       </c>
     </row>
     <row r="13">
@@ -3031,14 +4921,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.00740198173398593</v>
+        <v>0.00134922590741986</v>
       </c>
       <c r="D13" t="n">
-        <v>0.002431426169549128</v>
+        <v>0.002737054549409479</v>
       </c>
     </row>
     <row r="14">
@@ -3047,14 +4937,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.006163480871744653</v>
+        <v>0.0008768741801767454</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002581828362376977</v>
+        <v>0.0009069841466530784</v>
       </c>
     </row>
     <row r="15">
@@ -3063,14 +4953,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.004288328365881566</v>
+        <v>0.0008747056634513028</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002122115331948373</v>
+        <v>0.0006681675182436563</v>
       </c>
     </row>
     <row r="16">
@@ -3079,14 +4969,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.004086444523113397</v>
+        <v>0.0007631619335715545</v>
       </c>
       <c r="D16" t="n">
-        <v>0.007599350723431568</v>
+        <v>0.0004384499456352019</v>
       </c>
     </row>
     <row r="17">
@@ -3095,14 +4985,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.002427038219831312</v>
+        <v>0.0005977563814497211</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003607869074374544</v>
+        <v>0.0002513368068618049</v>
       </c>
     </row>
     <row r="18">
@@ -3111,14 +5001,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001258370923873708</v>
+        <v>0.0005825194984571235</v>
       </c>
       <c r="D18" t="n">
-        <v>0.007879031268487964</v>
+        <v>0.0009586767377339917</v>
       </c>
     </row>
     <row r="19">
@@ -3127,14 +5017,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0001180161300002869</v>
+        <v>0.0005616933527610391</v>
       </c>
       <c r="D19" t="n">
-        <v>0.001684846935847453</v>
+        <v>0.000829353596009071</v>
       </c>
     </row>
     <row r="20">
@@ -3143,14 +5033,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-2.316683218667182e-05</v>
+        <v>0.0004460295429333461</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0003401099273970284</v>
+        <v>0.0006782670089298317</v>
       </c>
     </row>
     <row r="21">
@@ -3159,14 +5049,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.001797485393857956</v>
+        <v>0.0004073960740187954</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0003963589957708699</v>
+        <v>0.0005452346466679499</v>
       </c>
     </row>
     <row r="22">
@@ -3175,14 +5065,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.002974200876968913</v>
+        <v>0.0003666531390621785</v>
       </c>
       <c r="D22" t="n">
-        <v>0.003603926651393345</v>
+        <v>0.0004265232256629062</v>
       </c>
     </row>
     <row r="23">
@@ -3191,14 +5081,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.005320301525803484</v>
+        <v>0.0003438099849484844</v>
       </c>
       <c r="D23" t="n">
-        <v>0.002856217947864842</v>
+        <v>0.0005556239020614254</v>
       </c>
     </row>
     <row r="24">
@@ -3207,14 +5097,494 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.01052200717441567</v>
+        <v>0.0002408118842709972</v>
       </c>
       <c r="D24" t="n">
-        <v>0.008448912619199863</v>
+        <v>0.0003201131837060857</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0001786858351194631</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0008784799406043609</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0001645951792163758</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0007333194994945873</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0001186463784928926</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0005899887470113857</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>8.937264546736712e-05</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0002750365377112809</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>7.389424923087695e-05</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0005469189574644383</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4.52069388739873e-05</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0002536904485510328</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3.42480824476743e-06</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.67730498610776e-05</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>8.260306988083776e-07</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.077779574043899e-05</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-4.000226660227924e-06</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4.618455757052209e-05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-3.411137786994978e-05</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.001060918824704263</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>-5.17778356995513e-05</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0002903634799220685</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.000150599280333874</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.001161691316603162</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.0002125872452711342</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0002232838083595478</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.0002185553499171378</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.0002748523023249961</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.0002857415488159099</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.00063939773860479</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.0003352761374145863</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.00015225827502806</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.0003430546552071423</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.0002974642290730215</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>raw_syrup_color</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.0005387010116341684</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.0006524947907731651</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>raw_sugar_color</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.0006264921433683068</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.001025470680071647</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.0006793108609644549</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.0007272407173725139</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.0007137982229562412</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.0003862232186170492</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.0007357061907502071</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.0006398468600055023</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.0007792542138363778</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.00057411940886759</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>white_quality_ash_1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.001391353341655666</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.0006661100573220528</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.00142048526763473</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.001116923499046042</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.00147404199285428</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.002138484806446759</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.00164232973952384</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.001533643250496913</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.001715218802246488</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.002350138801836446</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.002235304855133002</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.0005336470482927344</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.02194819670442113</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.0172356459420017</v>
       </c>
     </row>
   </sheetData>
@@ -3228,7 +5598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3258,7 +5628,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.212173756026052</v>
+        <v>3.494570036984816</v>
       </c>
     </row>
     <row r="3">
@@ -3267,11 +5637,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7542731971311465</v>
+        <v>0.8278717553569916</v>
       </c>
     </row>
     <row r="4">
@@ -3280,11 +5650,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7375076242816028</v>
+        <v>0.8096637815779482</v>
       </c>
     </row>
     <row r="5">
@@ -3293,11 +5663,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6515954121834011</v>
+        <v>0.7206125907865633</v>
       </c>
     </row>
     <row r="6">
@@ -3310,7 +5680,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6396065787575287</v>
+        <v>0.692930115106654</v>
       </c>
     </row>
     <row r="7">
@@ -3319,11 +5689,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5195526016396697</v>
+        <v>0.6835552164975804</v>
       </c>
     </row>
     <row r="8">
@@ -3332,11 +5702,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1212993169885603</v>
+        <v>0.5379885324465508</v>
       </c>
     </row>
     <row r="9">
@@ -3345,11 +5715,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.113700174686393</v>
+        <v>0.379242517438104</v>
       </c>
     </row>
     <row r="10">
@@ -3358,11 +5728,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0815786599915107</v>
+        <v>0.3359020433126672</v>
       </c>
     </row>
     <row r="11">
@@ -3371,11 +5741,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.07984587565996115</v>
+        <v>0.1435422164601232</v>
       </c>
     </row>
     <row r="12">
@@ -3384,11 +5754,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.06575116056268948</v>
+        <v>0.1317323699311772</v>
       </c>
     </row>
     <row r="13">
@@ -3397,11 +5767,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.05788806699944393</v>
+        <v>0.1270074286839145</v>
       </c>
     </row>
     <row r="14">
@@ -3410,11 +5780,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.04077465670107427</v>
+        <v>0.1153905285354511</v>
       </c>
     </row>
     <row r="15">
@@ -3423,11 +5793,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03993354619787093</v>
+        <v>0.1053126868845498</v>
       </c>
     </row>
     <row r="16">
@@ -3436,11 +5806,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03987430440062978</v>
+        <v>0.1005354258648734</v>
       </c>
     </row>
     <row r="17">
@@ -3449,11 +5819,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03722798557969842</v>
+        <v>0.09638604513066973</v>
       </c>
     </row>
     <row r="18">
@@ -3462,11 +5832,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03414653424672087</v>
+        <v>0.09626847402319516</v>
       </c>
     </row>
     <row r="19">
@@ -3475,11 +5845,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.03380436337285975</v>
+        <v>0.09325412685993539</v>
       </c>
     </row>
     <row r="20">
@@ -3488,11 +5858,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02855948983542422</v>
+        <v>0.09116504893459432</v>
       </c>
     </row>
     <row r="21">
@@ -3501,11 +5871,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01668648957024255</v>
+        <v>0.08626015139544796</v>
       </c>
     </row>
     <row r="22">
@@ -3514,11 +5884,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0005879810303510702</v>
+        <v>0.0851360275683648</v>
       </c>
     </row>
     <row r="23">
@@ -3527,23 +5897,413 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.0847919741349199</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.08428896967463562</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.07919767859878446</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.07631384256049234</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.07578163492785395</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.07258453014363386</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.07165645316039404</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.07016872245278982</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.06857522721585374</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.06851967201496523</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.06405963718412444</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.06235080822428163</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.06094154532836749</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.06049050796130562</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>co2_percent</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C37" t="n">
+        <v>0.05715507498948114</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.05634842949855523</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.05594284296521712</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.05533991156553952</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.05407251610368879</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.04947098822750107</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0479470393911634</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_1</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.04417439044620686</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.04168210238512593</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>white_quality_ash_1</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.03999331145754903</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.02715593727123222</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.01820777581569377</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.008267973532043449</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.005673998930172619</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0008470847830079897</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3595,17 +6355,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D2" t="n">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-11 04:48:38 UTC</t>
+          <t>2026-06-11 05:10:04 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_invert.xlsx
+++ b/NN/reports/feature_importance_white_invert.xlsx
@@ -501,25 +501,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2392785615738154</v>
+        <v>0.2397114599236186</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7020986585130535</v>
+        <v>0.7016337763885306</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4995727851397694</v>
+        <v>0.5060052298913096</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.494570036984816</v>
+        <v>3.217199826770076</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -534,29 +534,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04822482659425891</v>
+        <v>0.07555841023038526</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03150354708145633</v>
+        <v>0.02545845305899258</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01109876378887378</v>
+        <v>0.0338395779654817</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8096637815779482</v>
+        <v>0.570501621941216</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -571,35 +571,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07626919443993266</v>
+        <v>0.04439170737250882</v>
       </c>
       <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.03074073436150961</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01091706533964594</v>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.02585223668624248</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.03187028379250897</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
+        <v>0.6266812437229703</v>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.7206125907865633</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
@@ -612,31 +612,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04517764016305515</v>
+        <v>0.04554023223891198</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0268120915623819</v>
+        <v>0.03078065349082866</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006611205109028462</v>
+        <v>0.006303376524204596</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8278717553569916</v>
+        <v>0.5494760899262703</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -645,35 +645,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04354714772811538</v>
+        <v>0.04116181535255319</v>
       </c>
       <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.04190947857859352</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.007697035974072464</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4483518173824934</v>
+      </c>
+      <c r="J6" t="n">
         <v>6</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.01898519156507235</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.00805747393289582</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.692930115106654</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5.75</v>
       </c>
     </row>
     <row r="7">
@@ -682,35 +682,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03750440698185665</v>
+        <v>0.04752706336620215</v>
       </c>
       <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02002625205703273</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.008045855817688996</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4345403141362918</v>
+      </c>
+      <c r="J7" t="n">
         <v>7</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.02372824530537914</v>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.006696035472563022</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.6835552164975804</v>
-      </c>
-      <c r="J7" t="n">
-        <v>6</v>
-      </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="8">
@@ -719,35 +719,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03656710558333551</v>
+        <v>0.03319575360829841</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04749754356039777</v>
+        <v>0.02386438557647791</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00625049212052472</v>
+        <v>0.005680258449072129</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5379885324465508</v>
+        <v>0.4977597455062317</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
@@ -760,31 +760,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01122596803523677</v>
+        <v>0.01102503516812055</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004788354009875164</v>
+        <v>0.004999106252286981</v>
       </c>
       <c r="F9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001578014665222949</v>
+      </c>
+      <c r="H9" t="n">
         <v>12</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.001521671257992752</v>
-      </c>
-      <c r="H9" t="n">
-        <v>11</v>
-      </c>
       <c r="I9" t="n">
-        <v>0.379242517438104</v>
+        <v>0.3646130720404273</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>10.75</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="10">
@@ -793,35 +793,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0100511404669856</v>
+        <v>0.006245177584653407</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00268917621439448</v>
+        <v>0.02242991503526511</v>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0008747056634513028</v>
+        <v>-0.0001168675218212956</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1317323699311772</v>
+        <v>0.3053870398541658</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>14.75</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.006033194988754455</v>
+        <v>0.00936647249038355</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02199497678977943</v>
+        <v>0.003334167945865149</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0005616933527610391</v>
+        <v>-0.0002662016962840186</v>
       </c>
       <c r="H11" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3359020433126672</v>
+        <v>0.1692192791397593</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>16.25</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.009748713791755263</v>
+        <v>0.01022013666717844</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002376658975893509</v>
+        <v>0.002706838273313216</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001688412376054249</v>
+        <v>0.0006447795586071115</v>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07631384256049234</v>
+        <v>0.07556918317667227</v>
       </c>
       <c r="J12" t="n">
         <v>25</v>
       </c>
       <c r="K12" t="n">
-        <v>18.25</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="13">
@@ -908,31 +908,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.01933099434164613</v>
+        <v>0.01923936412412708</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003598491630996464</v>
+        <v>0.003155865441077805</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00134922590741986</v>
+        <v>0.001983795074001027</v>
       </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05533991156553952</v>
+        <v>0.0293026860189376</v>
       </c>
       <c r="J13" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K13" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="14">
@@ -941,35 +941,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.009318921880566915</v>
+        <v>0.1869942634619149</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0.003302288829380732</v>
+        <v>0.005467398730094412</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0006264921433683068</v>
+        <v>-0.02065342838184092</v>
       </c>
       <c r="H14" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1435422164601232</v>
+        <v>0.1019034609444729</v>
       </c>
       <c r="J14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>21</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="15">
@@ -982,31 +982,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002627038859039394</v>
+        <v>0.003003792597306548</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00755226422145774</v>
+        <v>0.008368080722640158</v>
       </c>
       <c r="F15" t="n">
         <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001878851563722894</v>
+        <v>0.00205287097141571</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07919767859878446</v>
+        <v>0.09174321924453599</v>
       </c>
       <c r="J15" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
-        <v>22.25</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="16">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.007499976221640881</v>
+        <v>0.00273220366734912</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001830038906218063</v>
+        <v>0.007442495456984892</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0003438099849484844</v>
+        <v>0.001779321916018972</v>
       </c>
       <c r="H16" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.0905561334862468</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20</v>
+      </c>
+      <c r="K16" t="n">
         <v>22</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.1153905285354511</v>
-      </c>
-      <c r="J16" t="n">
-        <v>13</v>
-      </c>
-      <c r="K16" t="n">
-        <v>22.25</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.008998429978499685</v>
+        <v>0.01094492555671265</v>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001381383685993206</v>
+        <v>0.002595658814339139</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0005825194984571235</v>
+        <v>-0.0003553317883045026</v>
       </c>
       <c r="H17" t="n">
+        <v>40</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.093166113702428</v>
+      </c>
+      <c r="J17" t="n">
         <v>17</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.1270074286839145</v>
-      </c>
-      <c r="J17" t="n">
-        <v>12</v>
-      </c>
       <c r="K17" t="n">
-        <v>22.5</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="18">
@@ -1089,32 +1089,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.00310941172531338</v>
+        <v>0.008952661308969673</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
-        <v>0.007299630567400027</v>
+        <v>0.001415015655483802</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>0.002067810914767354</v>
+        <v>0.001001010980186467</v>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06857522721585374</v>
+        <v>0.08689986240107084</v>
       </c>
       <c r="J18" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
         <v>23.5</v>
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.1873988696456341</v>
+        <v>0.008186584491951624</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>0.004297102478633507</v>
+        <v>0.002722187506063482</v>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.02194819670442113</v>
+        <v>-0.0001324463469226989</v>
       </c>
       <c r="H19" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06851967201496523</v>
+        <v>0.08716430811798048</v>
       </c>
       <c r="J19" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
-        <v>24.75</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01096156082556342</v>
+        <v>0.009872146266763672</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002766614765557432</v>
+        <v>0.002538717532790274</v>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.000150599280333874</v>
+        <v>0.001844892000747178</v>
       </c>
       <c r="H20" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="I20" t="n">
-        <v>0.05715507498948114</v>
+        <v>0.0170518314484025</v>
       </c>
       <c r="J20" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K20" t="n">
-        <v>25.5</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="21">
@@ -1204,31 +1204,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.006737243445710204</v>
+        <v>0.006817526391507141</v>
       </c>
       <c r="D21" t="n">
         <v>26</v>
       </c>
       <c r="E21" t="n">
-        <v>0.003086007355575549</v>
+        <v>0.002806254462714189</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0005387010116341684</v>
+        <v>-0.0005601240915245054</v>
       </c>
       <c r="H21" t="n">
         <v>41</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0847919741349199</v>
+        <v>0.1254434905924073</v>
       </c>
       <c r="J21" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
-        <v>26.5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.008413229029541468</v>
+        <v>0.008543577892239676</v>
       </c>
       <c r="D22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00242472011931414</v>
+        <v>0.003057272628888262</v>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0002857415488159099</v>
+        <v>-0.002288258689627743</v>
       </c>
       <c r="H22" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I22" t="n">
-        <v>0.07016872245278982</v>
+        <v>0.1048756534983135</v>
       </c>
       <c r="J22" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>27.25</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.005886969378862915</v>
+        <v>0.007709983451279802</v>
       </c>
       <c r="D23" t="n">
+        <v>23</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.001800396019521926</v>
+      </c>
+      <c r="F23" t="n">
         <v>32</v>
       </c>
-      <c r="E23" t="n">
-        <v>0.001894858111643036</v>
-      </c>
-      <c r="F23" t="n">
-        <v>30</v>
-      </c>
       <c r="G23" t="n">
-        <v>0.0001645951792163758</v>
+        <v>0.0008432482924328521</v>
       </c>
       <c r="H23" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.07578163492785395</v>
+        <v>0.06889905503980076</v>
       </c>
       <c r="J23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K23" t="n">
-        <v>28.25</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.00719535894968134</v>
+        <v>0.01235405614677315</v>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>0.002032766054721776</v>
+        <v>0.005733252069745269</v>
       </c>
       <c r="F24" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0001186463784928926</v>
+        <v>-0.001176210536536926</v>
       </c>
       <c r="H24" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="I24" t="n">
-        <v>0.06049050796130562</v>
+        <v>0.05645906764891739</v>
       </c>
       <c r="J24" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K24" t="n">
-        <v>28.25</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="25">
@@ -1348,35 +1348,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.008421856859704643</v>
+        <v>0.007102439015698039</v>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00211370215016681</v>
+        <v>0.002249283561726051</v>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.00164232973952384</v>
+        <v>0.0001266286008866579</v>
       </c>
       <c r="H25" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="I25" t="n">
-        <v>0.08626015139544796</v>
+        <v>0.06451952483190393</v>
       </c>
       <c r="J25" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K25" t="n">
-        <v>28.75</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="26">
@@ -1385,35 +1385,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01224841297601068</v>
+        <v>0.01409531660167823</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>0.005984435520218248</v>
+        <v>0.00223530326313844</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.00142048526763473</v>
+        <v>-0.00159413418785822</v>
       </c>
       <c r="H26" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I26" t="n">
-        <v>0.01820777581569377</v>
+        <v>0.08685309691882903</v>
       </c>
       <c r="J26" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="K26" t="n">
-        <v>29.25</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="27">
@@ -1422,35 +1422,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01001883877945995</v>
+        <v>0.005575459110547282</v>
       </c>
       <c r="D27" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E27" t="n">
-        <v>0.002063085015217124</v>
+        <v>0.001838011076629077</v>
       </c>
       <c r="F27" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.00147404199285428</v>
+        <v>-0.0001176716425592028</v>
       </c>
       <c r="H27" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="I27" t="n">
-        <v>0.07258453014363386</v>
+        <v>0.1025833414056709</v>
       </c>
       <c r="J27" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>29.25</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="28">
@@ -1459,35 +1459,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01413753573266014</v>
+        <v>0.008005821997730537</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E28" t="n">
-        <v>0.002002564792444114</v>
+        <v>0.001818644195808831</v>
       </c>
       <c r="F28" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.001715218802246488</v>
+        <v>-0.0003362640018051977</v>
       </c>
       <c r="H28" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="I28" t="n">
-        <v>0.07165645316039404</v>
+        <v>0.06885634059986057</v>
       </c>
       <c r="J28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K28" t="n">
-        <v>29.25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
@@ -1496,35 +1496,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002624802007073004</v>
+        <v>0.005910721975406701</v>
       </c>
       <c r="D29" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E29" t="n">
-        <v>0.002696027020492809</v>
+        <v>0.00176602312229494</v>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G29" t="n">
-        <v>-4.000226660227924e-06</v>
+        <v>3.235721233372235e-05</v>
       </c>
       <c r="H29" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1053126868845498</v>
+        <v>0.06251763089092144</v>
       </c>
       <c r="J29" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K29" t="n">
-        <v>29.25</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="30">
@@ -1533,35 +1533,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.008441719886500443</v>
+        <v>0.006423611938019026</v>
       </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00315498963606712</v>
+        <v>0.001707886595362008</v>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.002235304855133002</v>
+        <v>0.0003768028270288881</v>
       </c>
       <c r="H30" t="n">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="I30" t="n">
-        <v>0.06235080822428163</v>
+        <v>0.04840436921305802</v>
       </c>
       <c r="J30" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="K30" t="n">
-        <v>30</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="31">
@@ -1570,35 +1570,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.005585420911260726</v>
+        <v>0.007352663814316513</v>
       </c>
       <c r="D31" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001960520668127841</v>
+        <v>0.002274586281777611</v>
       </c>
       <c r="F31" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0002185553499171378</v>
+        <v>-0.001000268056234965</v>
       </c>
       <c r="H31" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0851360275683648</v>
+        <v>0.05563326314330963</v>
       </c>
       <c r="J31" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="K31" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
@@ -1607,35 +1607,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.006283205113379683</v>
+        <v>0.00510644188920121</v>
       </c>
       <c r="D32" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001548638105296112</v>
+        <v>0.001406914216697856</v>
       </c>
       <c r="F32" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0007631619335715545</v>
+        <v>0.0001024898684281017</v>
       </c>
       <c r="H32" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0479470393911634</v>
+        <v>0.08363311392339945</v>
       </c>
       <c r="J32" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="K32" t="n">
-        <v>30.25</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="33">
@@ -1644,35 +1644,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.003585041625533856</v>
+        <v>0.00354871592234068</v>
       </c>
       <c r="D33" t="n">
         <v>43</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001145237844529358</v>
+        <v>0.002118530515049348</v>
       </c>
       <c r="F33" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0005977563814497211</v>
+        <v>0.0009197150622953898</v>
       </c>
       <c r="H33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1005354258648734</v>
+        <v>0.02641531674244479</v>
       </c>
       <c r="J33" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="K33" t="n">
-        <v>30.25</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="34">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.007913312452445673</v>
+        <v>0.006301249394623563</v>
       </c>
       <c r="D34" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001828120984901879</v>
+        <v>0.001524426275126526</v>
       </c>
       <c r="F34" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G34" t="n">
-        <v>-3.411137786994978e-05</v>
+        <v>0.0007888315273503865</v>
       </c>
       <c r="H34" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="I34" t="n">
-        <v>0.05594284296521712</v>
+        <v>0.01399424186190457</v>
       </c>
       <c r="J34" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="K34" t="n">
-        <v>31.25</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="35">
@@ -1718,35 +1718,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.006484374560023289</v>
+        <v>0.005663959699826464</v>
       </c>
       <c r="D35" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E35" t="n">
-        <v>0.001624730669403799</v>
+        <v>0.001527646230426919</v>
       </c>
       <c r="F35" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0001786858351194631</v>
+        <v>0.0003960994362950831</v>
       </c>
       <c r="H35" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I35" t="n">
-        <v>0.04168210238512593</v>
+        <v>0.03837673494691041</v>
       </c>
       <c r="J35" t="n">
         <v>44</v>
       </c>
       <c r="K35" t="n">
-        <v>32.25</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="36">
@@ -1755,35 +1755,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.005388925526459861</v>
+        <v>0.003486287167757974</v>
       </c>
       <c r="D36" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00141860717341115</v>
+        <v>0.001085018578042294</v>
       </c>
       <c r="F36" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G36" t="n">
-        <v>7.389424923087695e-05</v>
+        <v>0.0009240955433844622</v>
       </c>
       <c r="H36" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I36" t="n">
-        <v>0.08428896967463562</v>
+        <v>0.07160750944347871</v>
       </c>
       <c r="J36" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K36" t="n">
-        <v>32.25</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="37">
@@ -1792,35 +1792,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.003929903466314806</v>
+        <v>0.008282611440005038</v>
       </c>
       <c r="D37" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E37" t="n">
-        <v>0.001166344695713981</v>
+        <v>0.001839160971955053</v>
       </c>
       <c r="F37" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G37" t="n">
-        <v>8.937264546736712e-05</v>
+        <v>-0.001754181676085709</v>
       </c>
       <c r="H37" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I37" t="n">
-        <v>0.09638604513066973</v>
+        <v>0.05509654477754156</v>
       </c>
       <c r="J37" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="K37" t="n">
-        <v>32.5</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="38">
@@ -1829,35 +1829,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.006130200583785508</v>
+        <v>0.006066651165962322</v>
       </c>
       <c r="D38" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E38" t="n">
-        <v>0.001508301193739607</v>
+        <v>0.001498815679236424</v>
       </c>
       <c r="F38" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0003666531390621785</v>
+        <v>0.0003175231346934093</v>
       </c>
       <c r="H38" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I38" t="n">
-        <v>0.04947098822750107</v>
+        <v>0.04226815071445378</v>
       </c>
       <c r="J38" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K38" t="n">
-        <v>32.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39">
@@ -1866,35 +1866,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.00351009649134086</v>
+        <v>0.005166038317832973</v>
       </c>
       <c r="D39" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E39" t="n">
-        <v>0.002308898723905178</v>
+        <v>0.001427125570284084</v>
       </c>
       <c r="F39" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0008768741801767454</v>
+        <v>-0.0005821095161208434</v>
       </c>
       <c r="H39" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>0.09512582013044524</v>
       </c>
       <c r="J39" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="K39" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40">
@@ -1903,35 +1903,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.003582832798197596</v>
+        <v>0.0002476139724240329</v>
       </c>
       <c r="D40" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E40" t="n">
-        <v>0.00112987366556819</v>
+        <v>0.00303423736790386</v>
       </c>
       <c r="F40" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0002408118842709972</v>
+        <v>-7.469104474953082e-05</v>
       </c>
       <c r="H40" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I40" t="n">
-        <v>0.09626847402319516</v>
+        <v>0.05172742536939401</v>
       </c>
       <c r="J40" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="K40" t="n">
-        <v>33.25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
@@ -1940,35 +1940,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.005251037937169436</v>
+        <v>0.004867321492435589</v>
       </c>
       <c r="D41" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E41" t="n">
-        <v>0.001534295373496901</v>
+        <v>0.001226467172121567</v>
       </c>
       <c r="F41" t="n">
+        <v>45</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.0003226108771942737</v>
+      </c>
+      <c r="H41" t="n">
         <v>37</v>
       </c>
-      <c r="G41" t="n">
-        <v>-0.0003430546552071423</v>
-      </c>
-      <c r="H41" t="n">
-        <v>40</v>
-      </c>
       <c r="I41" t="n">
-        <v>0.09116504893459432</v>
+        <v>0.09940350944057874</v>
       </c>
       <c r="J41" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K41" t="n">
-        <v>33.5</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="42">
@@ -1977,35 +1977,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.005398859642255072</v>
+        <v>0.00353229525521392</v>
       </c>
       <c r="D42" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E42" t="n">
-        <v>0.001486162317343822</v>
+        <v>0.001148045527509397</v>
       </c>
       <c r="F42" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0004073960740187954</v>
+        <v>0.0003445564674893431</v>
       </c>
       <c r="H42" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I42" t="n">
-        <v>0.05407251610368879</v>
+        <v>0.06996116746814574</v>
       </c>
       <c r="J42" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="K42" t="n">
-        <v>33.75</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="43">
@@ -2014,35 +2014,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.004569159793192584</v>
+        <v>0.005066300372071085</v>
       </c>
       <c r="D43" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E43" t="n">
-        <v>0.001352934041462639</v>
+        <v>0.001414835809914732</v>
       </c>
       <c r="F43" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G43" t="n">
-        <v>-5.17778356995513e-05</v>
+        <v>0.0003557141340886805</v>
       </c>
       <c r="H43" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I43" t="n">
-        <v>0.09325412685993539</v>
+        <v>0.05161042521237746</v>
       </c>
       <c r="J43" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="K43" t="n">
-        <v>34.25</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="44">
@@ -2051,35 +2051,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.007247496005988886</v>
+        <v>0.01009547244346568</v>
       </c>
       <c r="D44" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E44" t="n">
-        <v>0.002238429857352846</v>
+        <v>0.001863924872907539</v>
       </c>
       <c r="F44" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.001391353341655666</v>
+        <v>-0.001835082163533341</v>
       </c>
       <c r="H44" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I44" t="n">
-        <v>0.03999331145754903</v>
+        <v>0.004580767337865055</v>
       </c>
       <c r="J44" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K44" t="n">
-        <v>35</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="45">
@@ -2088,35 +2088,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.004957844870211341</v>
+        <v>0.005592008449403107</v>
       </c>
       <c r="D45" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E45" t="n">
-        <v>0.001424224768173518</v>
+        <v>0.001526035484687893</v>
       </c>
       <c r="F45" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0004460295429333461</v>
+        <v>-0.000697389370586865</v>
       </c>
       <c r="H45" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="I45" t="n">
-        <v>0.04417439044620686</v>
+        <v>0.06237385659098482</v>
       </c>
       <c r="J45" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K45" t="n">
-        <v>35.5</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="46">
@@ -2125,35 +2125,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.005570404394293522</v>
+        <v>0.006159608075331081</v>
       </c>
       <c r="D46" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E46" t="n">
-        <v>0.00149890594579983</v>
+        <v>0.001527400343618118</v>
       </c>
       <c r="F46" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.0007137982229562412</v>
+        <v>-0.0008029358153880173</v>
       </c>
       <c r="H46" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I46" t="n">
-        <v>0.06405963718412444</v>
+        <v>0.05214674385507667</v>
       </c>
       <c r="J46" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K46" t="n">
-        <v>37.25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47">
@@ -2162,35 +2162,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.006218100461482147</v>
+        <v>0.005176066401549557</v>
       </c>
       <c r="D47" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E47" t="n">
-        <v>0.001593668657358322</v>
+        <v>0.001200527758229824</v>
       </c>
       <c r="F47" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.0007357061907502071</v>
+        <v>-0.001400142969639295</v>
       </c>
       <c r="H47" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I47" t="n">
-        <v>0.005673998930172619</v>
+        <v>0.09083086368305082</v>
       </c>
       <c r="J47" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="K47" t="n">
-        <v>39.5</v>
+        <v>37.25</v>
       </c>
     </row>
     <row r="48">
@@ -2203,31 +2203,31 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.001663360782748484</v>
+        <v>0.001637804208301506</v>
       </c>
       <c r="D48" t="n">
         <v>48</v>
       </c>
       <c r="E48" t="n">
-        <v>0.001757441345586086</v>
+        <v>0.001942218956458511</v>
       </c>
       <c r="F48" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G48" t="n">
-        <v>4.52069388739873e-05</v>
+        <v>-0.0001130712297018111</v>
       </c>
       <c r="H48" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K48" t="n">
-        <v>40.25</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="49">
@@ -2236,35 +2236,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.005366524830917239</v>
+        <v>0.004171436267001193</v>
       </c>
       <c r="D49" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E49" t="n">
-        <v>0.001147542919868919</v>
+        <v>0.001399417616068388</v>
       </c>
       <c r="F49" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.0006793108609644549</v>
+        <v>-0.0001846802514274159</v>
       </c>
       <c r="H49" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I49" t="n">
-        <v>0.05634842949855523</v>
+        <v>0.05086326753294923</v>
       </c>
       <c r="J49" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K49" t="n">
-        <v>40.75</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50">
@@ -2273,35 +2273,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.004784381846940302</v>
+        <v>0.0001276585670788098</v>
       </c>
       <c r="D50" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E50" t="n">
-        <v>0.001129882934385539</v>
+        <v>9.7443621415004e-05</v>
       </c>
       <c r="F50" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.0007792542138363778</v>
+        <v>-1.359412867504295e-05</v>
       </c>
       <c r="H50" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="I50" t="n">
-        <v>0.06094154532836749</v>
+        <v>0.05798891292858066</v>
       </c>
       <c r="J50" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K50" t="n">
-        <v>42</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="51">
@@ -2310,35 +2310,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.0009385338490848201</v>
+        <v>0.00420572754496519</v>
       </c>
       <c r="D51" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0003852495780667005</v>
+        <v>0.001186039531280904</v>
       </c>
       <c r="F51" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.0002125872452711342</v>
+        <v>-0.0005687217856254589</v>
       </c>
       <c r="H51" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I51" t="n">
-        <v>0.02715593727123222</v>
+        <v>0.04887474577110318</v>
       </c>
       <c r="J51" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K51" t="n">
-        <v>45.5</v>
+        <v>42.75</v>
       </c>
     </row>
     <row r="52">
@@ -2351,31 +2351,31 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.000409422954063243</v>
+        <v>0.0003523387898693042</v>
       </c>
       <c r="D52" t="n">
         <v>51</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0003466637184265833</v>
+        <v>0.0002858886754939298</v>
       </c>
       <c r="F52" t="n">
         <v>52</v>
       </c>
       <c r="G52" t="n">
-        <v>3.42480824476743e-06</v>
+        <v>8.437338592059972e-06</v>
       </c>
       <c r="H52" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0008470847830079897</v>
+        <v>0.001886324116872284</v>
       </c>
       <c r="J52" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K52" t="n">
-        <v>45.75</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="53">
@@ -2384,32 +2384,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.0001275446562220433</v>
+        <v>0.0009456147320250668</v>
       </c>
       <c r="D53" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E53" t="n">
-        <v>9.828944389033009e-05</v>
+        <v>0.0003530842890096436</v>
       </c>
       <c r="F53" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G53" t="n">
-        <v>8.260306988083776e-07</v>
+        <v>-0.000234381195863842</v>
       </c>
       <c r="H53" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I53" t="n">
-        <v>0.008267973532043449</v>
+        <v>0.007422689391729964</v>
       </c>
       <c r="J53" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K53" t="n">
         <v>46.25</v>
@@ -2425,31 +2425,31 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.0004672653828441226</v>
+        <v>0.0004403946182090141</v>
       </c>
       <c r="D54" t="n">
         <v>50</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0005593842487669528</v>
+        <v>0.0004907007807858693</v>
       </c>
       <c r="F54" t="n">
         <v>50</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.0003352761374145863</v>
+        <v>-0.0003381286588022614</v>
       </c>
       <c r="H54" t="n">
         <v>39</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>0.007442339912218543</v>
       </c>
       <c r="J54" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K54" t="n">
-        <v>47.5</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2392785615738154</v>
+        <v>0.2397114599236186</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7020986585130535</v>
+        <v>0.7016337763885306</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4995727851397694</v>
+        <v>0.5060052298913096</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.494570036984816</v>
+        <v>3.217199826770076</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -2566,29 +2566,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04822482659425891</v>
+        <v>0.07555841023038526</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03150354708145633</v>
+        <v>0.02545845305899258</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01109876378887378</v>
+        <v>0.0338395779654817</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8096637815779482</v>
+        <v>0.570501621941216</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -2603,35 +2603,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07626919443993266</v>
+        <v>0.04439170737250882</v>
       </c>
       <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.03074073436150961</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01091706533964594</v>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.02585223668624248</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.03187028379250897</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
+        <v>0.6266812437229703</v>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.7206125907865633</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
@@ -2644,31 +2644,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04517764016305515</v>
+        <v>0.04554023223891198</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0268120915623819</v>
+        <v>0.03078065349082866</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006611205109028462</v>
+        <v>0.006303376524204596</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8278717553569916</v>
+        <v>0.5494760899262703</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -2677,35 +2677,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04354714772811538</v>
+        <v>0.04116181535255319</v>
       </c>
       <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.04190947857859352</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.007697035974072464</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4483518173824934</v>
+      </c>
+      <c r="J6" t="n">
         <v>6</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.01898519156507235</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.00805747393289582</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.692930115106654</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5.75</v>
       </c>
     </row>
     <row r="7">
@@ -2714,35 +2714,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03750440698185665</v>
+        <v>0.04752706336620215</v>
       </c>
       <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02002625205703273</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.008045855817688996</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4345403141362918</v>
+      </c>
+      <c r="J7" t="n">
         <v>7</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.02372824530537914</v>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.006696035472563022</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.6835552164975804</v>
-      </c>
-      <c r="J7" t="n">
-        <v>6</v>
-      </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="8">
@@ -2751,35 +2751,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03656710558333551</v>
+        <v>0.03319575360829841</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04749754356039777</v>
+        <v>0.02386438557647791</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00625049212052472</v>
+        <v>0.005680258449072129</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5379885324465508</v>
+        <v>0.4977597455062317</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
@@ -2792,31 +2792,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01122596803523677</v>
+        <v>0.01102503516812055</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004788354009875164</v>
+        <v>0.004999106252286981</v>
       </c>
       <c r="F9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001578014665222949</v>
+      </c>
+      <c r="H9" t="n">
         <v>12</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.001521671257992752</v>
-      </c>
-      <c r="H9" t="n">
-        <v>11</v>
-      </c>
       <c r="I9" t="n">
-        <v>0.379242517438104</v>
+        <v>0.3646130720404273</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>10.75</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="10">
@@ -2825,35 +2825,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0100511404669856</v>
+        <v>0.006245177584653407</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00268917621439448</v>
+        <v>0.02242991503526511</v>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0008747056634513028</v>
+        <v>-0.0001168675218212956</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1317323699311772</v>
+        <v>0.3053870398541658</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>14.75</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -2862,35 +2862,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.006033194988754455</v>
+        <v>0.00936647249038355</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02199497678977943</v>
+        <v>0.003334167945865149</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0005616933527610391</v>
+        <v>-0.0002662016962840186</v>
       </c>
       <c r="H11" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3359020433126672</v>
+        <v>0.1692192791397593</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>16.25</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="12">
@@ -2899,35 +2899,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.009748713791755263</v>
+        <v>0.01022013666717844</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002376658975893509</v>
+        <v>0.002706838273313216</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001688412376054249</v>
+        <v>0.0006447795586071115</v>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07631384256049234</v>
+        <v>0.07556918317667227</v>
       </c>
       <c r="J12" t="n">
         <v>25</v>
       </c>
       <c r="K12" t="n">
-        <v>18.25</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="13">
@@ -2940,31 +2940,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.01933099434164613</v>
+        <v>0.01923936412412708</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003598491630996464</v>
+        <v>0.003155865441077805</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00134922590741986</v>
+        <v>0.001983795074001027</v>
       </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05533991156553952</v>
+        <v>0.0293026860189376</v>
       </c>
       <c r="J13" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K13" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="14">
@@ -2973,35 +2973,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.009318921880566915</v>
+        <v>0.1869942634619149</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0.003302288829380732</v>
+        <v>0.005467398730094412</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0006264921433683068</v>
+        <v>-0.02065342838184092</v>
       </c>
       <c r="H14" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1435422164601232</v>
+        <v>0.1019034609444729</v>
       </c>
       <c r="J14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>21</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="15">
@@ -3014,31 +3014,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002627038859039394</v>
+        <v>0.003003792597306548</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00755226422145774</v>
+        <v>0.008368080722640158</v>
       </c>
       <c r="F15" t="n">
         <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001878851563722894</v>
+        <v>0.00205287097141571</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07919767859878446</v>
+        <v>0.09174321924453599</v>
       </c>
       <c r="J15" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
-        <v>22.25</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="16">
@@ -3047,35 +3047,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.007499976221640881</v>
+        <v>0.00273220366734912</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001830038906218063</v>
+        <v>0.007442495456984892</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0003438099849484844</v>
+        <v>0.001779321916018972</v>
       </c>
       <c r="H16" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.0905561334862468</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20</v>
+      </c>
+      <c r="K16" t="n">
         <v>22</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.1153905285354511</v>
-      </c>
-      <c r="J16" t="n">
-        <v>13</v>
-      </c>
-      <c r="K16" t="n">
-        <v>22.25</v>
       </c>
     </row>
     <row r="17">
@@ -3084,35 +3084,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.008998429978499685</v>
+        <v>0.01094492555671265</v>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001381383685993206</v>
+        <v>0.002595658814339139</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0005825194984571235</v>
+        <v>-0.0003553317883045026</v>
       </c>
       <c r="H17" t="n">
+        <v>40</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.093166113702428</v>
+      </c>
+      <c r="J17" t="n">
         <v>17</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.1270074286839145</v>
-      </c>
-      <c r="J17" t="n">
-        <v>12</v>
-      </c>
       <c r="K17" t="n">
-        <v>22.5</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="18">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.00310941172531338</v>
+        <v>0.008952661308969673</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
-        <v>0.007299630567400027</v>
+        <v>0.001415015655483802</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>0.002067810914767354</v>
+        <v>0.001001010980186467</v>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06857522721585374</v>
+        <v>0.08689986240107084</v>
       </c>
       <c r="J18" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
         <v>23.5</v>
@@ -3158,35 +3158,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.1873988696456341</v>
+        <v>0.008186584491951624</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>0.004297102478633507</v>
+        <v>0.002722187506063482</v>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.02194819670442113</v>
+        <v>-0.0001324463469226989</v>
       </c>
       <c r="H19" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06851967201496523</v>
+        <v>0.08716430811798048</v>
       </c>
       <c r="J19" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
-        <v>24.75</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="20">
@@ -3195,35 +3195,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01096156082556342</v>
+        <v>0.009872146266763672</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002766614765557432</v>
+        <v>0.002538717532790274</v>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.000150599280333874</v>
+        <v>0.001844892000747178</v>
       </c>
       <c r="H20" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="I20" t="n">
-        <v>0.05715507498948114</v>
+        <v>0.0170518314484025</v>
       </c>
       <c r="J20" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K20" t="n">
-        <v>25.5</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="21">
@@ -3236,31 +3236,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.006737243445710204</v>
+        <v>0.006817526391507141</v>
       </c>
       <c r="D21" t="n">
         <v>26</v>
       </c>
       <c r="E21" t="n">
-        <v>0.003086007355575549</v>
+        <v>0.002806254462714189</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0005387010116341684</v>
+        <v>-0.0005601240915245054</v>
       </c>
       <c r="H21" t="n">
         <v>41</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0847919741349199</v>
+        <v>0.1254434905924073</v>
       </c>
       <c r="J21" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
-        <v>26.5</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2392785615738154</v>
+        <v>0.2397114599236186</v>
       </c>
     </row>
     <row r="3">
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1873988696456341</v>
+        <v>0.1869942634619149</v>
       </c>
     </row>
     <row r="4">
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07626919443993266</v>
+        <v>0.07555841023038526</v>
       </c>
     </row>
     <row r="5">
@@ -3339,11 +3339,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04822482659425891</v>
+        <v>0.04752706336620215</v>
       </c>
     </row>
     <row r="6">
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04517764016305515</v>
+        <v>0.04554023223891198</v>
       </c>
     </row>
     <row r="7">
@@ -3365,11 +3365,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04354714772811538</v>
+        <v>0.04439170737250882</v>
       </c>
     </row>
     <row r="8">
@@ -3378,11 +3378,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03750440698185665</v>
+        <v>0.04116181535255319</v>
       </c>
     </row>
     <row r="9">
@@ -3391,11 +3391,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03656710558333551</v>
+        <v>0.03319575360829841</v>
       </c>
     </row>
     <row r="10">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.01933099434164613</v>
+        <v>0.01923936412412708</v>
       </c>
     </row>
     <row r="11">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01413753573266014</v>
+        <v>0.01409531660167823</v>
       </c>
     </row>
     <row r="12">
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.01224841297601068</v>
+        <v>0.01235405614677315</v>
       </c>
     </row>
     <row r="13">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.01122596803523677</v>
+        <v>0.01102503516812055</v>
       </c>
     </row>
     <row r="14">
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.01096156082556342</v>
+        <v>0.01094492555671265</v>
       </c>
     </row>
     <row r="15">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0100511404669856</v>
+        <v>0.01022013666717844</v>
       </c>
     </row>
     <row r="16">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01001883877945995</v>
+        <v>0.01009547244346568</v>
       </c>
     </row>
     <row r="17">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.009748713791755263</v>
+        <v>0.009872146266763672</v>
       </c>
     </row>
     <row r="18">
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.009318921880566915</v>
+        <v>0.00936647249038355</v>
       </c>
     </row>
     <row r="19">
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.008998429978499685</v>
+        <v>0.008952661308969673</v>
       </c>
     </row>
     <row r="20">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.008441719886500443</v>
+        <v>0.008543577892239676</v>
       </c>
     </row>
     <row r="21">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.008421856859704643</v>
+        <v>0.008282611440005038</v>
       </c>
     </row>
     <row r="22">
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.008413229029541468</v>
+        <v>0.008186584491951624</v>
       </c>
     </row>
     <row r="23">
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.007913312452445673</v>
+        <v>0.008005821997730537</v>
       </c>
     </row>
     <row r="24">
@@ -3590,7 +3590,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.007499976221640881</v>
+        <v>0.007709983451279802</v>
       </c>
     </row>
     <row r="25">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.007247496005988886</v>
+        <v>0.007352663814316513</v>
       </c>
     </row>
     <row r="26">
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.00719535894968134</v>
+        <v>0.007102439015698039</v>
       </c>
     </row>
     <row r="27">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.006737243445710204</v>
+        <v>0.006817526391507141</v>
       </c>
     </row>
     <row r="28">
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.006484374560023289</v>
+        <v>0.006423611938019026</v>
       </c>
     </row>
     <row r="29">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.006283205113379683</v>
+        <v>0.006301249394623563</v>
       </c>
     </row>
     <row r="30">
@@ -3664,11 +3664,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.006218100461482147</v>
+        <v>0.006245177584653407</v>
       </c>
     </row>
     <row r="31">
@@ -3677,11 +3677,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.006130200583785508</v>
+        <v>0.006159608075331081</v>
       </c>
     </row>
     <row r="32">
@@ -3690,11 +3690,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.006033194988754455</v>
+        <v>0.006066651165962322</v>
       </c>
     </row>
     <row r="33">
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.005886969378862915</v>
+        <v>0.005910721975406701</v>
       </c>
     </row>
     <row r="34">
@@ -3716,11 +3716,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.005585420911260726</v>
+        <v>0.005663959699826464</v>
       </c>
     </row>
     <row r="35">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.005570404394293522</v>
+        <v>0.005592008449403107</v>
       </c>
     </row>
     <row r="36">
@@ -3742,11 +3742,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.005398859642255072</v>
+        <v>0.005575459110547282</v>
       </c>
     </row>
     <row r="37">
@@ -3755,11 +3755,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.005388925526459861</v>
+        <v>0.005176066401549557</v>
       </c>
     </row>
     <row r="38">
@@ -3768,11 +3768,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.005366524830917239</v>
+        <v>0.005166038317832973</v>
       </c>
     </row>
     <row r="39">
@@ -3781,11 +3781,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.005251037937169436</v>
+        <v>0.00510644188920121</v>
       </c>
     </row>
     <row r="40">
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.004957844870211341</v>
+        <v>0.005066300372071085</v>
       </c>
     </row>
     <row r="41">
@@ -3807,11 +3807,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.004784381846940302</v>
+        <v>0.004867321492435589</v>
       </c>
     </row>
     <row r="42">
@@ -3820,11 +3820,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.004569159793192584</v>
+        <v>0.00420572754496519</v>
       </c>
     </row>
     <row r="43">
@@ -3833,11 +3833,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.003929903466314806</v>
+        <v>0.004171436267001193</v>
       </c>
     </row>
     <row r="44">
@@ -3846,11 +3846,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.003585041625533856</v>
+        <v>0.00354871592234068</v>
       </c>
     </row>
     <row r="45">
@@ -3859,11 +3859,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.003582832798197596</v>
+        <v>0.00353229525521392</v>
       </c>
     </row>
     <row r="46">
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.00351009649134086</v>
+        <v>0.003486287167757974</v>
       </c>
     </row>
     <row r="47">
@@ -3885,11 +3885,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.00310941172531338</v>
+        <v>0.003003792597306548</v>
       </c>
     </row>
     <row r="48">
@@ -3898,11 +3898,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.002627038859039394</v>
+        <v>0.00273220366734912</v>
       </c>
     </row>
     <row r="49">
@@ -3915,7 +3915,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.001663360782748484</v>
+        <v>0.001637804208301506</v>
       </c>
     </row>
     <row r="50">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0009385338490848201</v>
+        <v>0.0009456147320250668</v>
       </c>
     </row>
     <row r="51">
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.0004672653828441226</v>
+        <v>0.0004403946182090141</v>
       </c>
     </row>
     <row r="52">
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.000409422954063243</v>
+        <v>0.0003523387898693042</v>
       </c>
     </row>
     <row r="53">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.0002624802007073004</v>
+        <v>0.0002476139724240329</v>
       </c>
     </row>
     <row r="54">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.0001275446562220433</v>
+        <v>0.0001276585670788098</v>
       </c>
     </row>
   </sheetData>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7020986585130535</v>
+        <v>0.7016337763885306</v>
       </c>
     </row>
     <row r="3">
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04749754356039777</v>
+        <v>0.04190947857859352</v>
       </c>
     </row>
     <row r="4">
@@ -4046,11 +4046,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03150354708145633</v>
+        <v>0.03078065349082866</v>
       </c>
     </row>
     <row r="5">
@@ -4059,11 +4059,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0268120915623819</v>
+        <v>0.03074073436150961</v>
       </c>
     </row>
     <row r="6">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02585223668624248</v>
+        <v>0.02545845305899258</v>
       </c>
     </row>
     <row r="7">
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02372824530537914</v>
+        <v>0.02386438557647791</v>
       </c>
     </row>
     <row r="8">
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02199497678977943</v>
+        <v>0.02242991503526511</v>
       </c>
     </row>
     <row r="9">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01898519156507235</v>
+        <v>0.02002625205703273</v>
       </c>
     </row>
     <row r="10">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.00755226422145774</v>
+        <v>0.008368080722640158</v>
       </c>
     </row>
     <row r="11">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.007299630567400027</v>
+        <v>0.007442495456984892</v>
       </c>
     </row>
     <row r="12">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.005984435520218248</v>
+        <v>0.005733252069745269</v>
       </c>
     </row>
     <row r="13">
@@ -4163,11 +4163,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.004788354009875164</v>
+        <v>0.005467398730094412</v>
       </c>
     </row>
     <row r="14">
@@ -4176,11 +4176,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.004297102478633507</v>
+        <v>0.004999106252286981</v>
       </c>
     </row>
     <row r="15">
@@ -4189,11 +4189,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003598491630996464</v>
+        <v>0.003334167945865149</v>
       </c>
     </row>
     <row r="16">
@@ -4202,11 +4202,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.003302288829380732</v>
+        <v>0.003155865441077805</v>
       </c>
     </row>
     <row r="17">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.00315498963606712</v>
+        <v>0.003057272628888262</v>
       </c>
     </row>
     <row r="18">
@@ -4228,11 +4228,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.003086007355575549</v>
+        <v>0.00303423736790386</v>
       </c>
     </row>
     <row r="19">
@@ -4241,11 +4241,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002766614765557432</v>
+        <v>0.002806254462714189</v>
       </c>
     </row>
     <row r="20">
@@ -4254,11 +4254,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002696027020492809</v>
+        <v>0.002722187506063482</v>
       </c>
     </row>
     <row r="21">
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.00268917621439448</v>
+        <v>0.002706838273313216</v>
       </c>
     </row>
     <row r="22">
@@ -4280,11 +4280,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.00242472011931414</v>
+        <v>0.002595658814339139</v>
       </c>
     </row>
     <row r="23">
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.002376658975893509</v>
+        <v>0.002538717532790274</v>
       </c>
     </row>
     <row r="24">
@@ -4306,11 +4306,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.002308898723905178</v>
+        <v>0.002274586281777611</v>
       </c>
     </row>
     <row r="25">
@@ -4319,11 +4319,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.002238429857352846</v>
+        <v>0.002249283561726051</v>
       </c>
     </row>
     <row r="26">
@@ -4332,11 +4332,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.00211370215016681</v>
+        <v>0.00223530326313844</v>
       </c>
     </row>
     <row r="27">
@@ -4345,11 +4345,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.002063085015217124</v>
+        <v>0.002118530515049348</v>
       </c>
     </row>
     <row r="28">
@@ -4358,11 +4358,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.002032766054721776</v>
+        <v>0.001942218956458511</v>
       </c>
     </row>
     <row r="29">
@@ -4371,11 +4371,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.002002564792444114</v>
+        <v>0.001863924872907539</v>
       </c>
     </row>
     <row r="30">
@@ -4384,11 +4384,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.001960520668127841</v>
+        <v>0.001839160971955053</v>
       </c>
     </row>
     <row r="31">
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.001894858111643036</v>
+        <v>0.001838011076629077</v>
       </c>
     </row>
     <row r="32">
@@ -4410,11 +4410,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001830038906218063</v>
+        <v>0.001818644195808831</v>
       </c>
     </row>
     <row r="33">
@@ -4423,11 +4423,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.001828120984901879</v>
+        <v>0.001800396019521926</v>
       </c>
     </row>
     <row r="34">
@@ -4436,11 +4436,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.001757441345586086</v>
+        <v>0.00176602312229494</v>
       </c>
     </row>
     <row r="35">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001624730669403799</v>
+        <v>0.001707886595362008</v>
       </c>
     </row>
     <row r="36">
@@ -4462,11 +4462,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.001593668657358322</v>
+        <v>0.001527646230426919</v>
       </c>
     </row>
     <row r="37">
@@ -4475,11 +4475,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.001548638105296112</v>
+        <v>0.001527400343618118</v>
       </c>
     </row>
     <row r="38">
@@ -4488,11 +4488,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.001534295373496901</v>
+        <v>0.001526035484687893</v>
       </c>
     </row>
     <row r="39">
@@ -4501,11 +4501,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.001508301193739607</v>
+        <v>0.001524426275126526</v>
       </c>
     </row>
     <row r="40">
@@ -4514,11 +4514,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.00149890594579983</v>
+        <v>0.001498815679236424</v>
       </c>
     </row>
     <row r="41">
@@ -4527,11 +4527,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.001486162317343822</v>
+        <v>0.001427125570284084</v>
       </c>
     </row>
     <row r="42">
@@ -4540,11 +4540,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.001424224768173518</v>
+        <v>0.001415015655483802</v>
       </c>
     </row>
     <row r="43">
@@ -4553,11 +4553,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.00141860717341115</v>
+        <v>0.001414835809914732</v>
       </c>
     </row>
     <row r="44">
@@ -4566,11 +4566,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.001381383685993206</v>
+        <v>0.001406914216697856</v>
       </c>
     </row>
     <row r="45">
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.001352934041462639</v>
+        <v>0.001399417616068388</v>
       </c>
     </row>
     <row r="46">
@@ -4592,11 +4592,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.001166344695713981</v>
+        <v>0.001226467172121567</v>
       </c>
     </row>
     <row r="47">
@@ -4605,11 +4605,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.001147542919868919</v>
+        <v>0.001200527758229824</v>
       </c>
     </row>
     <row r="48">
@@ -4618,11 +4618,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.001145237844529358</v>
+        <v>0.001186039531280904</v>
       </c>
     </row>
     <row r="49">
@@ -4631,11 +4631,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.001129882934385539</v>
+        <v>0.001148045527509397</v>
       </c>
     </row>
     <row r="50">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.00112987366556819</v>
+        <v>0.001085018578042294</v>
       </c>
     </row>
     <row r="51">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.0005593842487669528</v>
+        <v>0.0004907007807858693</v>
       </c>
     </row>
     <row r="52">
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.0003852495780667005</v>
+        <v>0.0003530842890096436</v>
       </c>
     </row>
     <row r="53">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.0003466637184265833</v>
+        <v>0.0002858886754939298</v>
       </c>
     </row>
     <row r="54">
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>9.828944389033009e-05</v>
+        <v>9.7443621415004e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4995727851397694</v>
+        <v>0.5060052298913096</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01857695332894564</v>
+        <v>0.01887199810102201</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03187028379250897</v>
+        <v>0.0338395779654817</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008589619572648633</v>
+        <v>0.008895305012611683</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.01109876378887378</v>
+        <v>0.01091706533964594</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008308217314278074</v>
+        <v>0.007702337358314838</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.00805747393289582</v>
+        <v>0.008045855817688996</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005979374089886852</v>
+        <v>0.006414602234832935</v>
       </c>
     </row>
     <row r="6">
@@ -4809,14 +4809,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.006696035472563022</v>
+        <v>0.007697035974072464</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007032935668823118</v>
+        <v>0.00810651645131924</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.006611205109028462</v>
+        <v>0.006303376524204596</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007768903585070768</v>
+        <v>0.007871613096928937</v>
       </c>
     </row>
     <row r="8">
@@ -4841,14 +4841,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.00625049212052472</v>
+        <v>0.005680258449072129</v>
       </c>
       <c r="D8" t="n">
-        <v>0.007272452258322136</v>
+        <v>0.006256462536271941</v>
       </c>
     </row>
     <row r="9">
@@ -4857,14 +4857,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002067810914767354</v>
+        <v>0.00205287097141571</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009010450608744553</v>
+        <v>0.0010155960695085</v>
       </c>
     </row>
     <row r="10">
@@ -4873,14 +4873,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001878851563722894</v>
+        <v>0.001983795074001027</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0009052369613553881</v>
+        <v>0.003207552672988284</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001688412376054249</v>
+        <v>0.001844892000747178</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001357517417666689</v>
+        <v>0.001423253453173156</v>
       </c>
     </row>
     <row r="12">
@@ -4905,14 +4905,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001521671257992752</v>
+        <v>0.001779321916018972</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0006774631949469078</v>
+        <v>0.0008036913823119508</v>
       </c>
     </row>
     <row r="13">
@@ -4921,14 +4921,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.00134922590741986</v>
+        <v>0.001578014665222949</v>
       </c>
       <c r="D13" t="n">
-        <v>0.002737054549409479</v>
+        <v>0.0007915481404603266</v>
       </c>
     </row>
     <row r="14">
@@ -4937,14 +4937,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0008768741801767454</v>
+        <v>0.001001010980186467</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0009069841466530784</v>
+        <v>0.0009487944580273079</v>
       </c>
     </row>
     <row r="15">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0008747056634513028</v>
+        <v>0.0009240955433844622</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0006681675182436563</v>
+        <v>0.0003862988151962236</v>
       </c>
     </row>
     <row r="16">
@@ -4969,14 +4969,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0007631619335715545</v>
+        <v>0.0009197150622953898</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0004384499456352019</v>
+        <v>0.000897657379254809</v>
       </c>
     </row>
     <row r="17">
@@ -4985,14 +4985,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0005977563814497211</v>
+        <v>0.0008432482924328521</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0002513368068618049</v>
+        <v>0.0006481511736487669</v>
       </c>
     </row>
     <row r="18">
@@ -5001,14 +5001,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0005825194984571235</v>
+        <v>0.0007888315273503865</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0009586767377339917</v>
+        <v>0.0004382710824525623</v>
       </c>
     </row>
     <row r="19">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0005616933527610391</v>
+        <v>0.0006447795586071115</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000829353596009071</v>
+        <v>0.0007866134215646046</v>
       </c>
     </row>
     <row r="20">
@@ -5033,14 +5033,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0004460295429333461</v>
+        <v>0.0003960994362950831</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0006782670089298317</v>
+        <v>0.0005777017136408172</v>
       </c>
     </row>
     <row r="21">
@@ -5049,14 +5049,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0004073960740187954</v>
+        <v>0.0003768028270288881</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0005452346466679499</v>
+        <v>0.0007659054584839415</v>
       </c>
     </row>
     <row r="22">
@@ -5065,14 +5065,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0003666531390621785</v>
+        <v>0.0003557141340886805</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0004265232256629062</v>
+        <v>0.0006339294208247931</v>
       </c>
     </row>
     <row r="23">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0003438099849484844</v>
+        <v>0.0003445564674893431</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0005556239020614254</v>
+        <v>0.0004497170012049657</v>
       </c>
     </row>
     <row r="24">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0002408118842709972</v>
+        <v>0.0003175231346934093</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0003201131837060857</v>
+        <v>0.0004633366953445097</v>
       </c>
     </row>
     <row r="25">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0001786858351194631</v>
+        <v>0.0001266286008866579</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0008784799406043609</v>
+        <v>0.0004421366487265933</v>
       </c>
     </row>
     <row r="26">
@@ -5129,14 +5129,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0001645951792163758</v>
+        <v>0.0001024898684281017</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0007333194994945873</v>
+        <v>0.0003451227360610369</v>
       </c>
     </row>
     <row r="27">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0001186463784928926</v>
+        <v>3.235721233372235e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0005899887470113857</v>
+        <v>0.0007478295686550885</v>
       </c>
     </row>
     <row r="28">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8.937264546736712e-05</v>
+        <v>8.437338592059972e-06</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0002750365377112809</v>
+        <v>4.050035965240566e-05</v>
       </c>
     </row>
     <row r="29">
@@ -5177,14 +5177,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7.389424923087695e-05</v>
+        <v>-1.359412867504295e-05</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0005469189574644383</v>
+        <v>9.738304911400796e-06</v>
       </c>
     </row>
     <row r="30">
@@ -5193,14 +5193,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4.52069388739873e-05</v>
+        <v>-7.469104474953082e-05</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0002536904485510328</v>
+        <v>2.374961421896184e-05</v>
       </c>
     </row>
     <row r="31">
@@ -5209,14 +5209,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.42480824476743e-06</v>
+        <v>-0.0001130712297018111</v>
       </c>
       <c r="D31" t="n">
-        <v>2.67730498610776e-05</v>
+        <v>0.0002439198331223938</v>
       </c>
     </row>
     <row r="32">
@@ -5225,14 +5225,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8.260306988083776e-07</v>
+        <v>-0.0001168675218212956</v>
       </c>
       <c r="D32" t="n">
-        <v>1.077779574043899e-05</v>
+        <v>0.0007925235861204217</v>
       </c>
     </row>
     <row r="33">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-4.000226660227924e-06</v>
+        <v>-0.0001176716425592028</v>
       </c>
       <c r="D33" t="n">
-        <v>4.618455757052209e-05</v>
+        <v>0.0004003034082453242</v>
       </c>
     </row>
     <row r="34">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-3.411137786994978e-05</v>
+        <v>-0.0001324463469226989</v>
       </c>
       <c r="D34" t="n">
-        <v>0.001060918824704263</v>
+        <v>0.0006454520225867181</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-5.17778356995513e-05</v>
+        <v>-0.0001846802514274159</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0002903634799220685</v>
+        <v>0.0003716426206432473</v>
       </c>
     </row>
     <row r="36">
@@ -5289,14 +5289,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-0.000150599280333874</v>
+        <v>-0.000234381195863842</v>
       </c>
       <c r="D36" t="n">
-        <v>0.001161691316603162</v>
+        <v>0.000236980132998242</v>
       </c>
     </row>
     <row r="37">
@@ -5305,14 +5305,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-0.0002125872452711342</v>
+        <v>-0.0002662016962840186</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0002232838083595478</v>
+        <v>0.001046252188397907</v>
       </c>
     </row>
     <row r="38">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.0002185553499171378</v>
+        <v>-0.0003226108771942737</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0002748523023249961</v>
+        <v>0.0005679444414766771</v>
       </c>
     </row>
     <row r="39">
@@ -5337,14 +5337,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-0.0002857415488159099</v>
+        <v>-0.0003362640018051977</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00063939773860479</v>
+        <v>0.001038346870652598</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.0003352761374145863</v>
+        <v>-0.0003381286588022614</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00015225827502806</v>
+        <v>0.0001501861388581764</v>
       </c>
     </row>
     <row r="41">
@@ -5369,14 +5369,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.0003430546552071423</v>
+        <v>-0.0003553317883045026</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0002974642290730215</v>
+        <v>0.001327973294740724</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.0005387010116341684</v>
+        <v>-0.0005601240915245054</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0006524947907731651</v>
+        <v>0.0006924028490437499</v>
       </c>
     </row>
     <row r="43">
@@ -5401,14 +5401,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.0006264921433683068</v>
+        <v>-0.0005687217856254589</v>
       </c>
       <c r="D43" t="n">
-        <v>0.001025470680071647</v>
+        <v>0.000368836531241739</v>
       </c>
     </row>
     <row r="44">
@@ -5417,14 +5417,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.0006793108609644549</v>
+        <v>-0.0005821095161208434</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0007272407173725139</v>
+        <v>0.0003091784580536161</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.0007137982229562412</v>
+        <v>-0.000697389370586865</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0003862232186170492</v>
+        <v>0.0005757197257349418</v>
       </c>
     </row>
     <row r="46">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.0007357061907502071</v>
+        <v>-0.0008029358153880173</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0006398468600055023</v>
+        <v>0.0006061992663920004</v>
       </c>
     </row>
     <row r="47">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.0007792542138363778</v>
+        <v>-0.001000268056234965</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00057411940886759</v>
+        <v>0.0007029745038290113</v>
       </c>
     </row>
     <row r="48">
@@ -5481,14 +5481,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.001391353341655666</v>
+        <v>-0.001176210536536926</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0006661100573220528</v>
+        <v>0.001130222240312276</v>
       </c>
     </row>
     <row r="49">
@@ -5497,14 +5497,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.00142048526763473</v>
+        <v>-0.001400142969639295</v>
       </c>
       <c r="D49" t="n">
-        <v>0.001116923499046042</v>
+        <v>0.0007410231991515997</v>
       </c>
     </row>
     <row r="50">
@@ -5513,14 +5513,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.00147404199285428</v>
+        <v>-0.00159413418785822</v>
       </c>
       <c r="D50" t="n">
-        <v>0.002138484806446759</v>
+        <v>0.002652903816507177</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.00164232973952384</v>
+        <v>-0.001754181676085709</v>
       </c>
       <c r="D51" t="n">
-        <v>0.001533643250496913</v>
+        <v>0.001477833540605643</v>
       </c>
     </row>
     <row r="52">
@@ -5545,14 +5545,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.001715218802246488</v>
+        <v>-0.001835082163533341</v>
       </c>
       <c r="D52" t="n">
-        <v>0.002350138801836446</v>
+        <v>0.001875595212132226</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.002235304855133002</v>
+        <v>-0.002288258689627743</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0005336470482927344</v>
+        <v>0.0007930398669021704</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.02194819670442113</v>
+        <v>-0.02065342838184092</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0172356459420017</v>
+        <v>0.01710128647155753</v>
       </c>
     </row>
   </sheetData>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.494570036984816</v>
+        <v>3.217199826770076</v>
       </c>
     </row>
     <row r="3">
@@ -5637,11 +5637,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8278717553569916</v>
+        <v>0.6266812437229703</v>
       </c>
     </row>
     <row r="4">
@@ -5650,11 +5650,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8096637815779482</v>
+        <v>0.570501621941216</v>
       </c>
     </row>
     <row r="5">
@@ -5663,11 +5663,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7206125907865633</v>
+        <v>0.5494760899262703</v>
       </c>
     </row>
     <row r="6">
@@ -5676,11 +5676,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.692930115106654</v>
+        <v>0.4977597455062317</v>
       </c>
     </row>
     <row r="7">
@@ -5689,11 +5689,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6835552164975804</v>
+        <v>0.4483518173824934</v>
       </c>
     </row>
     <row r="8">
@@ -5702,11 +5702,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5379885324465508</v>
+        <v>0.4345403141362918</v>
       </c>
     </row>
     <row r="9">
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.379242517438104</v>
+        <v>0.3646130720404273</v>
       </c>
     </row>
     <row r="10">
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3359020433126672</v>
+        <v>0.3053870398541658</v>
       </c>
     </row>
     <row r="11">
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1435422164601232</v>
+        <v>0.1692192791397593</v>
       </c>
     </row>
     <row r="12">
@@ -5754,11 +5754,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1317323699311772</v>
+        <v>0.1254434905924073</v>
       </c>
     </row>
     <row r="13">
@@ -5767,11 +5767,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1270074286839145</v>
+        <v>0.1048756534983135</v>
       </c>
     </row>
     <row r="14">
@@ -5780,11 +5780,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.1153905285354511</v>
+        <v>0.1025833414056709</v>
       </c>
     </row>
     <row r="15">
@@ -5793,11 +5793,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.1053126868845498</v>
+        <v>0.1019034609444729</v>
       </c>
     </row>
     <row r="16">
@@ -5806,11 +5806,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.1005354258648734</v>
+        <v>0.09940350944057874</v>
       </c>
     </row>
     <row r="17">
@@ -5819,11 +5819,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.09638604513066973</v>
+        <v>0.09512582013044524</v>
       </c>
     </row>
     <row r="18">
@@ -5832,11 +5832,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.09626847402319516</v>
+        <v>0.093166113702428</v>
       </c>
     </row>
     <row r="19">
@@ -5845,11 +5845,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.09325412685993539</v>
+        <v>0.09174321924453599</v>
       </c>
     </row>
     <row r="20">
@@ -5858,11 +5858,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.09116504893459432</v>
+        <v>0.09083086368305082</v>
       </c>
     </row>
     <row r="21">
@@ -5871,11 +5871,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.08626015139544796</v>
+        <v>0.0905561334862468</v>
       </c>
     </row>
     <row r="22">
@@ -5884,11 +5884,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0851360275683648</v>
+        <v>0.08716430811798048</v>
       </c>
     </row>
     <row r="23">
@@ -5897,11 +5897,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0847919741349199</v>
+        <v>0.08689986240107084</v>
       </c>
     </row>
     <row r="24">
@@ -5910,11 +5910,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.08428896967463562</v>
+        <v>0.08685309691882903</v>
       </c>
     </row>
     <row r="25">
@@ -5923,11 +5923,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.07919767859878446</v>
+        <v>0.08363311392339945</v>
       </c>
     </row>
     <row r="26">
@@ -5936,11 +5936,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.07631384256049234</v>
+        <v>0.07556918317667227</v>
       </c>
     </row>
     <row r="27">
@@ -5949,11 +5949,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.07578163492785395</v>
+        <v>0.07160750944347871</v>
       </c>
     </row>
     <row r="28">
@@ -5962,11 +5962,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.07258453014363386</v>
+        <v>0.06996116746814574</v>
       </c>
     </row>
     <row r="29">
@@ -5975,11 +5975,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.07165645316039404</v>
+        <v>0.06889905503980076</v>
       </c>
     </row>
     <row r="30">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.07016872245278982</v>
+        <v>0.06885634059986057</v>
       </c>
     </row>
     <row r="31">
@@ -6001,11 +6001,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.06857522721585374</v>
+        <v>0.06451952483190393</v>
       </c>
     </row>
     <row r="32">
@@ -6014,11 +6014,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.06851967201496523</v>
+        <v>0.06251763089092144</v>
       </c>
     </row>
     <row r="33">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.06405963718412444</v>
+        <v>0.06237385659098482</v>
       </c>
     </row>
     <row r="34">
@@ -6040,11 +6040,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.06235080822428163</v>
+        <v>0.05798891292858066</v>
       </c>
     </row>
     <row r="35">
@@ -6053,11 +6053,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.06094154532836749</v>
+        <v>0.05645906764891739</v>
       </c>
     </row>
     <row r="36">
@@ -6066,11 +6066,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.06049050796130562</v>
+        <v>0.05563326314330963</v>
       </c>
     </row>
     <row r="37">
@@ -6079,11 +6079,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.05715507498948114</v>
+        <v>0.05509654477754156</v>
       </c>
     </row>
     <row r="38">
@@ -6092,11 +6092,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.05634842949855523</v>
+        <v>0.05214674385507667</v>
       </c>
     </row>
     <row r="39">
@@ -6105,11 +6105,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.05594284296521712</v>
+        <v>0.05172742536939401</v>
       </c>
     </row>
     <row r="40">
@@ -6118,11 +6118,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.05533991156553952</v>
+        <v>0.05161042521237746</v>
       </c>
     </row>
     <row r="41">
@@ -6131,11 +6131,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.05407251610368879</v>
+        <v>0.05086326753294923</v>
       </c>
     </row>
     <row r="42">
@@ -6144,11 +6144,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.04947098822750107</v>
+        <v>0.04887474577110318</v>
       </c>
     </row>
     <row r="43">
@@ -6157,11 +6157,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0479470393911634</v>
+        <v>0.04840436921305802</v>
       </c>
     </row>
     <row r="44">
@@ -6170,11 +6170,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.04417439044620686</v>
+        <v>0.04226815071445378</v>
       </c>
     </row>
     <row r="45">
@@ -6183,11 +6183,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.04168210238512593</v>
+        <v>0.03837673494691041</v>
       </c>
     </row>
     <row r="46">
@@ -6196,11 +6196,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.03999331145754903</v>
+        <v>0.0293026860189376</v>
       </c>
     </row>
     <row r="47">
@@ -6209,11 +6209,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.02715593727123222</v>
+        <v>0.02641531674244479</v>
       </c>
     </row>
     <row r="48">
@@ -6222,11 +6222,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.01820777581569377</v>
+        <v>0.0170518314484025</v>
       </c>
     </row>
     <row r="49">
@@ -6235,11 +6235,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.008267973532043449</v>
+        <v>0.01399424186190457</v>
       </c>
     </row>
     <row r="50">
@@ -6248,11 +6248,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.005673998930172619</v>
+        <v>0.007442339912218543</v>
       </c>
     </row>
     <row r="51">
@@ -6261,11 +6261,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.0008470847830079897</v>
+        <v>0.007422689391729964</v>
       </c>
     </row>
     <row r="52">
@@ -6274,29 +6274,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.004580767337865055</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.001886324116872284</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6334,15 +6334,30 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>training_rows_used</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>permutation_rows_used</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>source_variables_ranked</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>encoded_feature_count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>preprocessing_scope</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>created_at_utc</t>
         </is>
@@ -6358,14 +6373,25 @@
         <v>788</v>
       </c>
       <c r="C2" t="n">
+        <v>591</v>
+      </c>
+      <c r="D2" t="n">
+        <v>197</v>
+      </c>
+      <c r="E2" t="n">
         <v>53</v>
       </c>
-      <c r="D2" t="n">
-        <v>446</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-06-11 05:10:04 UTC</t>
+      <c r="F2" t="n">
+        <v>414</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>fit_on_training_split_only</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-06-14 22:03:17 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_invert.xlsx
+++ b/NN/reports/feature_importance_white_invert.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5060052298913096</v>
+        <v>0.5060052298913537</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -550,7 +550,7 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0338395779654817</v>
+        <v>0.03383957796548179</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01091706533964594</v>
+        <v>0.01091706533964614</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -624,7 +624,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006303376524204596</v>
+        <v>0.00630337652420474</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
@@ -661,7 +661,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007697035974072464</v>
+        <v>0.007697035974072719</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008045855817688996</v>
+        <v>0.008045855817689152</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -735,7 +735,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005680258449072129</v>
+        <v>0.00568025844907224</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -772,7 +772,7 @@
         <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001578014665222949</v>
+        <v>0.001578014665223137</v>
       </c>
       <c r="H9" t="n">
         <v>12</v>
@@ -809,7 +809,7 @@
         <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0001168675218212956</v>
+        <v>-0.000116867521821129</v>
       </c>
       <c r="H10" t="n">
         <v>31</v>
@@ -846,7 +846,7 @@
         <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0002662016962840186</v>
+        <v>-0.0002662016962839186</v>
       </c>
       <c r="H11" t="n">
         <v>36</v>
@@ -883,7 +883,7 @@
         <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0006447795586071115</v>
+        <v>0.000644779558607167</v>
       </c>
       <c r="H12" t="n">
         <v>18</v>
@@ -920,7 +920,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001983795074001027</v>
+        <v>0.001983795074001271</v>
       </c>
       <c r="H13" t="n">
         <v>9</v>
@@ -957,7 +957,7 @@
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.02065342838184092</v>
+        <v>-0.02065342838184088</v>
       </c>
       <c r="H14" t="n">
         <v>53</v>
@@ -994,7 +994,7 @@
         <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.00205287097141571</v>
+        <v>0.002052870971415743</v>
       </c>
       <c r="H15" t="n">
         <v>8</v>
@@ -1068,7 +1068,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0003553317883045026</v>
+        <v>-0.000355331788304325</v>
       </c>
       <c r="H17" t="n">
         <v>40</v>
@@ -1105,7 +1105,7 @@
         <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001001010980186467</v>
+        <v>0.00100101098018659</v>
       </c>
       <c r="H18" t="n">
         <v>13</v>
@@ -1142,7 +1142,7 @@
         <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0001324463469226989</v>
+        <v>-0.0001324463469226211</v>
       </c>
       <c r="H19" t="n">
         <v>33</v>
@@ -1179,7 +1179,7 @@
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001844892000747178</v>
+        <v>0.001844892000747289</v>
       </c>
       <c r="H20" t="n">
         <v>10</v>
@@ -1216,7 +1216,7 @@
         <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0005601240915245054</v>
+        <v>-0.0005601240915243166</v>
       </c>
       <c r="H21" t="n">
         <v>41</v>
@@ -1253,7 +1253,7 @@
         <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.002288258689627743</v>
+        <v>-0.002288258689627687</v>
       </c>
       <c r="H22" t="n">
         <v>52</v>
@@ -1290,7 +1290,7 @@
         <v>32</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0008432482924328521</v>
+        <v>0.0008432482924329964</v>
       </c>
       <c r="H23" t="n">
         <v>16</v>
@@ -1327,7 +1327,7 @@
         <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.001176210536536926</v>
+        <v>-0.001176210536536837</v>
       </c>
       <c r="H24" t="n">
         <v>47</v>
@@ -1364,7 +1364,7 @@
         <v>24</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001266286008866579</v>
+        <v>0.0001266286008868023</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>25</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.00159413418785822</v>
+        <v>-0.001594134187858076</v>
       </c>
       <c r="H26" t="n">
         <v>49</v>
@@ -1438,7 +1438,7 @@
         <v>30</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0001176716425592028</v>
+        <v>-0.0001176716425591029</v>
       </c>
       <c r="H27" t="n">
         <v>32</v>
@@ -1475,7 +1475,7 @@
         <v>31</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0003362640018051977</v>
+        <v>-0.0003362640018050534</v>
       </c>
       <c r="H28" t="n">
         <v>38</v>
@@ -1512,7 +1512,7 @@
         <v>33</v>
       </c>
       <c r="G29" t="n">
-        <v>3.235721233372235e-05</v>
+        <v>3.235721233383337e-05</v>
       </c>
       <c r="H29" t="n">
         <v>26</v>
@@ -1549,7 +1549,7 @@
         <v>34</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0003768028270288881</v>
+        <v>0.0003768028270291435</v>
       </c>
       <c r="H30" t="n">
         <v>20</v>
@@ -1586,7 +1586,7 @@
         <v>23</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.001000268056234965</v>
+        <v>-0.001000268056234821</v>
       </c>
       <c r="H31" t="n">
         <v>46</v>
@@ -1623,7 +1623,7 @@
         <v>43</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0001024898684281017</v>
+        <v>0.0001024898684282127</v>
       </c>
       <c r="H32" t="n">
         <v>25</v>
@@ -1660,7 +1660,7 @@
         <v>26</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0009197150622953898</v>
+        <v>0.000919715062295523</v>
       </c>
       <c r="H33" t="n">
         <v>15</v>
@@ -1697,7 +1697,7 @@
         <v>38</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0007888315273503865</v>
+        <v>0.0007888315273505309</v>
       </c>
       <c r="H34" t="n">
         <v>17</v>
@@ -1734,7 +1734,7 @@
         <v>35</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0003960994362950831</v>
+        <v>0.0003960994362952164</v>
       </c>
       <c r="H35" t="n">
         <v>19</v>
@@ -1771,7 +1771,7 @@
         <v>49</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0009240955433844622</v>
+        <v>0.0009240955433845843</v>
       </c>
       <c r="H36" t="n">
         <v>14</v>
@@ -1808,7 +1808,7 @@
         <v>29</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.001754181676085709</v>
+        <v>-0.001754181676085642</v>
       </c>
       <c r="H37" t="n">
         <v>50</v>
@@ -1845,7 +1845,7 @@
         <v>39</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0003175231346934093</v>
+        <v>0.0003175231346934648</v>
       </c>
       <c r="H38" t="n">
         <v>23</v>
@@ -1882,7 +1882,7 @@
         <v>40</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0005821095161208434</v>
+        <v>-0.0005821095161207101</v>
       </c>
       <c r="H39" t="n">
         <v>43</v>
@@ -1919,7 +1919,7 @@
         <v>17</v>
       </c>
       <c r="G40" t="n">
-        <v>-7.469104474953082e-05</v>
+        <v>-7.469104474945309e-05</v>
       </c>
       <c r="H40" t="n">
         <v>29</v>
@@ -1956,7 +1956,7 @@
         <v>45</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0003226108771942737</v>
+        <v>-0.000322610877194085</v>
       </c>
       <c r="H41" t="n">
         <v>37</v>
@@ -1993,7 +1993,7 @@
         <v>48</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0003445564674893431</v>
+        <v>0.0003445564674894541</v>
       </c>
       <c r="H42" t="n">
         <v>22</v>
@@ -2030,7 +2030,7 @@
         <v>42</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0003557141340886805</v>
+        <v>0.0003557141340888026</v>
       </c>
       <c r="H43" t="n">
         <v>21</v>
@@ -2067,7 +2067,7 @@
         <v>28</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.001835082163533341</v>
+        <v>-0.001835082163533219</v>
       </c>
       <c r="H44" t="n">
         <v>51</v>
@@ -2104,7 +2104,7 @@
         <v>37</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.000697389370586865</v>
+        <v>-0.0006973893705868095</v>
       </c>
       <c r="H45" t="n">
         <v>44</v>
@@ -2141,7 +2141,7 @@
         <v>36</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.0008029358153880173</v>
+        <v>-0.0008029358153878397</v>
       </c>
       <c r="H46" t="n">
         <v>45</v>
@@ -2178,7 +2178,7 @@
         <v>46</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.001400142969639295</v>
+        <v>-0.001400142969639095</v>
       </c>
       <c r="H47" t="n">
         <v>48</v>
@@ -2215,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.0001130712297018111</v>
+        <v>-0.0001130712297016445</v>
       </c>
       <c r="H48" t="n">
         <v>30</v>
@@ -2252,7 +2252,7 @@
         <v>44</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.0001846802514274159</v>
+        <v>-0.0001846802514273493</v>
       </c>
       <c r="H49" t="n">
         <v>34</v>
@@ -2289,7 +2289,7 @@
         <v>53</v>
       </c>
       <c r="G50" t="n">
-        <v>-1.359412867504295e-05</v>
+        <v>-1.359412867494303e-05</v>
       </c>
       <c r="H50" t="n">
         <v>28</v>
@@ -2326,7 +2326,7 @@
         <v>47</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.0005687217856254589</v>
+        <v>-0.0005687217856254368</v>
       </c>
       <c r="H51" t="n">
         <v>42</v>
@@ -2363,7 +2363,7 @@
         <v>52</v>
       </c>
       <c r="G52" t="n">
-        <v>8.437338592059972e-06</v>
+        <v>8.437338592170995e-06</v>
       </c>
       <c r="H52" t="n">
         <v>27</v>
@@ -2400,7 +2400,7 @@
         <v>51</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.000234381195863842</v>
+        <v>-0.0002343811958638198</v>
       </c>
       <c r="H53" t="n">
         <v>35</v>
@@ -2437,7 +2437,7 @@
         <v>50</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.0003381286588022614</v>
+        <v>-0.0003381286588021282</v>
       </c>
       <c r="H54" t="n">
         <v>39</v>
@@ -2545,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5060052298913096</v>
+        <v>0.5060052298913537</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -2582,7 +2582,7 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0338395779654817</v>
+        <v>0.03383957796548179</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2619,7 +2619,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01091706533964594</v>
+        <v>0.01091706533964614</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -2656,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006303376524204596</v>
+        <v>0.00630337652420474</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
@@ -2693,7 +2693,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007697035974072464</v>
+        <v>0.007697035974072719</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008045855817688996</v>
+        <v>0.008045855817689152</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -2767,7 +2767,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005680258449072129</v>
+        <v>0.00568025844907224</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -2804,7 +2804,7 @@
         <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001578014665222949</v>
+        <v>0.001578014665223137</v>
       </c>
       <c r="H9" t="n">
         <v>12</v>
@@ -2841,7 +2841,7 @@
         <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0001168675218212956</v>
+        <v>-0.000116867521821129</v>
       </c>
       <c r="H10" t="n">
         <v>31</v>
@@ -2878,7 +2878,7 @@
         <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0002662016962840186</v>
+        <v>-0.0002662016962839186</v>
       </c>
       <c r="H11" t="n">
         <v>36</v>
@@ -2915,7 +2915,7 @@
         <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0006447795586071115</v>
+        <v>0.000644779558607167</v>
       </c>
       <c r="H12" t="n">
         <v>18</v>
@@ -2952,7 +2952,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001983795074001027</v>
+        <v>0.001983795074001271</v>
       </c>
       <c r="H13" t="n">
         <v>9</v>
@@ -2989,7 +2989,7 @@
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.02065342838184092</v>
+        <v>-0.02065342838184088</v>
       </c>
       <c r="H14" t="n">
         <v>53</v>
@@ -3026,7 +3026,7 @@
         <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.00205287097141571</v>
+        <v>0.002052870971415743</v>
       </c>
       <c r="H15" t="n">
         <v>8</v>
@@ -3100,7 +3100,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0003553317883045026</v>
+        <v>-0.000355331788304325</v>
       </c>
       <c r="H17" t="n">
         <v>40</v>
@@ -3137,7 +3137,7 @@
         <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001001010980186467</v>
+        <v>0.00100101098018659</v>
       </c>
       <c r="H18" t="n">
         <v>13</v>
@@ -3174,7 +3174,7 @@
         <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0001324463469226989</v>
+        <v>-0.0001324463469226211</v>
       </c>
       <c r="H19" t="n">
         <v>33</v>
@@ -3211,7 +3211,7 @@
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001844892000747178</v>
+        <v>0.001844892000747289</v>
       </c>
       <c r="H20" t="n">
         <v>10</v>
@@ -3248,7 +3248,7 @@
         <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0005601240915245054</v>
+        <v>-0.0005601240915243166</v>
       </c>
       <c r="H21" t="n">
         <v>41</v>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5060052298913096</v>
+        <v>0.5060052298913537</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01887199810102201</v>
+        <v>0.01887199810102249</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0338395779654817</v>
+        <v>0.03383957796548179</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008895305012611683</v>
+        <v>0.008895305012611664</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.01091706533964594</v>
+        <v>0.01091706533964614</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007702337358314838</v>
+        <v>0.007702337358314788</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.008045855817688996</v>
+        <v>0.008045855817689152</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006414602234832935</v>
+        <v>0.006414602234832921</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.007697035974072464</v>
+        <v>0.007697035974072719</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00810651645131924</v>
+        <v>0.00810651645131932</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.006303376524204596</v>
+        <v>0.00630337652420474</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007871613096928937</v>
+        <v>0.007871613096928918</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.005680258449072129</v>
+        <v>0.00568025844907224</v>
       </c>
       <c r="D8" t="n">
-        <v>0.006256462536271941</v>
+        <v>0.006256462536271989</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.00205287097141571</v>
+        <v>0.002052870971415743</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0010155960695085</v>
+        <v>0.001015596069508513</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001983795074001027</v>
+        <v>0.001983795074001271</v>
       </c>
       <c r="D10" t="n">
-        <v>0.003207552672988284</v>
+        <v>0.0032075526729883</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001844892000747178</v>
+        <v>0.001844892000747289</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001423253453173156</v>
+        <v>0.001423253453173209</v>
       </c>
     </row>
     <row r="12">
@@ -4912,7 +4912,7 @@
         <v>0.001779321916018972</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0008036913823119508</v>
+        <v>0.0008036913823119692</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001578014665222949</v>
+        <v>0.001578014665223137</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0007915481404603266</v>
+        <v>0.0007915481404603431</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001001010980186467</v>
+        <v>0.00100101098018659</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0009487944580273079</v>
+        <v>0.0009487944580273456</v>
       </c>
     </row>
     <row r="15">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0009240955433844622</v>
+        <v>0.0009240955433845843</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0003862988151962236</v>
+        <v>0.0003862988151961709</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0009197150622953898</v>
+        <v>0.000919715062295523</v>
       </c>
       <c r="D16" t="n">
-        <v>0.000897657379254809</v>
+        <v>0.0008976573792548613</v>
       </c>
     </row>
     <row r="17">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0008432482924328521</v>
+        <v>0.0008432482924329964</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0006481511736487669</v>
+        <v>0.0006481511736487772</v>
       </c>
     </row>
     <row r="18">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0007888315273503865</v>
+        <v>0.0007888315273505309</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004382710824525623</v>
+        <v>0.0004382710824525421</v>
       </c>
     </row>
     <row r="19">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0006447795586071115</v>
+        <v>0.000644779558607167</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0007866134215646046</v>
+        <v>0.0007866134215645804</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0003960994362950831</v>
+        <v>0.0003960994362952164</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0005777017136408172</v>
+        <v>0.000577701713640764</v>
       </c>
     </row>
     <row r="21">
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0003768028270288881</v>
+        <v>0.0003768028270291435</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0007659054584839415</v>
+        <v>0.0007659054584839693</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0003557141340886805</v>
+        <v>0.0003557141340888026</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0006339294208247931</v>
+        <v>0.0006339294208247717</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0003445564674893431</v>
+        <v>0.0003445564674894541</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0004497170012049657</v>
+        <v>0.0004497170012050446</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0003175231346934093</v>
+        <v>0.0003175231346934648</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0004633366953445097</v>
+        <v>0.0004633366953444537</v>
       </c>
     </row>
     <row r="25">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0001266286008866579</v>
+        <v>0.0001266286008868023</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0004421366487265933</v>
+        <v>0.0004421366487265692</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0001024898684281017</v>
+        <v>0.0001024898684282127</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0003451227360610369</v>
+        <v>0.0003451227360610102</v>
       </c>
     </row>
     <row r="27">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3.235721233372235e-05</v>
+        <v>3.235721233383337e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0007478295686550885</v>
+        <v>0.0007478295686550927</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8.437338592059972e-06</v>
+        <v>8.437338592170995e-06</v>
       </c>
       <c r="D28" t="n">
-        <v>4.050035965240566e-05</v>
+        <v>4.05003596524061e-05</v>
       </c>
     </row>
     <row r="29">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-1.359412867504295e-05</v>
+        <v>-1.359412867494303e-05</v>
       </c>
       <c r="D29" t="n">
-        <v>9.738304911400796e-06</v>
+        <v>9.738304911571115e-06</v>
       </c>
     </row>
     <row r="30">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-7.469104474953082e-05</v>
+        <v>-7.469104474945309e-05</v>
       </c>
       <c r="D30" t="n">
-        <v>2.374961421896184e-05</v>
+        <v>2.374961421901144e-05</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.0001130712297018111</v>
+        <v>-0.0001130712297016445</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0002439198331223938</v>
+        <v>0.0002439198331223278</v>
       </c>
     </row>
     <row r="32">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.0001168675218212956</v>
+        <v>-0.000116867521821129</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0007925235861204217</v>
+        <v>0.0007925235861203656</v>
       </c>
     </row>
     <row r="33">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.0001176716425592028</v>
+        <v>-0.0001176716425591029</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0004003034082453242</v>
+        <v>0.0004003034082453291</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-0.0001324463469226989</v>
+        <v>-0.0001324463469226211</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0006454520225867181</v>
+        <v>0.0006454520225867166</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.0001846802514274159</v>
+        <v>-0.0001846802514273493</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0003716426206432473</v>
+        <v>0.0003716426206432347</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-0.000234381195863842</v>
+        <v>-0.0002343811958638198</v>
       </c>
       <c r="D36" t="n">
-        <v>0.000236980132998242</v>
+        <v>0.0002369801329982529</v>
       </c>
     </row>
     <row r="37">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-0.0002662016962840186</v>
+        <v>-0.0002662016962839186</v>
       </c>
       <c r="D37" t="n">
-        <v>0.001046252188397907</v>
+        <v>0.001046252188397809</v>
       </c>
     </row>
     <row r="38">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.0003226108771942737</v>
+        <v>-0.000322610877194085</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0005679444414766771</v>
+        <v>0.0005679444414767533</v>
       </c>
     </row>
     <row r="39">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-0.0003362640018051977</v>
+        <v>-0.0003362640018050534</v>
       </c>
       <c r="D39" t="n">
-        <v>0.001038346870652598</v>
+        <v>0.001038346870652626</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.0003381286588022614</v>
+        <v>-0.0003381286588021282</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0001501861388581764</v>
+        <v>0.0001501861388582111</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.0003553317883045026</v>
+        <v>-0.000355331788304325</v>
       </c>
       <c r="D41" t="n">
-        <v>0.001327973294740724</v>
+        <v>0.001327973294740708</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.0005601240915245054</v>
+        <v>-0.0005601240915243166</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0006924028490437499</v>
+        <v>0.0006924028490437183</v>
       </c>
     </row>
     <row r="43">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.0005687217856254589</v>
+        <v>-0.0005687217856254368</v>
       </c>
       <c r="D43" t="n">
-        <v>0.000368836531241739</v>
+        <v>0.0003688365312417473</v>
       </c>
     </row>
     <row r="44">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.0005821095161208434</v>
+        <v>-0.0005821095161207101</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0003091784580536161</v>
+        <v>0.000309178458053625</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.000697389370586865</v>
+        <v>-0.0006973893705868095</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0005757197257349418</v>
+        <v>0.0005757197257350385</v>
       </c>
     </row>
     <row r="46">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.0008029358153880173</v>
+        <v>-0.0008029358153878397</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0006061992663920004</v>
+        <v>0.0006061992663919949</v>
       </c>
     </row>
     <row r="47">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.001000268056234965</v>
+        <v>-0.001000268056234821</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0007029745038290113</v>
+        <v>0.000702974503828963</v>
       </c>
     </row>
     <row r="48">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.001176210536536926</v>
+        <v>-0.001176210536536837</v>
       </c>
       <c r="D48" t="n">
-        <v>0.001130222240312276</v>
+        <v>0.00113022224031234</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.001400142969639295</v>
+        <v>-0.001400142969639095</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0007410231991515997</v>
+        <v>0.0007410231991515731</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.00159413418785822</v>
+        <v>-0.001594134187858076</v>
       </c>
       <c r="D50" t="n">
-        <v>0.002652903816507177</v>
+        <v>0.002652903816507246</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.001754181676085709</v>
+        <v>-0.001754181676085642</v>
       </c>
       <c r="D51" t="n">
-        <v>0.001477833540605643</v>
+        <v>0.001477833540605645</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.001835082163533341</v>
+        <v>-0.001835082163533219</v>
       </c>
       <c r="D52" t="n">
-        <v>0.001875595212132226</v>
+        <v>0.001875595212132234</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.002288258689627743</v>
+        <v>-0.002288258689627687</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0007930398669021704</v>
+        <v>0.0007930398669021883</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.02065342838184092</v>
+        <v>-0.02065342838184088</v>
       </c>
       <c r="D54" t="n">
-        <v>0.01710128647155753</v>
+        <v>0.01710128647155745</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:03:17 UTC</t>
+          <t>2026-06-15 07:32:25 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_invert.xlsx
+++ b/NN/reports/feature_importance_white_invert.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,25 +501,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2397114599236186</v>
+        <v>0.2443335456717661</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7016337763885306</v>
+        <v>0.7148532832912768</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5060052298913537</v>
+        <v>0.4989035165520892</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.217199826770076</v>
+        <v>3.30932801191722</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -534,32 +534,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.07555841023038526</v>
+        <v>0.05554840785146799</v>
       </c>
       <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.03749121217389985</v>
+      </c>
+      <c r="F3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.02545845305899258</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5</v>
-      </c>
       <c r="G3" t="n">
-        <v>0.03383957796548179</v>
+        <v>0.01397738149444664</v>
       </c>
       <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.6133443525541211</v>
+      </c>
+      <c r="J3" t="n">
         <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.570501621941216</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>3.25</v>
@@ -571,35 +571,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04439170737250882</v>
+        <v>0.07736000041727491</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03074073436150961</v>
+        <v>0.02516787566298575</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01091706533964614</v>
+        <v>0.03795103460855278</v>
       </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5633470533289877</v>
+      </c>
+      <c r="J4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.6266812437229703</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="5">
@@ -608,35 +608,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04554023223891198</v>
+        <v>0.05309370659178378</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03078065349082866</v>
+        <v>0.03065744962923901</v>
       </c>
       <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.01405496590223929</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.00630337652420474</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.5494760899262703</v>
+        <v>0.4679373941863858</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -649,28 +649,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04116181535255319</v>
+        <v>0.05036232173781784</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04190947857859352</v>
+        <v>0.0564266033108806</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007697035974072719</v>
+        <v>0.01005752284711602</v>
       </c>
       <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4417430249048664</v>
+      </c>
+      <c r="J6" t="n">
         <v>5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.4483518173824934</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04752706336620215</v>
+        <v>0.05178963060890207</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02002625205703273</v>
+        <v>0.02286047869720887</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008045855817689152</v>
+        <v>0.01054244038022029</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4345403141362918</v>
+        <v>0.4236412742884825</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -719,35 +719,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03319575360829841</v>
+        <v>0.01227189190830135</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02386438557647791</v>
+        <v>0.005199734037982766</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00568025844907224</v>
+        <v>0.001891118951760018</v>
       </c>
       <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3877720983365793</v>
+      </c>
+      <c r="J8" t="n">
         <v>7</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.4977597455062317</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5</v>
-      </c>
       <c r="K8" t="n">
-        <v>6.5</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="9">
@@ -756,35 +756,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01102503516812055</v>
+        <v>0.006376466567860458</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004999106252286981</v>
+        <v>0.02329908607962096</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001578014665223137</v>
+        <v>0.0004704219754355088</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3646130720404273</v>
+        <v>0.2878244382117314</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>11.25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -793,35 +793,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.006245177584653407</v>
+        <v>0.01170591082522039</v>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02242991503526511</v>
+        <v>0.002724036403689031</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.000116867521821129</v>
+        <v>0.0009191789197563916</v>
       </c>
       <c r="H10" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3053870398541658</v>
+        <v>0.07904268812929427</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>19</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.00936647249038355</v>
+        <v>0.002941355807422103</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="E11" t="n">
-        <v>0.003334167945865149</v>
+        <v>0.007202351863120548</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0002662016962839186</v>
+        <v>0.002026978927481926</v>
       </c>
       <c r="H11" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1692192791397593</v>
+        <v>0.1217307240155732</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>19.25</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.01022013666717844</v>
+        <v>0.0201750457943884</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002706838273313216</v>
+        <v>0.003359423066211459</v>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000644779558607167</v>
+        <v>0.002896110449496803</v>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07556918317667227</v>
+        <v>0.01280977170108821</v>
       </c>
       <c r="J12" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="K12" t="n">
-        <v>19.25</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="13">
@@ -904,35 +904,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.01923936412412708</v>
+        <v>0.01057197928479211</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003155865441077805</v>
+        <v>0.003113349978878013</v>
       </c>
       <c r="F13" t="n">
         <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001983795074001271</v>
+        <v>-0.0009536340026055856</v>
       </c>
       <c r="H13" t="n">
+        <v>38</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.175949438741982</v>
+      </c>
+      <c r="J13" t="n">
         <v>9</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.0293026860189376</v>
-      </c>
-      <c r="J13" t="n">
-        <v>45</v>
-      </c>
       <c r="K13" t="n">
-        <v>19.5</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="14">
@@ -941,35 +941,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.1869942634619149</v>
+        <v>0.009863260706949243</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>0.005467398730094412</v>
+        <v>0.00155918849642525</v>
       </c>
       <c r="F14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.001452730860708928</v>
+      </c>
+      <c r="H14" t="n">
         <v>12</v>
       </c>
-      <c r="G14" t="n">
-        <v>-0.02065342838184088</v>
-      </c>
-      <c r="H14" t="n">
-        <v>53</v>
-      </c>
       <c r="I14" t="n">
-        <v>0.1019034609444729</v>
+        <v>0.08951116693305528</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K14" t="n">
-        <v>20.25</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="15">
@@ -978,32 +978,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003003792597306548</v>
+        <v>0.01218713882854919</v>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.008368080722640158</v>
+        <v>0.002596982373369849</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002052870971415743</v>
+        <v>-3.759668213295653e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09174321924453599</v>
+        <v>0.08598618280692882</v>
       </c>
       <c r="J15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K15" t="n">
         <v>20.25</v>
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.00273220366734912</v>
+        <v>0.01057089295506954</v>
       </c>
       <c r="D16" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>0.007442495456984892</v>
+        <v>0.002635442976014092</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001779321916018972</v>
+        <v>0.002187830985377948</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0905561334862468</v>
+        <v>0.02826597200514547</v>
       </c>
       <c r="J16" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K16" t="n">
-        <v>22</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01094492555671265</v>
+        <v>0.008850087657301244</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002595658814339139</v>
+        <v>0.002639303057098715</v>
       </c>
       <c r="F17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0001399817309445828</v>
+      </c>
+      <c r="H17" t="n">
+        <v>23</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.06928567198810898</v>
+      </c>
+      <c r="J17" t="n">
         <v>21</v>
       </c>
-      <c r="G17" t="n">
-        <v>-0.000355331788304325</v>
-      </c>
-      <c r="H17" t="n">
-        <v>40</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.093166113702428</v>
-      </c>
-      <c r="J17" t="n">
-        <v>17</v>
-      </c>
       <c r="K17" t="n">
-        <v>22.75</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.008952661308969673</v>
+        <v>0.00777004168616293</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001415015655483802</v>
+        <v>0.003278403693519699</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>0.00100101098018659</v>
+        <v>-0.0003059325027456649</v>
       </c>
       <c r="H18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08689986240107084</v>
+        <v>0.0974960962474043</v>
       </c>
       <c r="J18" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
-        <v>23.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.008186584491951624</v>
+        <v>0.002877569877194559</v>
       </c>
       <c r="D19" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.00832606962986991</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.001760052614819696</v>
+      </c>
+      <c r="H19" t="n">
+        <v>11</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.0611594562303921</v>
+      </c>
+      <c r="J19" t="n">
+        <v>25</v>
+      </c>
+      <c r="K19" t="n">
         <v>21</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.002722187506063482</v>
-      </c>
-      <c r="F19" t="n">
-        <v>19</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-0.0001324463469226211</v>
-      </c>
-      <c r="H19" t="n">
-        <v>33</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.08716430811798048</v>
-      </c>
-      <c r="J19" t="n">
-        <v>21</v>
-      </c>
-      <c r="K19" t="n">
-        <v>23.5</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.009872146266763672</v>
+        <v>0.009098366627790405</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002538717532790274</v>
+        <v>0.003380599712404232</v>
       </c>
       <c r="F20" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001844892000747289</v>
+        <v>-0.001646701778544213</v>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0170518314484025</v>
+        <v>0.1178906114592553</v>
       </c>
       <c r="J20" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="K20" t="n">
-        <v>23.75</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.006817526391507141</v>
+        <v>0.01556963496303819</v>
       </c>
       <c r="D21" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>0.002806254462714189</v>
+        <v>0.002104076634160863</v>
       </c>
       <c r="F21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.0005945480339803022</v>
+      </c>
+      <c r="H21" t="n">
+        <v>37</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.08671619450310342</v>
+      </c>
+      <c r="J21" t="n">
         <v>18</v>
       </c>
-      <c r="G21" t="n">
-        <v>-0.0005601240915243166</v>
-      </c>
-      <c r="H21" t="n">
-        <v>41</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.1254434905924073</v>
-      </c>
-      <c r="J21" t="n">
-        <v>11</v>
-      </c>
       <c r="K21" t="n">
-        <v>24</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.008543577892239676</v>
+        <v>0.01315554243821884</v>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>0.003057272628888262</v>
+        <v>0.005859417799682523</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.002288258689627687</v>
+        <v>-0.001567533699965473</v>
       </c>
       <c r="H22" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1048756534983135</v>
+        <v>0.05757405598218046</v>
       </c>
       <c r="J22" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K22" t="n">
-        <v>24.75</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.007709983451279802</v>
+        <v>0.00645381617833605</v>
       </c>
       <c r="D23" t="n">
+        <v>30</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.00213283860922717</v>
+      </c>
+      <c r="F23" t="n">
+        <v>21</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.475633114864209e-05</v>
+      </c>
+      <c r="H23" t="n">
+        <v>24</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.08732432990716088</v>
+      </c>
+      <c r="J23" t="n">
+        <v>17</v>
+      </c>
+      <c r="K23" t="n">
         <v>23</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.001800396019521926</v>
-      </c>
-      <c r="F23" t="n">
-        <v>32</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.0008432482924329964</v>
-      </c>
-      <c r="H23" t="n">
-        <v>16</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.06889905503980076</v>
-      </c>
-      <c r="J23" t="n">
-        <v>28</v>
-      </c>
-      <c r="K23" t="n">
-        <v>24.75</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01235405614677315</v>
+        <v>0.008225329691033822</v>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E24" t="n">
-        <v>0.005733252069745269</v>
+        <v>0.001955893398859076</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.001176210536536837</v>
+        <v>0.0003696691256181106</v>
       </c>
       <c r="H24" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="I24" t="n">
-        <v>0.05645906764891739</v>
+        <v>0.06646898364123421</v>
       </c>
       <c r="J24" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="K24" t="n">
-        <v>25.75</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
@@ -1348,35 +1348,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.007102439015698039</v>
+        <v>0.006765314282944909</v>
       </c>
       <c r="D25" t="n">
+        <v>29</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.001990343165510374</v>
+      </c>
+      <c r="F25" t="n">
         <v>25</v>
       </c>
-      <c r="E25" t="n">
-        <v>0.002249283561726051</v>
-      </c>
-      <c r="F25" t="n">
-        <v>24</v>
-      </c>
       <c r="G25" t="n">
-        <v>0.0001266286008868023</v>
+        <v>0.0005103760204162921</v>
       </c>
       <c r="H25" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I25" t="n">
-        <v>0.06451952483190393</v>
+        <v>0.06509654794582742</v>
       </c>
       <c r="J25" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K25" t="n">
-        <v>25.75</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="26">
@@ -1385,35 +1385,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01409531660167823</v>
+        <v>0.00878380530781233</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00223530326313844</v>
+        <v>0.001750898473832609</v>
       </c>
       <c r="F26" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.001594134187858076</v>
+        <v>0.001049348338898826</v>
       </c>
       <c r="H26" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="I26" t="n">
-        <v>0.08685309691882903</v>
+        <v>0.04358031670766582</v>
       </c>
       <c r="J26" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="K26" t="n">
-        <v>26.75</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -1422,35 +1422,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.005575459110547282</v>
+        <v>0.1879466557768895</v>
       </c>
       <c r="D27" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001838011076629077</v>
+        <v>0.00125243382946587</v>
       </c>
       <c r="F27" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0001176716425591029</v>
+        <v>-0.01994800481155735</v>
       </c>
       <c r="H27" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1025833414056709</v>
+        <v>0.09636673418645758</v>
       </c>
       <c r="J27" t="n">
         <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>27.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="28">
@@ -1463,31 +1463,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.008005821997730537</v>
+        <v>0.009549556091472008</v>
       </c>
       <c r="D28" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001818644195808831</v>
+        <v>0.001954139429504102</v>
       </c>
       <c r="F28" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0003362640018050534</v>
+        <v>-0.0001981603957494582</v>
       </c>
       <c r="H28" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I28" t="n">
-        <v>0.06885634059986057</v>
+        <v>0.05817112037781236</v>
       </c>
       <c r="J28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K28" t="n">
-        <v>30</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="29">
@@ -1496,35 +1496,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.005910721975406701</v>
+        <v>0.007081167884871175</v>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00176602312229494</v>
+        <v>0.001745166238192159</v>
       </c>
       <c r="F29" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>3.235721233383337e-05</v>
+        <v>0.0004690914681675706</v>
       </c>
       <c r="H29" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I29" t="n">
-        <v>0.06251763089092144</v>
+        <v>0.04621172202372525</v>
       </c>
       <c r="J29" t="n">
         <v>31</v>
       </c>
       <c r="K29" t="n">
-        <v>30.5</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="30">
@@ -1533,35 +1533,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.006423611938019026</v>
+        <v>0.0002145014102888934</v>
       </c>
       <c r="D30" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001707886595362008</v>
+        <v>0.003012859404853337</v>
       </c>
       <c r="F30" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0003768028270291435</v>
+        <v>2.670205550561189e-05</v>
       </c>
       <c r="H30" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I30" t="n">
-        <v>0.04840436921305802</v>
+        <v>0.06252618266775078</v>
       </c>
       <c r="J30" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="K30" t="n">
-        <v>30.75</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="31">
@@ -1570,35 +1570,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.007352663814316513</v>
+        <v>0.007175666309996734</v>
       </c>
       <c r="D31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E31" t="n">
-        <v>0.002274586281777611</v>
+        <v>0.001683825079637375</v>
       </c>
       <c r="F31" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.001000268056234821</v>
+        <v>0.000968130304840853</v>
       </c>
       <c r="H31" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="I31" t="n">
-        <v>0.05563326314330963</v>
+        <v>0.008165286133118066</v>
       </c>
       <c r="J31" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K31" t="n">
-        <v>32</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="32">
@@ -1607,35 +1607,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.00510644188920121</v>
+        <v>0.006211176129763884</v>
       </c>
       <c r="D32" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001406914216697856</v>
+        <v>0.001546826218155441</v>
       </c>
       <c r="F32" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0001024898684282127</v>
+        <v>0.0005761158334296801</v>
       </c>
       <c r="H32" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>0.08363311392339945</v>
+        <v>0.04349393965321102</v>
       </c>
       <c r="J32" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K32" t="n">
-        <v>32.5</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="33">
@@ -1644,35 +1644,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.00354871592234068</v>
+        <v>0.007062819465296365</v>
       </c>
       <c r="D33" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002118530515049348</v>
+        <v>0.001821322318337347</v>
       </c>
       <c r="F33" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G33" t="n">
-        <v>0.000919715062295523</v>
+        <v>3.065640373776102e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.02641531674244479</v>
+        <v>0.03891875623741914</v>
       </c>
       <c r="J33" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K33" t="n">
-        <v>32.5</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="34">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.006301249394623563</v>
+        <v>0.009027049676944988</v>
       </c>
       <c r="D34" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001524426275126526</v>
+        <v>0.0020654433649505</v>
       </c>
       <c r="F34" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0007888315273505309</v>
+        <v>-0.001431881710101368</v>
       </c>
       <c r="H34" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="I34" t="n">
-        <v>0.01399424186190457</v>
+        <v>0.04221691003306827</v>
       </c>
       <c r="J34" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="K34" t="n">
-        <v>32.75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35">
@@ -1718,35 +1718,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.005663959699826464</v>
+        <v>0.01120912990006109</v>
       </c>
       <c r="D35" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E35" t="n">
-        <v>0.001527646230426919</v>
+        <v>0.002092613348455604</v>
       </c>
       <c r="F35" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0003960994362952164</v>
+        <v>-0.001282062987169463</v>
       </c>
       <c r="H35" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03837673494691041</v>
+        <v>0.00267286399738742</v>
       </c>
       <c r="J35" t="n">
         <v>44</v>
       </c>
       <c r="K35" t="n">
-        <v>32.75</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="36">
@@ -1755,35 +1755,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.003486287167757974</v>
+        <v>0.006956865323940975</v>
       </c>
       <c r="D36" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001085018578042294</v>
+        <v>0.001610008419256461</v>
       </c>
       <c r="F36" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0009240955433845843</v>
+        <v>-0.0003889017021755592</v>
       </c>
       <c r="H36" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="I36" t="n">
-        <v>0.07160750944347871</v>
+        <v>0.0610933553138997</v>
       </c>
       <c r="J36" t="n">
         <v>26</v>
       </c>
       <c r="K36" t="n">
-        <v>33.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="37">
@@ -1792,35 +1792,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.008282611440005038</v>
+        <v>0.0042090334248013</v>
       </c>
       <c r="D37" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E37" t="n">
-        <v>0.001839160971955053</v>
+        <v>0.001269577453504093</v>
       </c>
       <c r="F37" t="n">
+        <v>36</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.0001710574240983198</v>
+      </c>
+      <c r="H37" t="n">
+        <v>22</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.05687193118223988</v>
+      </c>
+      <c r="J37" t="n">
         <v>29</v>
       </c>
-      <c r="G37" t="n">
-        <v>-0.001754181676085642</v>
-      </c>
-      <c r="H37" t="n">
-        <v>50</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.05509654477754156</v>
-      </c>
-      <c r="J37" t="n">
-        <v>36</v>
-      </c>
       <c r="K37" t="n">
-        <v>33.75</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
@@ -1829,35 +1829,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.006066651165962322</v>
+        <v>0.005892114291373612</v>
       </c>
       <c r="D38" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E38" t="n">
-        <v>0.001498815679236424</v>
+        <v>0.001268457938418235</v>
       </c>
       <c r="F38" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0003175231346934648</v>
+        <v>-0.001108651769762337</v>
       </c>
       <c r="H38" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I38" t="n">
-        <v>0.04226815071445378</v>
+        <v>0.09295511854923344</v>
       </c>
       <c r="J38" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="K38" t="n">
-        <v>34</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="39">
@@ -1866,35 +1866,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.005166038317832973</v>
+        <v>0.005450512232233132</v>
       </c>
       <c r="D39" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E39" t="n">
-        <v>0.001427125570284084</v>
+        <v>0.001223697016620204</v>
       </c>
       <c r="F39" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0005821095161207101</v>
+        <v>-0.001043504817726881</v>
       </c>
       <c r="H39" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I39" t="n">
-        <v>0.09512582013044524</v>
+        <v>0.09455010903131766</v>
       </c>
       <c r="J39" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K39" t="n">
-        <v>34</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="40">
@@ -1903,35 +1903,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0002476139724240329</v>
+        <v>0.003814288985877651</v>
       </c>
       <c r="D40" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E40" t="n">
-        <v>0.00303423736790386</v>
+        <v>0.001144427589984408</v>
       </c>
       <c r="F40" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G40" t="n">
-        <v>-7.469104474945309e-05</v>
+        <v>0.0004800275824715427</v>
       </c>
       <c r="H40" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I40" t="n">
-        <v>0.05172742536939401</v>
+        <v>0.05200628049966616</v>
       </c>
       <c r="J40" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K40" t="n">
-        <v>34</v>
+        <v>31.75</v>
       </c>
     </row>
     <row r="41">
@@ -1940,32 +1940,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.004867321492435589</v>
+        <v>0.004521030721642496</v>
       </c>
       <c r="D41" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E41" t="n">
-        <v>0.001226467172121567</v>
+        <v>0.001332959620662572</v>
       </c>
       <c r="F41" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.000322610877194085</v>
+        <v>-1.197908755594668e-05</v>
       </c>
       <c r="H41" t="n">
+        <v>29</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.03194442705109424</v>
+      </c>
+      <c r="J41" t="n">
         <v>37</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.09940350944057874</v>
-      </c>
-      <c r="J41" t="n">
-        <v>15</v>
       </c>
       <c r="K41" t="n">
         <v>34.25</v>
@@ -1977,35 +1977,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.00353229525521392</v>
+        <v>0.004783196219423467</v>
       </c>
       <c r="D42" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E42" t="n">
-        <v>0.001148045527509397</v>
+        <v>0.001198301931399005</v>
       </c>
       <c r="F42" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0003445564674894541</v>
+        <v>-6.699779075663992e-05</v>
       </c>
       <c r="H42" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I42" t="n">
-        <v>0.06996116746814574</v>
+        <v>0.02062727123276442</v>
       </c>
       <c r="J42" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="K42" t="n">
-        <v>35.25</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="43">
@@ -2014,35 +2014,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.005066300372071085</v>
+        <v>0.0004870656553349718</v>
       </c>
       <c r="D43" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E43" t="n">
-        <v>0.001414835809914732</v>
+        <v>0.000375897527010226</v>
       </c>
       <c r="F43" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0003557141340888026</v>
+        <v>2.178003377117932e-05</v>
       </c>
       <c r="H43" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05161042521237746</v>
+        <v>0.02619112774519694</v>
       </c>
       <c r="J43" t="n">
         <v>39</v>
       </c>
       <c r="K43" t="n">
-        <v>35.25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44">
@@ -2051,35 +2051,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.01009547244346568</v>
+        <v>0.0009830689947895612</v>
       </c>
       <c r="D44" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E44" t="n">
-        <v>0.001863924872907539</v>
+        <v>0.000283402283740292</v>
       </c>
       <c r="F44" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.001835082163533219</v>
+        <v>-0.0001084295481577846</v>
       </c>
       <c r="H44" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="I44" t="n">
-        <v>0.004580767337865055</v>
+        <v>0.03709267834490237</v>
       </c>
       <c r="J44" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="K44" t="n">
-        <v>36.25</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="45">
@@ -2088,35 +2088,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.005592008449403107</v>
+        <v>0.0001443942479262907</v>
       </c>
       <c r="D45" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E45" t="n">
-        <v>0.001526035484687893</v>
+        <v>9.101875924567753e-05</v>
       </c>
       <c r="F45" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.0006973893705868095</v>
+        <v>2.261269987002823e-06</v>
       </c>
       <c r="H45" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I45" t="n">
-        <v>0.06237385659098482</v>
+        <v>0.01042125524955018</v>
       </c>
       <c r="J45" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="K45" t="n">
-        <v>36.75</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46">
@@ -2125,331 +2125,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.006159608075331081</v>
+        <v>0.0005796429896732087</v>
       </c>
       <c r="D46" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E46" t="n">
-        <v>0.001527400343618118</v>
+        <v>0.0004632800136390914</v>
       </c>
       <c r="F46" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.0008029358153878397</v>
+        <v>-0.0003667063536589743</v>
       </c>
       <c r="H46" t="n">
+        <v>35</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
         <v>45</v>
       </c>
-      <c r="I46" t="n">
-        <v>0.05214674385507667</v>
-      </c>
-      <c r="J46" t="n">
-        <v>37</v>
-      </c>
       <c r="K46" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>wastewater_r1_q</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.005176066401549557</v>
-      </c>
-      <c r="D47" t="n">
-        <v>36</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.001200527758229824</v>
-      </c>
-      <c r="F47" t="n">
-        <v>46</v>
-      </c>
-      <c r="G47" t="n">
-        <v>-0.001400142969639095</v>
-      </c>
-      <c r="H47" t="n">
-        <v>48</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.09083086368305082</v>
-      </c>
-      <c r="J47" t="n">
-        <v>19</v>
-      </c>
-      <c r="K47" t="n">
-        <v>37.25</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.001637804208301506</v>
-      </c>
-      <c r="D48" t="n">
-        <v>48</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.001942218956458511</v>
-      </c>
-      <c r="F48" t="n">
-        <v>27</v>
-      </c>
-      <c r="G48" t="n">
-        <v>-0.0001130712297016445</v>
-      </c>
-      <c r="H48" t="n">
-        <v>30</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>53</v>
-      </c>
-      <c r="K48" t="n">
-        <v>39.5</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>wastewater_r2_q</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.004171436267001193</v>
-      </c>
-      <c r="D49" t="n">
-        <v>42</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.001399417616068388</v>
-      </c>
-      <c r="F49" t="n">
-        <v>44</v>
-      </c>
-      <c r="G49" t="n">
-        <v>-0.0001846802514273493</v>
-      </c>
-      <c r="H49" t="n">
-        <v>34</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.05086326753294923</v>
-      </c>
-      <c r="J49" t="n">
-        <v>40</v>
-      </c>
-      <c r="K49" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.0001276585670788098</v>
-      </c>
-      <c r="D50" t="n">
-        <v>53</v>
-      </c>
-      <c r="E50" t="n">
-        <v>9.7443621415004e-05</v>
-      </c>
-      <c r="F50" t="n">
-        <v>53</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-1.359412867494303e-05</v>
-      </c>
-      <c r="H50" t="n">
-        <v>28</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.05798891292858066</v>
-      </c>
-      <c r="J50" t="n">
-        <v>33</v>
-      </c>
-      <c r="K50" t="n">
-        <v>41.75</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>boiling_r2_q</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.00420572754496519</v>
-      </c>
-      <c r="D51" t="n">
         <v>41</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.001186039531280904</v>
-      </c>
-      <c r="F51" t="n">
-        <v>47</v>
-      </c>
-      <c r="G51" t="n">
-        <v>-0.0005687217856254368</v>
-      </c>
-      <c r="H51" t="n">
-        <v>42</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.04887474577110318</v>
-      </c>
-      <c r="J51" t="n">
-        <v>41</v>
-      </c>
-      <c r="K51" t="n">
-        <v>42.75</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.0003523387898693042</v>
-      </c>
-      <c r="D52" t="n">
-        <v>51</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.0002858886754939298</v>
-      </c>
-      <c r="F52" t="n">
-        <v>52</v>
-      </c>
-      <c r="G52" t="n">
-        <v>8.437338592170995e-06</v>
-      </c>
-      <c r="H52" t="n">
-        <v>27</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.001886324116872284</v>
-      </c>
-      <c r="J52" t="n">
-        <v>52</v>
-      </c>
-      <c r="K52" t="n">
-        <v>45.5</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.0009456147320250668</v>
-      </c>
-      <c r="D53" t="n">
-        <v>49</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.0003530842890096436</v>
-      </c>
-      <c r="F53" t="n">
-        <v>51</v>
-      </c>
-      <c r="G53" t="n">
-        <v>-0.0002343811958638198</v>
-      </c>
-      <c r="H53" t="n">
-        <v>35</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.007422689391729964</v>
-      </c>
-      <c r="J53" t="n">
-        <v>50</v>
-      </c>
-      <c r="K53" t="n">
-        <v>46.25</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.0004403946182090141</v>
-      </c>
-      <c r="D54" t="n">
-        <v>50</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.0004907007807858693</v>
-      </c>
-      <c r="F54" t="n">
-        <v>50</v>
-      </c>
-      <c r="G54" t="n">
-        <v>-0.0003381286588021282</v>
-      </c>
-      <c r="H54" t="n">
-        <v>39</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.007442339912218543</v>
-      </c>
-      <c r="J54" t="n">
-        <v>49</v>
-      </c>
-      <c r="K54" t="n">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2533,25 +2237,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2397114599236186</v>
+        <v>0.2443335456717661</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7016337763885306</v>
+        <v>0.7148532832912768</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5060052298913537</v>
+        <v>0.4989035165520892</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.217199826770076</v>
+        <v>3.30932801191722</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -2566,32 +2270,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.07555841023038526</v>
+        <v>0.05554840785146799</v>
       </c>
       <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.03749121217389985</v>
+      </c>
+      <c r="F3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.02545845305899258</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5</v>
-      </c>
       <c r="G3" t="n">
-        <v>0.03383957796548179</v>
+        <v>0.01397738149444664</v>
       </c>
       <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.6133443525541211</v>
+      </c>
+      <c r="J3" t="n">
         <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.570501621941216</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>3.25</v>
@@ -2603,35 +2307,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04439170737250882</v>
+        <v>0.07736000041727491</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03074073436150961</v>
+        <v>0.02516787566298575</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01091706533964614</v>
+        <v>0.03795103460855278</v>
       </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5633470533289877</v>
+      </c>
+      <c r="J4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.6266812437229703</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="5">
@@ -2640,35 +2344,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04554023223891198</v>
+        <v>0.05309370659178378</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03078065349082866</v>
+        <v>0.03065744962923901</v>
       </c>
       <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.01405496590223929</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.00630337652420474</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.5494760899262703</v>
+        <v>0.4679373941863858</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2681,28 +2385,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04116181535255319</v>
+        <v>0.05036232173781784</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04190947857859352</v>
+        <v>0.0564266033108806</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007697035974072719</v>
+        <v>0.01005752284711602</v>
       </c>
       <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4417430249048664</v>
+      </c>
+      <c r="J6" t="n">
         <v>5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.4483518173824934</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
@@ -2718,31 +2422,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04752706336620215</v>
+        <v>0.05178963060890207</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02002625205703273</v>
+        <v>0.02286047869720887</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008045855817689152</v>
+        <v>0.01054244038022029</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4345403141362918</v>
+        <v>0.4236412742884825</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2751,35 +2455,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03319575360829841</v>
+        <v>0.01227189190830135</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02386438557647791</v>
+        <v>0.005199734037982766</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00568025844907224</v>
+        <v>0.001891118951760018</v>
       </c>
       <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3877720983365793</v>
+      </c>
+      <c r="J8" t="n">
         <v>7</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.4977597455062317</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5</v>
-      </c>
       <c r="K8" t="n">
-        <v>6.5</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="9">
@@ -2788,35 +2492,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01102503516812055</v>
+        <v>0.006376466567860458</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004999106252286981</v>
+        <v>0.02329908607962096</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001578014665223137</v>
+        <v>0.0004704219754355088</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3646130720404273</v>
+        <v>0.2878244382117314</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>11.25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -2825,35 +2529,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.006245177584653407</v>
+        <v>0.01170591082522039</v>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02242991503526511</v>
+        <v>0.002724036403689031</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.000116867521821129</v>
+        <v>0.0009191789197563916</v>
       </c>
       <c r="H10" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3053870398541658</v>
+        <v>0.07904268812929427</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>19</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="11">
@@ -2862,35 +2566,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.00936647249038355</v>
+        <v>0.002941355807422103</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="E11" t="n">
-        <v>0.003334167945865149</v>
+        <v>0.007202351863120548</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0002662016962839186</v>
+        <v>0.002026978927481926</v>
       </c>
       <c r="H11" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1692192791397593</v>
+        <v>0.1217307240155732</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>19.25</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="12">
@@ -2899,35 +2603,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.01022013666717844</v>
+        <v>0.0201750457943884</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002706838273313216</v>
+        <v>0.003359423066211459</v>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000644779558607167</v>
+        <v>0.002896110449496803</v>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07556918317667227</v>
+        <v>0.01280977170108821</v>
       </c>
       <c r="J12" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="K12" t="n">
-        <v>19.25</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="13">
@@ -2936,35 +2640,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.01923936412412708</v>
+        <v>0.01057197928479211</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003155865441077805</v>
+        <v>0.003113349978878013</v>
       </c>
       <c r="F13" t="n">
         <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001983795074001271</v>
+        <v>-0.0009536340026055856</v>
       </c>
       <c r="H13" t="n">
+        <v>38</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.175949438741982</v>
+      </c>
+      <c r="J13" t="n">
         <v>9</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.0293026860189376</v>
-      </c>
-      <c r="J13" t="n">
-        <v>45</v>
-      </c>
       <c r="K13" t="n">
-        <v>19.5</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="14">
@@ -2973,35 +2677,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.1869942634619149</v>
+        <v>0.009863260706949243</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>0.005467398730094412</v>
+        <v>0.00155918849642525</v>
       </c>
       <c r="F14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.001452730860708928</v>
+      </c>
+      <c r="H14" t="n">
         <v>12</v>
       </c>
-      <c r="G14" t="n">
-        <v>-0.02065342838184088</v>
-      </c>
-      <c r="H14" t="n">
-        <v>53</v>
-      </c>
       <c r="I14" t="n">
-        <v>0.1019034609444729</v>
+        <v>0.08951116693305528</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K14" t="n">
-        <v>20.25</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="15">
@@ -3010,32 +2714,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003003792597306548</v>
+        <v>0.01218713882854919</v>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.008368080722640158</v>
+        <v>0.002596982373369849</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002052870971415743</v>
+        <v>-3.759668213295653e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09174321924453599</v>
+        <v>0.08598618280692882</v>
       </c>
       <c r="J15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K15" t="n">
         <v>20.25</v>
@@ -3047,35 +2751,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.00273220366734912</v>
+        <v>0.01057089295506954</v>
       </c>
       <c r="D16" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>0.007442495456984892</v>
+        <v>0.002635442976014092</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001779321916018972</v>
+        <v>0.002187830985377948</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0905561334862468</v>
+        <v>0.02826597200514547</v>
       </c>
       <c r="J16" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K16" t="n">
-        <v>22</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="17">
@@ -3084,35 +2788,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01094492555671265</v>
+        <v>0.008850087657301244</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002595658814339139</v>
+        <v>0.002639303057098715</v>
       </c>
       <c r="F17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0001399817309445828</v>
+      </c>
+      <c r="H17" t="n">
+        <v>23</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.06928567198810898</v>
+      </c>
+      <c r="J17" t="n">
         <v>21</v>
       </c>
-      <c r="G17" t="n">
-        <v>-0.000355331788304325</v>
-      </c>
-      <c r="H17" t="n">
-        <v>40</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.093166113702428</v>
-      </c>
-      <c r="J17" t="n">
-        <v>17</v>
-      </c>
       <c r="K17" t="n">
-        <v>22.75</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="18">
@@ -3121,35 +2825,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.008952661308969673</v>
+        <v>0.00777004168616293</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001415015655483802</v>
+        <v>0.003278403693519699</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>0.00100101098018659</v>
+        <v>-0.0003059325027456649</v>
       </c>
       <c r="H18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08689986240107084</v>
+        <v>0.0974960962474043</v>
       </c>
       <c r="J18" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
-        <v>23.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -3158,35 +2862,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.008186584491951624</v>
+        <v>0.002877569877194559</v>
       </c>
       <c r="D19" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.00832606962986991</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.001760052614819696</v>
+      </c>
+      <c r="H19" t="n">
+        <v>11</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.0611594562303921</v>
+      </c>
+      <c r="J19" t="n">
+        <v>25</v>
+      </c>
+      <c r="K19" t="n">
         <v>21</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.002722187506063482</v>
-      </c>
-      <c r="F19" t="n">
-        <v>19</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-0.0001324463469226211</v>
-      </c>
-      <c r="H19" t="n">
-        <v>33</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.08716430811798048</v>
-      </c>
-      <c r="J19" t="n">
-        <v>21</v>
-      </c>
-      <c r="K19" t="n">
-        <v>23.5</v>
       </c>
     </row>
     <row r="20">
@@ -3195,35 +2899,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.009872146266763672</v>
+        <v>0.009098366627790405</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002538717532790274</v>
+        <v>0.003380599712404232</v>
       </c>
       <c r="F20" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001844892000747289</v>
+        <v>-0.001646701778544213</v>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0170518314484025</v>
+        <v>0.1178906114592553</v>
       </c>
       <c r="J20" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="K20" t="n">
-        <v>23.75</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="21">
@@ -3232,35 +2936,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.006817526391507141</v>
+        <v>0.01556963496303819</v>
       </c>
       <c r="D21" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>0.002806254462714189</v>
+        <v>0.002104076634160863</v>
       </c>
       <c r="F21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.0005945480339803022</v>
+      </c>
+      <c r="H21" t="n">
+        <v>37</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.08671619450310342</v>
+      </c>
+      <c r="J21" t="n">
         <v>18</v>
       </c>
-      <c r="G21" t="n">
-        <v>-0.0005601240915243166</v>
-      </c>
-      <c r="H21" t="n">
-        <v>41</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.1254434905924073</v>
-      </c>
-      <c r="J21" t="n">
-        <v>11</v>
-      </c>
       <c r="K21" t="n">
-        <v>24</v>
+        <v>21.5</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +2978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3304,7 +3008,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2397114599236186</v>
+        <v>0.2443335456717661</v>
       </c>
     </row>
     <row r="3">
@@ -3317,7 +3021,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1869942634619149</v>
+        <v>0.1879466557768895</v>
       </c>
     </row>
     <row r="4">
@@ -3330,7 +3034,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07555841023038526</v>
+        <v>0.07736000041727491</v>
       </c>
     </row>
     <row r="5">
@@ -3339,11 +3043,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04752706336620215</v>
+        <v>0.05554840785146799</v>
       </c>
     </row>
     <row r="6">
@@ -3352,11 +3056,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04554023223891198</v>
+        <v>0.05309370659178378</v>
       </c>
     </row>
     <row r="7">
@@ -3365,11 +3069,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04439170737250882</v>
+        <v>0.05178963060890207</v>
       </c>
     </row>
     <row r="8">
@@ -3382,7 +3086,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.04116181535255319</v>
+        <v>0.05036232173781784</v>
       </c>
     </row>
     <row r="9">
@@ -3391,11 +3095,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03319575360829841</v>
+        <v>0.0201750457943884</v>
       </c>
     </row>
     <row r="10">
@@ -3404,11 +3108,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.01923936412412708</v>
+        <v>0.01556963496303819</v>
       </c>
     </row>
     <row r="11">
@@ -3417,11 +3121,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01409531660167823</v>
+        <v>0.01315554243821884</v>
       </c>
     </row>
     <row r="12">
@@ -3430,11 +3134,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.01235405614677315</v>
+        <v>0.01227189190830135</v>
       </c>
     </row>
     <row r="13">
@@ -3443,11 +3147,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.01102503516812055</v>
+        <v>0.01218713882854919</v>
       </c>
     </row>
     <row r="14">
@@ -3456,11 +3160,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.01094492555671265</v>
+        <v>0.01170591082522039</v>
       </c>
     </row>
     <row r="15">
@@ -3469,11 +3173,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.01022013666717844</v>
+        <v>0.01120912990006109</v>
       </c>
     </row>
     <row r="16">
@@ -3482,11 +3186,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01009547244346568</v>
+        <v>0.01057197928479211</v>
       </c>
     </row>
     <row r="17">
@@ -3499,7 +3203,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.009872146266763672</v>
+        <v>0.01057089295506954</v>
       </c>
     </row>
     <row r="18">
@@ -3508,11 +3212,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.00936647249038355</v>
+        <v>0.009863260706949243</v>
       </c>
     </row>
     <row r="19">
@@ -3521,11 +3225,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.008952661308969673</v>
+        <v>0.009549556091472008</v>
       </c>
     </row>
     <row r="20">
@@ -3538,7 +3242,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.008543577892239676</v>
+        <v>0.009098366627790405</v>
       </c>
     </row>
     <row r="21">
@@ -3551,7 +3255,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.008282611440005038</v>
+        <v>0.009027049676944988</v>
       </c>
     </row>
     <row r="22">
@@ -3564,7 +3268,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.008186584491951624</v>
+        <v>0.008850087657301244</v>
       </c>
     </row>
     <row r="23">
@@ -3573,11 +3277,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.008005821997730537</v>
+        <v>0.00878380530781233</v>
       </c>
     </row>
     <row r="24">
@@ -3586,11 +3290,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.007709983451279802</v>
+        <v>0.008225329691033822</v>
       </c>
     </row>
     <row r="25">
@@ -3599,11 +3303,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.007352663814316513</v>
+        <v>0.00777004168616293</v>
       </c>
     </row>
     <row r="26">
@@ -3612,11 +3316,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.007102439015698039</v>
+        <v>0.007175666309996734</v>
       </c>
     </row>
     <row r="27">
@@ -3625,11 +3329,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.006817526391507141</v>
+        <v>0.007081167884871175</v>
       </c>
     </row>
     <row r="28">
@@ -3642,7 +3346,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.006423611938019026</v>
+        <v>0.007062819465296365</v>
       </c>
     </row>
     <row r="29">
@@ -3651,11 +3355,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.006301249394623563</v>
+        <v>0.006956865323940975</v>
       </c>
     </row>
     <row r="30">
@@ -3664,11 +3368,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.006245177584653407</v>
+        <v>0.006765314282944909</v>
       </c>
     </row>
     <row r="31">
@@ -3677,11 +3381,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.006159608075331081</v>
+        <v>0.00645381617833605</v>
       </c>
     </row>
     <row r="32">
@@ -3690,11 +3394,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.006066651165962322</v>
+        <v>0.006376466567860458</v>
       </c>
     </row>
     <row r="33">
@@ -3703,11 +3407,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.005910721975406701</v>
+        <v>0.006211176129763884</v>
       </c>
     </row>
     <row r="34">
@@ -3716,11 +3420,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.005663959699826464</v>
+        <v>0.005892114291373612</v>
       </c>
     </row>
     <row r="35">
@@ -3729,11 +3433,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.005592008449403107</v>
+        <v>0.005450512232233132</v>
       </c>
     </row>
     <row r="36">
@@ -3742,11 +3446,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.005575459110547282</v>
+        <v>0.004783196219423467</v>
       </c>
     </row>
     <row r="37">
@@ -3755,11 +3459,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.005176066401549557</v>
+        <v>0.004521030721642496</v>
       </c>
     </row>
     <row r="38">
@@ -3768,11 +3472,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.005166038317832973</v>
+        <v>0.0042090334248013</v>
       </c>
     </row>
     <row r="39">
@@ -3781,11 +3485,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.00510644188920121</v>
+        <v>0.003814288985877651</v>
       </c>
     </row>
     <row r="40">
@@ -3794,11 +3498,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.005066300372071085</v>
+        <v>0.002941355807422103</v>
       </c>
     </row>
     <row r="41">
@@ -3807,11 +3511,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.004867321492435589</v>
+        <v>0.002877569877194559</v>
       </c>
     </row>
     <row r="42">
@@ -3820,11 +3524,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.00420572754496519</v>
+        <v>0.0009830689947895612</v>
       </c>
     </row>
     <row r="43">
@@ -3833,11 +3537,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.004171436267001193</v>
+        <v>0.0005796429896732087</v>
       </c>
     </row>
     <row r="44">
@@ -3846,11 +3550,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.00354871592234068</v>
+        <v>0.0004870656553349718</v>
       </c>
     </row>
     <row r="45">
@@ -3859,11 +3563,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.00353229525521392</v>
+        <v>0.0002145014102888934</v>
       </c>
     </row>
     <row r="46">
@@ -3872,115 +3576,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.003486287167757974</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>report_year</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.003003792597306548</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>report_date_year</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.00273220366734912</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.001637804208301506</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.0009456147320250668</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0004403946182090141</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.0003523387898693042</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>work_period</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.0002476139724240329</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.0001276585670788098</v>
+        <v>0.0001443942479262907</v>
       </c>
     </row>
   </sheetData>
@@ -3994,7 +3594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4024,7 +3624,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7016337763885306</v>
+        <v>0.7148532832912768</v>
       </c>
     </row>
     <row r="3">
@@ -4037,7 +3637,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04190947857859352</v>
+        <v>0.0564266033108806</v>
       </c>
     </row>
     <row r="4">
@@ -4046,11 +3646,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03078065349082866</v>
+        <v>0.03749121217389985</v>
       </c>
     </row>
     <row r="5">
@@ -4059,11 +3659,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03074073436150961</v>
+        <v>0.03065744962923901</v>
       </c>
     </row>
     <row r="6">
@@ -4076,7 +3676,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02545845305899258</v>
+        <v>0.02516787566298575</v>
       </c>
     </row>
     <row r="7">
@@ -4085,11 +3685,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02386438557647791</v>
+        <v>0.02329908607962096</v>
       </c>
     </row>
     <row r="8">
@@ -4098,11 +3698,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02242991503526511</v>
+        <v>0.02286047869720887</v>
       </c>
     </row>
     <row r="9">
@@ -4111,11 +3711,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02002625205703273</v>
+        <v>0.00832606962986991</v>
       </c>
     </row>
     <row r="10">
@@ -4128,7 +3728,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.008368080722640158</v>
+        <v>0.007202351863120548</v>
       </c>
     </row>
     <row r="11">
@@ -4137,11 +3737,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.007442495456984892</v>
+        <v>0.005859417799682523</v>
       </c>
     </row>
     <row r="12">
@@ -4150,11 +3750,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.005733252069745269</v>
+        <v>0.005199734037982766</v>
       </c>
     </row>
     <row r="13">
@@ -4163,11 +3763,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.005467398730094412</v>
+        <v>0.003380599712404232</v>
       </c>
     </row>
     <row r="14">
@@ -4176,11 +3776,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.004999106252286981</v>
+        <v>0.003359423066211459</v>
       </c>
     </row>
     <row r="15">
@@ -4189,11 +3789,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003334167945865149</v>
+        <v>0.003278403693519699</v>
       </c>
     </row>
     <row r="16">
@@ -4202,11 +3802,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.003155865441077805</v>
+        <v>0.003113349978878013</v>
       </c>
     </row>
     <row r="17">
@@ -4215,11 +3815,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.003057272628888262</v>
+        <v>0.003012859404853337</v>
       </c>
     </row>
     <row r="18">
@@ -4228,11 +3828,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.00303423736790386</v>
+        <v>0.002724036403689031</v>
       </c>
     </row>
     <row r="19">
@@ -4241,11 +3841,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002806254462714189</v>
+        <v>0.002639303057098715</v>
       </c>
     </row>
     <row r="20">
@@ -4254,11 +3854,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002722187506063482</v>
+        <v>0.002635442976014092</v>
       </c>
     </row>
     <row r="21">
@@ -4267,11 +3867,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002706838273313216</v>
+        <v>0.002596982373369849</v>
       </c>
     </row>
     <row r="22">
@@ -4280,11 +3880,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.002595658814339139</v>
+        <v>0.00213283860922717</v>
       </c>
     </row>
     <row r="23">
@@ -4293,11 +3893,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.002538717532790274</v>
+        <v>0.002104076634160863</v>
       </c>
     </row>
     <row r="24">
@@ -4306,11 +3906,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.002274586281777611</v>
+        <v>0.002092613348455604</v>
       </c>
     </row>
     <row r="25">
@@ -4319,11 +3919,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.002249283561726051</v>
+        <v>0.0020654433649505</v>
       </c>
     </row>
     <row r="26">
@@ -4332,11 +3932,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.00223530326313844</v>
+        <v>0.001990343165510374</v>
       </c>
     </row>
     <row r="27">
@@ -4345,11 +3945,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.002118530515049348</v>
+        <v>0.001955893398859076</v>
       </c>
     </row>
     <row r="28">
@@ -4358,11 +3958,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001942218956458511</v>
+        <v>0.001954139429504102</v>
       </c>
     </row>
     <row r="29">
@@ -4371,11 +3971,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.001863924872907539</v>
+        <v>0.001821322318337347</v>
       </c>
     </row>
     <row r="30">
@@ -4384,11 +3984,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.001839160971955053</v>
+        <v>0.001750898473832609</v>
       </c>
     </row>
     <row r="31">
@@ -4397,11 +3997,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.001838011076629077</v>
+        <v>0.001745166238192159</v>
       </c>
     </row>
     <row r="32">
@@ -4410,11 +4010,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001818644195808831</v>
+        <v>0.001683825079637375</v>
       </c>
     </row>
     <row r="33">
@@ -4423,11 +4023,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.001800396019521926</v>
+        <v>0.001610008419256461</v>
       </c>
     </row>
     <row r="34">
@@ -4436,11 +4036,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.00176602312229494</v>
+        <v>0.00155918849642525</v>
       </c>
     </row>
     <row r="35">
@@ -4449,11 +4049,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001707886595362008</v>
+        <v>0.001546826218155441</v>
       </c>
     </row>
     <row r="36">
@@ -4462,11 +4062,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.001527646230426919</v>
+        <v>0.001332959620662572</v>
       </c>
     </row>
     <row r="37">
@@ -4475,11 +4075,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.001527400343618118</v>
+        <v>0.001269577453504093</v>
       </c>
     </row>
     <row r="38">
@@ -4488,11 +4088,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.001526035484687893</v>
+        <v>0.001268457938418235</v>
       </c>
     </row>
     <row r="39">
@@ -4501,11 +4101,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.001524426275126526</v>
+        <v>0.00125243382946587</v>
       </c>
     </row>
     <row r="40">
@@ -4514,11 +4114,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.001498815679236424</v>
+        <v>0.001223697016620204</v>
       </c>
     </row>
     <row r="41">
@@ -4527,11 +4127,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.001427125570284084</v>
+        <v>0.001198301931399005</v>
       </c>
     </row>
     <row r="42">
@@ -4540,11 +4140,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.001415015655483802</v>
+        <v>0.001144427589984408</v>
       </c>
     </row>
     <row r="43">
@@ -4553,11 +4153,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.001414835809914732</v>
+        <v>0.0004632800136390914</v>
       </c>
     </row>
     <row r="44">
@@ -4566,11 +4166,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.001406914216697856</v>
+        <v>0.000375897527010226</v>
       </c>
     </row>
     <row r="45">
@@ -4579,11 +4179,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.001399417616068388</v>
+        <v>0.000283402283740292</v>
       </c>
     </row>
     <row r="46">
@@ -4592,115 +4192,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.001226467172121567</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>wastewater_r1_q</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.001200527758229824</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>boiling_r2_q</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.001186039531280904</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>wastewater_r2_pol</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.001148045527509397</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>boiling_r2_pol</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.001085018578042294</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0004907007807858693</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.0003530842890096436</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.0002858886754939298</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>9.7443621415004e-05</v>
+        <v>9.101875924567753e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4714,7 +4210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4749,10 +4245,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5060052298913537</v>
+        <v>0.4989035165520892</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01887199810102249</v>
+        <v>0.01819150998256065</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4261,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03383957796548179</v>
+        <v>0.03795103460855278</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008895305012611664</v>
+        <v>0.009126663824703301</v>
       </c>
     </row>
     <row r="4">
@@ -4777,14 +4273,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.01091706533964614</v>
+        <v>0.01405496590223929</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007702337358314788</v>
+        <v>0.01011127298399658</v>
       </c>
     </row>
     <row r="5">
@@ -4793,14 +4289,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.008045855817689152</v>
+        <v>0.01397738149444664</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006414602234832921</v>
+        <v>0.01003196773152265</v>
       </c>
     </row>
     <row r="6">
@@ -4809,14 +4305,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.007697035974072719</v>
+        <v>0.01054244038022029</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00810651645131932</v>
+        <v>0.007162386490488457</v>
       </c>
     </row>
     <row r="7">
@@ -4825,14 +4321,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.00630337652420474</v>
+        <v>0.01005752284711602</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007871613096928918</v>
+        <v>0.009482206029426404</v>
       </c>
     </row>
     <row r="8">
@@ -4841,14 +4337,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.00568025844907224</v>
+        <v>0.002896110449496803</v>
       </c>
       <c r="D8" t="n">
-        <v>0.006256462536271989</v>
+        <v>0.002979704670264355</v>
       </c>
     </row>
     <row r="9">
@@ -4857,14 +4353,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002052870971415743</v>
+        <v>0.002187830985377948</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001015596069508513</v>
+        <v>0.00124337066547511</v>
       </c>
     </row>
     <row r="10">
@@ -4873,14 +4369,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001983795074001271</v>
+        <v>0.002026978927481926</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0032075526729883</v>
+        <v>0.0008794336874163675</v>
       </c>
     </row>
     <row r="11">
@@ -4889,14 +4385,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001844892000747289</v>
+        <v>0.001891118951760018</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001423253453173209</v>
+        <v>0.000693013653229078</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4405,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001779321916018972</v>
+        <v>0.001760052614819696</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0008036913823119692</v>
+        <v>0.000741163319275532</v>
       </c>
     </row>
     <row r="13">
@@ -4921,14 +4417,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001578014665223137</v>
+        <v>0.001452730860708928</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0007915481404603431</v>
+        <v>0.0007434331820564014</v>
       </c>
     </row>
     <row r="14">
@@ -4937,14 +4433,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.00100101098018659</v>
+        <v>0.001049348338898826</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0009487944580273456</v>
+        <v>0.000708944762280956</v>
       </c>
     </row>
     <row r="15">
@@ -4953,14 +4449,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0009240955433845843</v>
+        <v>0.000968130304840853</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0003862988151961709</v>
+        <v>0.0004031229095314858</v>
       </c>
     </row>
     <row r="16">
@@ -4969,14 +4465,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.000919715062295523</v>
+        <v>0.0009191789197563916</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0008976573792548613</v>
+        <v>0.001030116055926881</v>
       </c>
     </row>
     <row r="17">
@@ -4985,14 +4481,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0008432482924329964</v>
+        <v>0.0005761158334296801</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0006481511736487772</v>
+        <v>0.000340834889009104</v>
       </c>
     </row>
     <row r="18">
@@ -5001,14 +4497,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0007888315273505309</v>
+        <v>0.0005103760204162921</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004382710824525421</v>
+        <v>0.001068686014161053</v>
       </c>
     </row>
     <row r="19">
@@ -5017,14 +4513,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.000644779558607167</v>
+        <v>0.0004800275824715427</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0007866134215645804</v>
+        <v>0.0002878537813064172</v>
       </c>
     </row>
     <row r="20">
@@ -5033,14 +4529,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0003960994362952164</v>
+        <v>0.0004704219754355088</v>
       </c>
       <c r="D20" t="n">
-        <v>0.000577701713640764</v>
+        <v>0.0009430689865364399</v>
       </c>
     </row>
     <row r="21">
@@ -5049,14 +4545,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0003768028270291435</v>
+        <v>0.0004690914681675706</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0007659054584839693</v>
+        <v>0.0006728725650358965</v>
       </c>
     </row>
     <row r="22">
@@ -5065,14 +4561,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0003557141340888026</v>
+        <v>0.0003696691256181106</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0006339294208247717</v>
+        <v>0.0005302413969517434</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +4581,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0003445564674894541</v>
+        <v>0.0001710574240983198</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0004497170012050446</v>
+        <v>0.0004214270206158944</v>
       </c>
     </row>
     <row r="24">
@@ -5097,14 +4593,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0003175231346934648</v>
+        <v>0.0001399817309445828</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0004633366953444537</v>
+        <v>0.0008752549210224343</v>
       </c>
     </row>
     <row r="25">
@@ -5113,14 +4609,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0001266286008868023</v>
+        <v>5.475633114864209e-05</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0004421366487265692</v>
+        <v>0.0002896047704000276</v>
       </c>
     </row>
     <row r="26">
@@ -5129,14 +4625,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0001024898684282127</v>
+        <v>3.065640373776102e-05</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0003451227360610102</v>
+        <v>0.001072227107456455</v>
       </c>
     </row>
     <row r="27">
@@ -5145,14 +4641,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3.235721233383337e-05</v>
+        <v>2.670205550561189e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0007478295686550927</v>
+        <v>5.595304995214385e-05</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +4661,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8.437338592170995e-06</v>
+        <v>2.178003377117932e-05</v>
       </c>
       <c r="D28" t="n">
-        <v>4.05003596524061e-05</v>
+        <v>4.742942043607184e-05</v>
       </c>
     </row>
     <row r="29">
@@ -5181,10 +4677,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-1.359412867494303e-05</v>
+        <v>2.261269987002823e-06</v>
       </c>
       <c r="D29" t="n">
-        <v>9.738304911571115e-06</v>
+        <v>1.394679902883111e-05</v>
       </c>
     </row>
     <row r="30">
@@ -5193,14 +4689,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-7.469104474945309e-05</v>
+        <v>-1.197908755594668e-05</v>
       </c>
       <c r="D30" t="n">
-        <v>2.374961421901144e-05</v>
+        <v>0.0002938786187225797</v>
       </c>
     </row>
     <row r="31">
@@ -5209,14 +4705,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.0001130712297016445</v>
+        <v>-3.759668213295653e-05</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0002439198331223278</v>
+        <v>0.001375536309292598</v>
       </c>
     </row>
     <row r="32">
@@ -5225,14 +4721,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.000116867521821129</v>
+        <v>-6.699779075663992e-05</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0007925235861203656</v>
+        <v>0.0003642295042400845</v>
       </c>
     </row>
     <row r="33">
@@ -5241,14 +4737,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.0001176716425591029</v>
+        <v>-0.0001084295481577846</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0004003034082453291</v>
+        <v>0.0002238110119874476</v>
       </c>
     </row>
     <row r="34">
@@ -5257,14 +4753,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-0.0001324463469226211</v>
+        <v>-0.0001981603957494582</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0006454520225867166</v>
+        <v>0.001285853683320945</v>
       </c>
     </row>
     <row r="35">
@@ -5273,14 +4769,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.0001846802514273493</v>
+        <v>-0.0003059325027456649</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0003716426206432347</v>
+        <v>0.0007227403281551511</v>
       </c>
     </row>
     <row r="36">
@@ -5289,14 +4785,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-0.0002343811958638198</v>
+        <v>-0.0003667063536589743</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0002369801329982529</v>
+        <v>0.0001064486771477869</v>
       </c>
     </row>
     <row r="37">
@@ -5305,14 +4801,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-0.0002662016962839186</v>
+        <v>-0.0003889017021755592</v>
       </c>
       <c r="D37" t="n">
-        <v>0.001046252188397809</v>
+        <v>0.0006589007058221225</v>
       </c>
     </row>
     <row r="38">
@@ -5321,14 +4817,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.000322610877194085</v>
+        <v>-0.0005945480339803022</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0005679444414767533</v>
+        <v>0.002519220233262997</v>
       </c>
     </row>
     <row r="39">
@@ -5337,14 +4833,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-0.0003362640018050534</v>
+        <v>-0.0009536340026055856</v>
       </c>
       <c r="D39" t="n">
-        <v>0.001038346870652626</v>
+        <v>0.001020407076883959</v>
       </c>
     </row>
     <row r="40">
@@ -5353,14 +4849,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.0003381286588021282</v>
+        <v>-0.001043504817726881</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0001501861388582111</v>
+        <v>0.0007044393561752445</v>
       </c>
     </row>
     <row r="41">
@@ -5369,14 +4865,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.000355331788304325</v>
+        <v>-0.001108651769762337</v>
       </c>
       <c r="D41" t="n">
-        <v>0.001327973294740708</v>
+        <v>0.0008287495657486651</v>
       </c>
     </row>
     <row r="42">
@@ -5385,14 +4881,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.0005601240915243166</v>
+        <v>-0.001282062987169463</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0006924028490437183</v>
+        <v>0.002191393682427736</v>
       </c>
     </row>
     <row r="43">
@@ -5401,14 +4897,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.0005687217856254368</v>
+        <v>-0.001431881710101368</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0003688365312417473</v>
+        <v>0.001589212883306287</v>
       </c>
     </row>
     <row r="44">
@@ -5417,14 +4913,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.0005821095161207101</v>
+        <v>-0.001567533699965473</v>
       </c>
       <c r="D44" t="n">
-        <v>0.000309178458053625</v>
+        <v>0.0009511263542079282</v>
       </c>
     </row>
     <row r="45">
@@ -5433,14 +4929,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.0006973893705868095</v>
+        <v>-0.001646701778544213</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0005757197257350385</v>
+        <v>0.0005677069968484419</v>
       </c>
     </row>
     <row r="46">
@@ -5449,142 +4945,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.0008029358153878397</v>
+        <v>-0.01994800481155735</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0006061992663919949</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>white_quality_ash_1</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.001000268056234821</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.000702974503828963</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>boiler_alkalinity</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.001176210536536837</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.00113022224031234</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>wastewater_r1_q</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.001400142969639095</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.0007410231991515731</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>sulphited_brix</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.001594134187858076</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.002652903816507246</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>wastewater_r3_pol</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.001754181676085642</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.001477833540605645</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>boiler_pH</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.001835082163533219</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.001875595212132234</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>boiler_tds</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.002288258689627687</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.0007930398669021883</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>boiling_r3_pol</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.02065342838184088</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.01710128647155745</v>
+        <v>0.01759865946527351</v>
       </c>
     </row>
   </sheetData>
@@ -5598,7 +4966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5628,7 +4996,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.217199826770076</v>
+        <v>3.30932801191722</v>
       </c>
     </row>
     <row r="3">
@@ -5641,7 +5009,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6266812437229703</v>
+        <v>0.6133443525541211</v>
       </c>
     </row>
     <row r="4">
@@ -5654,7 +5022,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.570501621941216</v>
+        <v>0.5633470533289877</v>
       </c>
     </row>
     <row r="5">
@@ -5663,11 +5031,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5494760899262703</v>
+        <v>0.4679373941863858</v>
       </c>
     </row>
     <row r="6">
@@ -5676,11 +5044,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4977597455062317</v>
+        <v>0.4417430249048664</v>
       </c>
     </row>
     <row r="7">
@@ -5689,11 +5057,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.4483518173824934</v>
+        <v>0.4236412742884825</v>
       </c>
     </row>
     <row r="8">
@@ -5702,11 +5070,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4345403141362918</v>
+        <v>0.3877720983365793</v>
       </c>
     </row>
     <row r="9">
@@ -5715,11 +5083,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.3646130720404273</v>
+        <v>0.2878244382117314</v>
       </c>
     </row>
     <row r="10">
@@ -5728,11 +5096,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3053870398541658</v>
+        <v>0.175949438741982</v>
       </c>
     </row>
     <row r="11">
@@ -5741,11 +5109,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1692192791397593</v>
+        <v>0.1217307240155732</v>
       </c>
     </row>
     <row r="12">
@@ -5754,11 +5122,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1254434905924073</v>
+        <v>0.1178906114592553</v>
       </c>
     </row>
     <row r="13">
@@ -5767,11 +5135,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1048756534983135</v>
+        <v>0.0974960962474043</v>
       </c>
     </row>
     <row r="14">
@@ -5780,11 +5148,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.1025833414056709</v>
+        <v>0.09636673418645758</v>
       </c>
     </row>
     <row r="15">
@@ -5793,11 +5161,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.1019034609444729</v>
+        <v>0.09455010903131766</v>
       </c>
     </row>
     <row r="16">
@@ -5806,11 +5174,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.09940350944057874</v>
+        <v>0.09295511854923344</v>
       </c>
     </row>
     <row r="17">
@@ -5819,11 +5187,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.09512582013044524</v>
+        <v>0.08951116693305528</v>
       </c>
     </row>
     <row r="18">
@@ -5832,11 +5200,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.093166113702428</v>
+        <v>0.08732432990716088</v>
       </c>
     </row>
     <row r="19">
@@ -5845,11 +5213,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.09174321924453599</v>
+        <v>0.08671619450310342</v>
       </c>
     </row>
     <row r="20">
@@ -5858,11 +5226,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.09083086368305082</v>
+        <v>0.08598618280692882</v>
       </c>
     </row>
     <row r="21">
@@ -5871,11 +5239,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0905561334862468</v>
+        <v>0.07904268812929427</v>
       </c>
     </row>
     <row r="22">
@@ -5888,7 +5256,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.08716430811798048</v>
+        <v>0.06928567198810898</v>
       </c>
     </row>
     <row r="23">
@@ -5897,11 +5265,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.08689986240107084</v>
+        <v>0.06646898364123421</v>
       </c>
     </row>
     <row r="24">
@@ -5910,11 +5278,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.08685309691882903</v>
+        <v>0.06509654794582742</v>
       </c>
     </row>
     <row r="25">
@@ -5923,11 +5291,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.08363311392339945</v>
+        <v>0.06252618266775078</v>
       </c>
     </row>
     <row r="26">
@@ -5936,11 +5304,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.07556918317667227</v>
+        <v>0.0611594562303921</v>
       </c>
     </row>
     <row r="27">
@@ -5949,11 +5317,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.07160750944347871</v>
+        <v>0.0610933553138997</v>
       </c>
     </row>
     <row r="28">
@@ -5962,11 +5330,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.06996116746814574</v>
+        <v>0.05817112037781236</v>
       </c>
     </row>
     <row r="29">
@@ -5975,11 +5343,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.06889905503980076</v>
+        <v>0.05757405598218046</v>
       </c>
     </row>
     <row r="30">
@@ -5988,11 +5356,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.06885634059986057</v>
+        <v>0.05687193118223988</v>
       </c>
     </row>
     <row r="31">
@@ -6001,11 +5369,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.06451952483190393</v>
+        <v>0.05200628049966616</v>
       </c>
     </row>
     <row r="32">
@@ -6014,11 +5382,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.06251763089092144</v>
+        <v>0.04621172202372525</v>
       </c>
     </row>
     <row r="33">
@@ -6027,11 +5395,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.06237385659098482</v>
+        <v>0.04358031670766582</v>
       </c>
     </row>
     <row r="34">
@@ -6040,11 +5408,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.05798891292858066</v>
+        <v>0.04349393965321102</v>
       </c>
     </row>
     <row r="35">
@@ -6053,11 +5421,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.05645906764891739</v>
+        <v>0.04221691003306827</v>
       </c>
     </row>
     <row r="36">
@@ -6066,11 +5434,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.05563326314330963</v>
+        <v>0.03891875623741914</v>
       </c>
     </row>
     <row r="37">
@@ -6079,11 +5447,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.05509654477754156</v>
+        <v>0.03709267834490237</v>
       </c>
     </row>
     <row r="38">
@@ -6092,11 +5460,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.05214674385507667</v>
+        <v>0.03194442705109424</v>
       </c>
     </row>
     <row r="39">
@@ -6105,11 +5473,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.05172742536939401</v>
+        <v>0.02826597200514547</v>
       </c>
     </row>
     <row r="40">
@@ -6118,11 +5486,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.05161042521237746</v>
+        <v>0.02619112774519694</v>
       </c>
     </row>
     <row r="41">
@@ -6135,7 +5503,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.05086326753294923</v>
+        <v>0.02062727123276442</v>
       </c>
     </row>
     <row r="42">
@@ -6144,11 +5512,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.04887474577110318</v>
+        <v>0.01280977170108821</v>
       </c>
     </row>
     <row r="43">
@@ -6157,11 +5525,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.04840436921305802</v>
+        <v>0.01042125524955018</v>
       </c>
     </row>
     <row r="44">
@@ -6170,11 +5538,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.04226815071445378</v>
+        <v>0.008165286133118066</v>
       </c>
     </row>
     <row r="45">
@@ -6183,11 +5551,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.03837673494691041</v>
+        <v>0.00267286399738742</v>
       </c>
     </row>
     <row r="46">
@@ -6196,114 +5564,10 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0293026860189376</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_1</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.02641531674244479</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>filtercake_moisture</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.0170518314484025</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>sulphited_pH</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.01399424186190457</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.007442339912218543</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.007422689391729964</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>boiler_pH</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.004580767337865055</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.001886324116872284</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6379,10 +5643,10 @@
         <v>197</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -6391,7 +5655,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-15 07:32:25 UTC</t>
+          <t>2026-06-16 12:02:47 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_invert.xlsx
+++ b/NN/reports/feature_importance_white_invert.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4989035165520892</v>
+        <v>0.4989035165521696</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -550,7 +550,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01397738149444664</v>
+        <v>0.01397738149444684</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03795103460855278</v>
+        <v>0.03795103460855298</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -624,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01405496590223929</v>
+        <v>0.01405496590223948</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -661,7 +661,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01005752284711602</v>
+        <v>0.01005752284711632</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
@@ -698,7 +698,7 @@
         <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01054244038022029</v>
+        <v>0.01054244038022048</v>
       </c>
       <c r="H7" t="n">
         <v>5</v>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001891118951760018</v>
+        <v>0.001891118951760251</v>
       </c>
       <c r="H8" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0004704219754355088</v>
+        <v>0.0004704219754356753</v>
       </c>
       <c r="H9" t="n">
         <v>19</v>
@@ -809,7 +809,7 @@
         <v>17</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0009191789197563916</v>
+        <v>0.0009191789197565914</v>
       </c>
       <c r="H10" t="n">
         <v>15</v>
@@ -846,7 +846,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002026978927481926</v>
+        <v>0.00202697892748207</v>
       </c>
       <c r="H11" t="n">
         <v>9</v>
@@ -883,7 +883,7 @@
         <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002896110449496803</v>
+        <v>0.002896110449496947</v>
       </c>
       <c r="H12" t="n">
         <v>7</v>
@@ -920,7 +920,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009536340026055856</v>
+        <v>-0.0009536340026054524</v>
       </c>
       <c r="H13" t="n">
         <v>38</v>
@@ -957,7 +957,7 @@
         <v>33</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001452730860708928</v>
+        <v>0.001452730860709106</v>
       </c>
       <c r="H14" t="n">
         <v>12</v>
@@ -994,7 +994,7 @@
         <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.759668213295653e-05</v>
+        <v>-3.759668213288991e-05</v>
       </c>
       <c r="H15" t="n">
         <v>30</v>
@@ -1031,7 +1031,7 @@
         <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002187830985377948</v>
+        <v>0.002187830985378136</v>
       </c>
       <c r="H16" t="n">
         <v>8</v>
@@ -1068,7 +1068,7 @@
         <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0001399817309445828</v>
+        <v>0.0001399817309448048</v>
       </c>
       <c r="H17" t="n">
         <v>23</v>
@@ -1105,7 +1105,7 @@
         <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0003059325027456649</v>
+        <v>-0.0003059325027454096</v>
       </c>
       <c r="H18" t="n">
         <v>34</v>
@@ -1142,7 +1142,7 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001760052614819696</v>
+        <v>0.001760052614819896</v>
       </c>
       <c r="H19" t="n">
         <v>11</v>
@@ -1179,7 +1179,7 @@
         <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.001646701778544213</v>
+        <v>-0.001646701778543946</v>
       </c>
       <c r="H20" t="n">
         <v>44</v>
@@ -1216,7 +1216,7 @@
         <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0005945480339803022</v>
+        <v>-0.000594548033980058</v>
       </c>
       <c r="H21" t="n">
         <v>37</v>
@@ -1253,7 +1253,7 @@
         <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.001567533699965473</v>
+        <v>-0.001567533699965351</v>
       </c>
       <c r="H22" t="n">
         <v>43</v>
@@ -1290,7 +1290,7 @@
         <v>21</v>
       </c>
       <c r="G23" t="n">
-        <v>5.475633114864209e-05</v>
+        <v>5.475633114891965e-05</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1327,7 +1327,7 @@
         <v>26</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0003696691256181106</v>
+        <v>0.0003696691256183437</v>
       </c>
       <c r="H24" t="n">
         <v>21</v>
@@ -1364,7 +1364,7 @@
         <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0005103760204162921</v>
+        <v>0.0005103760204165475</v>
       </c>
       <c r="H25" t="n">
         <v>17</v>
@@ -1401,7 +1401,7 @@
         <v>29</v>
       </c>
       <c r="G26" t="n">
-        <v>0.001049348338898826</v>
+        <v>0.001049348338899037</v>
       </c>
       <c r="H26" t="n">
         <v>13</v>
@@ -1438,7 +1438,7 @@
         <v>38</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.01994800481155735</v>
+        <v>-0.01994800481155714</v>
       </c>
       <c r="H27" t="n">
         <v>45</v>
@@ -1475,7 +1475,7 @@
         <v>27</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0001981603957494582</v>
+        <v>-0.0001981603957492362</v>
       </c>
       <c r="H28" t="n">
         <v>33</v>
@@ -1512,7 +1512,7 @@
         <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0004690914681675706</v>
+        <v>0.0004690914681677371</v>
       </c>
       <c r="H29" t="n">
         <v>20</v>
@@ -1549,7 +1549,7 @@
         <v>16</v>
       </c>
       <c r="G30" t="n">
-        <v>2.670205550561189e-05</v>
+        <v>2.670205550584503e-05</v>
       </c>
       <c r="H30" t="n">
         <v>26</v>
@@ -1586,7 +1586,7 @@
         <v>31</v>
       </c>
       <c r="G31" t="n">
-        <v>0.000968130304840853</v>
+        <v>0.0009681303048411194</v>
       </c>
       <c r="H31" t="n">
         <v>14</v>
@@ -1623,7 +1623,7 @@
         <v>34</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0005761158334296801</v>
+        <v>0.0005761158334298355</v>
       </c>
       <c r="H32" t="n">
         <v>16</v>
@@ -1660,7 +1660,7 @@
         <v>28</v>
       </c>
       <c r="G33" t="n">
-        <v>3.065640373776102e-05</v>
+        <v>3.065640373801637e-05</v>
       </c>
       <c r="H33" t="n">
         <v>25</v>
@@ -1697,7 +1697,7 @@
         <v>24</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.001431881710101368</v>
+        <v>-0.001431881710101224</v>
       </c>
       <c r="H34" t="n">
         <v>42</v>
@@ -1734,7 +1734,7 @@
         <v>23</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.001282062987169463</v>
+        <v>-0.001282062987169363</v>
       </c>
       <c r="H35" t="n">
         <v>41</v>
@@ -1771,7 +1771,7 @@
         <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0003889017021755592</v>
+        <v>-0.0003889017021754149</v>
       </c>
       <c r="H36" t="n">
         <v>36</v>
@@ -1808,7 +1808,7 @@
         <v>36</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0001710574240983198</v>
+        <v>0.0001710574240985085</v>
       </c>
       <c r="H37" t="n">
         <v>22</v>
@@ -1845,7 +1845,7 @@
         <v>37</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.001108651769762337</v>
+        <v>-0.001108651769762081</v>
       </c>
       <c r="H38" t="n">
         <v>40</v>
@@ -1882,7 +1882,7 @@
         <v>39</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.001043504817726881</v>
+        <v>-0.001043504817726693</v>
       </c>
       <c r="H39" t="n">
         <v>39</v>
@@ -1919,7 +1919,7 @@
         <v>41</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0004800275824715427</v>
+        <v>0.0004800275824717648</v>
       </c>
       <c r="H40" t="n">
         <v>18</v>
@@ -1956,7 +1956,7 @@
         <v>35</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.197908755594668e-05</v>
+        <v>-1.197908755564692e-05</v>
       </c>
       <c r="H41" t="n">
         <v>29</v>
@@ -1993,7 +1993,7 @@
         <v>40</v>
       </c>
       <c r="G42" t="n">
-        <v>-6.699779075663992e-05</v>
+        <v>-6.699779075645119e-05</v>
       </c>
       <c r="H42" t="n">
         <v>31</v>
@@ -2030,7 +2030,7 @@
         <v>43</v>
       </c>
       <c r="G43" t="n">
-        <v>2.178003377117932e-05</v>
+        <v>2.178003377140136e-05</v>
       </c>
       <c r="H43" t="n">
         <v>27</v>
@@ -2067,7 +2067,7 @@
         <v>44</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.0001084295481577846</v>
+        <v>-0.0001084295481575959</v>
       </c>
       <c r="H44" t="n">
         <v>32</v>
@@ -2104,7 +2104,7 @@
         <v>45</v>
       </c>
       <c r="G45" t="n">
-        <v>2.261269987002823e-06</v>
+        <v>2.261269987313685e-06</v>
       </c>
       <c r="H45" t="n">
         <v>28</v>
@@ -2141,7 +2141,7 @@
         <v>42</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.0003667063536589743</v>
+        <v>-0.0003667063536587411</v>
       </c>
       <c r="H46" t="n">
         <v>35</v>
@@ -2249,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4989035165520892</v>
+        <v>0.4989035165521696</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -2286,7 +2286,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01397738149444664</v>
+        <v>0.01397738149444684</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -2323,7 +2323,7 @@
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03795103460855278</v>
+        <v>0.03795103460855298</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -2360,7 +2360,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01405496590223929</v>
+        <v>0.01405496590223948</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -2397,7 +2397,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01005752284711602</v>
+        <v>0.01005752284711632</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
@@ -2434,7 +2434,7 @@
         <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01054244038022029</v>
+        <v>0.01054244038022048</v>
       </c>
       <c r="H7" t="n">
         <v>5</v>
@@ -2471,7 +2471,7 @@
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001891118951760018</v>
+        <v>0.001891118951760251</v>
       </c>
       <c r="H8" t="n">
         <v>10</v>
@@ -2508,7 +2508,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0004704219754355088</v>
+        <v>0.0004704219754356753</v>
       </c>
       <c r="H9" t="n">
         <v>19</v>
@@ -2545,7 +2545,7 @@
         <v>17</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0009191789197563916</v>
+        <v>0.0009191789197565914</v>
       </c>
       <c r="H10" t="n">
         <v>15</v>
@@ -2582,7 +2582,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002026978927481926</v>
+        <v>0.00202697892748207</v>
       </c>
       <c r="H11" t="n">
         <v>9</v>
@@ -2619,7 +2619,7 @@
         <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002896110449496803</v>
+        <v>0.002896110449496947</v>
       </c>
       <c r="H12" t="n">
         <v>7</v>
@@ -2656,7 +2656,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009536340026055856</v>
+        <v>-0.0009536340026054524</v>
       </c>
       <c r="H13" t="n">
         <v>38</v>
@@ -2693,7 +2693,7 @@
         <v>33</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001452730860708928</v>
+        <v>0.001452730860709106</v>
       </c>
       <c r="H14" t="n">
         <v>12</v>
@@ -2730,7 +2730,7 @@
         <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.759668213295653e-05</v>
+        <v>-3.759668213288991e-05</v>
       </c>
       <c r="H15" t="n">
         <v>30</v>
@@ -2767,7 +2767,7 @@
         <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002187830985377948</v>
+        <v>0.002187830985378136</v>
       </c>
       <c r="H16" t="n">
         <v>8</v>
@@ -2804,7 +2804,7 @@
         <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0001399817309445828</v>
+        <v>0.0001399817309448048</v>
       </c>
       <c r="H17" t="n">
         <v>23</v>
@@ -2841,7 +2841,7 @@
         <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0003059325027456649</v>
+        <v>-0.0003059325027454096</v>
       </c>
       <c r="H18" t="n">
         <v>34</v>
@@ -2878,7 +2878,7 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001760052614819696</v>
+        <v>0.001760052614819896</v>
       </c>
       <c r="H19" t="n">
         <v>11</v>
@@ -2915,7 +2915,7 @@
         <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.001646701778544213</v>
+        <v>-0.001646701778543946</v>
       </c>
       <c r="H20" t="n">
         <v>44</v>
@@ -2952,7 +2952,7 @@
         <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0005945480339803022</v>
+        <v>-0.000594548033980058</v>
       </c>
       <c r="H21" t="n">
         <v>37</v>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4989035165520892</v>
+        <v>0.4989035165521696</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01819150998256065</v>
+        <v>0.01819150998256155</v>
       </c>
     </row>
     <row r="3">
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03795103460855278</v>
+        <v>0.03795103460855298</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009126663824703301</v>
+        <v>0.009126663824703337</v>
       </c>
     </row>
     <row r="4">
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.01405496590223929</v>
+        <v>0.01405496590223948</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01011127298399658</v>
+        <v>0.01011127298399657</v>
       </c>
     </row>
     <row r="5">
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.01397738149444664</v>
+        <v>0.01397738149444684</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01003196773152265</v>
+        <v>0.01003196773152271</v>
       </c>
     </row>
     <row r="6">
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01054244038022029</v>
+        <v>0.01054244038022048</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007162386490488457</v>
+        <v>0.007162386490488453</v>
       </c>
     </row>
     <row r="7">
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01005752284711602</v>
+        <v>0.01005752284711632</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009482206029426404</v>
+        <v>0.009482206029426508</v>
       </c>
     </row>
     <row r="8">
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.002896110449496803</v>
+        <v>0.002896110449496947</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002979704670264355</v>
+        <v>0.002979704670264367</v>
       </c>
     </row>
     <row r="9">
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002187830985377948</v>
+        <v>0.002187830985378136</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00124337066547511</v>
+        <v>0.001243370665475124</v>
       </c>
     </row>
     <row r="10">
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002026978927481926</v>
+        <v>0.00202697892748207</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0008794336874163675</v>
+        <v>0.0008794336874163914</v>
       </c>
     </row>
     <row r="11">
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001891118951760018</v>
+        <v>0.001891118951760251</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000693013653229078</v>
+        <v>0.0006930136532290012</v>
       </c>
     </row>
     <row r="12">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001760052614819696</v>
+        <v>0.001760052614819896</v>
       </c>
       <c r="D12" t="n">
-        <v>0.000741163319275532</v>
+        <v>0.0007411633192756026</v>
       </c>
     </row>
     <row r="13">
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001452730860708928</v>
+        <v>0.001452730860709106</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0007434331820564014</v>
+        <v>0.0007434331820563361</v>
       </c>
     </row>
     <row r="14">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001049348338898826</v>
+        <v>0.001049348338899037</v>
       </c>
       <c r="D14" t="n">
-        <v>0.000708944762280956</v>
+        <v>0.0007089447622808853</v>
       </c>
     </row>
     <row r="15">
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.000968130304840853</v>
+        <v>0.0009681303048411194</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0004031229095314858</v>
+        <v>0.0004031229095314836</v>
       </c>
     </row>
     <row r="16">
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0009191789197563916</v>
+        <v>0.0009191789197565914</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001030116055926881</v>
+        <v>0.001030116055926961</v>
       </c>
     </row>
     <row r="17">
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0005761158334296801</v>
+        <v>0.0005761158334298355</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000340834889009104</v>
+        <v>0.0003408348890090258</v>
       </c>
     </row>
     <row r="18">
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0005103760204162921</v>
+        <v>0.0005103760204165475</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001068686014161053</v>
+        <v>0.001068686014161089</v>
       </c>
     </row>
     <row r="19">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004800275824715427</v>
+        <v>0.0004800275824717648</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0002878537813064172</v>
+        <v>0.0002878537813064774</v>
       </c>
     </row>
     <row r="20">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0004704219754355088</v>
+        <v>0.0004704219754356753</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0009430689865364399</v>
+        <v>0.0009430689865363904</v>
       </c>
     </row>
     <row r="21">
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0004690914681675706</v>
+        <v>0.0004690914681677371</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0006728725650358965</v>
+        <v>0.0006728725650358712</v>
       </c>
     </row>
     <row r="22">
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0003696691256181106</v>
+        <v>0.0003696691256183437</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0005302413969517434</v>
+        <v>0.0005302413969517993</v>
       </c>
     </row>
     <row r="23">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0001710574240983198</v>
+        <v>0.0001710574240985085</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0004214270206158944</v>
+        <v>0.0004214270206159044</v>
       </c>
     </row>
     <row r="24">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0001399817309445828</v>
+        <v>0.0001399817309448048</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0008752549210224343</v>
+        <v>0.0008752549210223893</v>
       </c>
     </row>
     <row r="25">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5.475633114864209e-05</v>
+        <v>5.475633114891965e-05</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0002896047704000276</v>
+        <v>0.0002896047704000793</v>
       </c>
     </row>
     <row r="26">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3.065640373776102e-05</v>
+        <v>3.065640373801637e-05</v>
       </c>
       <c r="D26" t="n">
-        <v>0.001072227107456455</v>
+        <v>0.001072227107456356</v>
       </c>
     </row>
     <row r="27">
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.670205550561189e-05</v>
+        <v>2.670205550584503e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>5.595304995214385e-05</v>
+        <v>5.595304995212911e-05</v>
       </c>
     </row>
     <row r="28">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.178003377117932e-05</v>
+        <v>2.178003377140136e-05</v>
       </c>
       <c r="D28" t="n">
-        <v>4.742942043607184e-05</v>
+        <v>4.742942043602188e-05</v>
       </c>
     </row>
     <row r="29">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.261269987002823e-06</v>
+        <v>2.261269987313685e-06</v>
       </c>
       <c r="D29" t="n">
-        <v>1.394679902883111e-05</v>
+        <v>1.394679902876654e-05</v>
       </c>
     </row>
     <row r="30">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-1.197908755594668e-05</v>
+        <v>-1.197908755564692e-05</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0002938786187225797</v>
+        <v>0.0002938786187225915</v>
       </c>
     </row>
     <row r="31">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-3.759668213295653e-05</v>
+        <v>-3.759668213288991e-05</v>
       </c>
       <c r="D31" t="n">
-        <v>0.001375536309292598</v>
+        <v>0.001375536309292667</v>
       </c>
     </row>
     <row r="32">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-6.699779075663992e-05</v>
+        <v>-6.699779075645119e-05</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0003642295042400845</v>
+        <v>0.0003642295042399658</v>
       </c>
     </row>
     <row r="33">
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.0001084295481577846</v>
+        <v>-0.0001084295481575959</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0002238110119874476</v>
+        <v>0.0002238110119874446</v>
       </c>
     </row>
     <row r="34">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-0.0001981603957494582</v>
+        <v>-0.0001981603957492362</v>
       </c>
       <c r="D34" t="n">
-        <v>0.001285853683320945</v>
+        <v>0.00128585368332098</v>
       </c>
     </row>
     <row r="35">
@@ -4773,10 +4773,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.0003059325027456649</v>
+        <v>-0.0003059325027454096</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0007227403281551511</v>
+        <v>0.0007227403281550962</v>
       </c>
     </row>
     <row r="36">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-0.0003667063536589743</v>
+        <v>-0.0003667063536587411</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0001064486771477869</v>
+        <v>0.000106448677147675</v>
       </c>
     </row>
     <row r="37">
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-0.0003889017021755592</v>
+        <v>-0.0003889017021754149</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0006589007058221225</v>
+        <v>0.0006589007058221275</v>
       </c>
     </row>
     <row r="38">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.0005945480339803022</v>
+        <v>-0.000594548033980058</v>
       </c>
       <c r="D38" t="n">
-        <v>0.002519220233262997</v>
+        <v>0.002519220233262982</v>
       </c>
     </row>
     <row r="39">
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-0.0009536340026055856</v>
+        <v>-0.0009536340026054524</v>
       </c>
       <c r="D39" t="n">
-        <v>0.001020407076883959</v>
+        <v>0.001020407076884006</v>
       </c>
     </row>
     <row r="40">
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.001043504817726881</v>
+        <v>-0.001043504817726693</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0007044393561752445</v>
+        <v>0.0007044393561752292</v>
       </c>
     </row>
     <row r="41">
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.001108651769762337</v>
+        <v>-0.001108651769762081</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0008287495657486651</v>
+        <v>0.0008287495657486152</v>
       </c>
     </row>
     <row r="42">
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.001282062987169463</v>
+        <v>-0.001282062987169363</v>
       </c>
       <c r="D42" t="n">
-        <v>0.002191393682427736</v>
+        <v>0.00219139368242773</v>
       </c>
     </row>
     <row r="43">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.001431881710101368</v>
+        <v>-0.001431881710101224</v>
       </c>
       <c r="D43" t="n">
-        <v>0.001589212883306287</v>
+        <v>0.001589212883306259</v>
       </c>
     </row>
     <row r="44">
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.001567533699965473</v>
+        <v>-0.001567533699965351</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0009511263542079282</v>
+        <v>0.0009511263542079075</v>
       </c>
     </row>
     <row r="45">
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.001646701778544213</v>
+        <v>-0.001646701778543946</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0005677069968484419</v>
+        <v>0.0005677069968485108</v>
       </c>
     </row>
     <row r="46">
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.01994800481155735</v>
+        <v>-0.01994800481155714</v>
       </c>
       <c r="D46" t="n">
-        <v>0.01759865946527351</v>
+        <v>0.01759865946527336</v>
       </c>
     </row>
   </sheetData>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-16 12:02:47 UTC</t>
+          <t>2026-06-16 14:10:15 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_invert.xlsx
+++ b/NN/reports/feature_importance_white_invert.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5060052298913096</v>
+        <v>0.5060052298913145</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -550,7 +550,7 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0338395779654817</v>
+        <v>0.03383957796548175</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01091706533964594</v>
+        <v>0.01091706533964596</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -624,7 +624,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006303376524204596</v>
+        <v>0.006303376524204696</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
@@ -661,7 +661,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007697035974072464</v>
+        <v>0.007697035974072531</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008045855817688996</v>
+        <v>0.008045855817689084</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -735,7 +735,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005680258449072129</v>
+        <v>0.005680258449072151</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -772,7 +772,7 @@
         <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001578014665222949</v>
+        <v>0.001578014665222971</v>
       </c>
       <c r="H9" t="n">
         <v>12</v>
@@ -809,7 +809,7 @@
         <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0001168675218212956</v>
+        <v>-0.0001168675218213067</v>
       </c>
       <c r="H10" t="n">
         <v>31</v>
@@ -846,7 +846,7 @@
         <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0002662016962840186</v>
+        <v>-0.0002662016962840297</v>
       </c>
       <c r="H11" t="n">
         <v>36</v>
@@ -883,7 +883,7 @@
         <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0006447795586071115</v>
+        <v>0.0006447795586070115</v>
       </c>
       <c r="H12" t="n">
         <v>18</v>
@@ -920,7 +920,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001983795074001027</v>
+        <v>0.001983795074001071</v>
       </c>
       <c r="H13" t="n">
         <v>9</v>
@@ -957,7 +957,7 @@
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.02065342838184092</v>
+        <v>-0.02065342838184094</v>
       </c>
       <c r="H14" t="n">
         <v>53</v>
@@ -994,7 +994,7 @@
         <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.00205287097141571</v>
+        <v>0.002052870971415699</v>
       </c>
       <c r="H15" t="n">
         <v>8</v>
@@ -1031,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001779321916018972</v>
+        <v>0.001779321916018906</v>
       </c>
       <c r="H16" t="n">
         <v>11</v>
@@ -1068,7 +1068,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0003553317883045026</v>
+        <v>-0.0003553317883044804</v>
       </c>
       <c r="H17" t="n">
         <v>40</v>
@@ -1105,7 +1105,7 @@
         <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001001010980186467</v>
+        <v>0.001001010980186423</v>
       </c>
       <c r="H18" t="n">
         <v>13</v>
@@ -1142,7 +1142,7 @@
         <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0001324463469226989</v>
+        <v>-0.0001324463469227211</v>
       </c>
       <c r="H19" t="n">
         <v>33</v>
@@ -1179,7 +1179,7 @@
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001844892000747178</v>
+        <v>0.001844892000747145</v>
       </c>
       <c r="H20" t="n">
         <v>10</v>
@@ -1216,7 +1216,7 @@
         <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0005601240915245054</v>
+        <v>-0.0005601240915244388</v>
       </c>
       <c r="H21" t="n">
         <v>41</v>
@@ -1253,7 +1253,7 @@
         <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.002288258689627743</v>
+        <v>-0.00228825868962772</v>
       </c>
       <c r="H22" t="n">
         <v>52</v>
@@ -1290,7 +1290,7 @@
         <v>32</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0008432482924328521</v>
+        <v>0.0008432482924329409</v>
       </c>
       <c r="H23" t="n">
         <v>16</v>
@@ -1327,7 +1327,7 @@
         <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.001176210536536926</v>
+        <v>-0.001176210536536981</v>
       </c>
       <c r="H24" t="n">
         <v>47</v>
@@ -1401,7 +1401,7 @@
         <v>25</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.00159413418785822</v>
+        <v>-0.001594134187858109</v>
       </c>
       <c r="H26" t="n">
         <v>49</v>
@@ -1438,7 +1438,7 @@
         <v>30</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0001176716425592028</v>
+        <v>-0.0001176716425591806</v>
       </c>
       <c r="H27" t="n">
         <v>32</v>
@@ -1475,7 +1475,7 @@
         <v>31</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0003362640018051977</v>
+        <v>-0.0003362640018051199</v>
       </c>
       <c r="H28" t="n">
         <v>38</v>
@@ -1512,7 +1512,7 @@
         <v>33</v>
       </c>
       <c r="G29" t="n">
-        <v>3.235721233372235e-05</v>
+        <v>3.235721233366684e-05</v>
       </c>
       <c r="H29" t="n">
         <v>26</v>
@@ -1549,7 +1549,7 @@
         <v>34</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0003768028270288881</v>
+        <v>0.0003768028270289214</v>
       </c>
       <c r="H30" t="n">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>43</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0001024898684281017</v>
+        <v>0.0001024898684280684</v>
       </c>
       <c r="H32" t="n">
         <v>25</v>
@@ -1660,7 +1660,7 @@
         <v>26</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0009197150622953898</v>
+        <v>0.0009197150622954897</v>
       </c>
       <c r="H33" t="n">
         <v>15</v>
@@ -1697,7 +1697,7 @@
         <v>38</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0007888315273503865</v>
+        <v>0.0007888315273503532</v>
       </c>
       <c r="H34" t="n">
         <v>17</v>
@@ -1734,7 +1734,7 @@
         <v>35</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0003960994362950831</v>
+        <v>0.000396099436295072</v>
       </c>
       <c r="H35" t="n">
         <v>19</v>
@@ -1771,7 +1771,7 @@
         <v>49</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0009240955433844622</v>
+        <v>0.0009240955433845067</v>
       </c>
       <c r="H36" t="n">
         <v>14</v>
@@ -1808,7 +1808,7 @@
         <v>29</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.001754181676085709</v>
+        <v>-0.001754181676085664</v>
       </c>
       <c r="H37" t="n">
         <v>50</v>
@@ -1845,7 +1845,7 @@
         <v>39</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0003175231346934093</v>
+        <v>0.0003175231346933871</v>
       </c>
       <c r="H38" t="n">
         <v>23</v>
@@ -1882,7 +1882,7 @@
         <v>40</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0005821095161208434</v>
+        <v>-0.0005821095161207879</v>
       </c>
       <c r="H39" t="n">
         <v>43</v>
@@ -1919,7 +1919,7 @@
         <v>17</v>
       </c>
       <c r="G40" t="n">
-        <v>-7.469104474953082e-05</v>
+        <v>-7.469104474955301e-05</v>
       </c>
       <c r="H40" t="n">
         <v>29</v>
@@ -1956,7 +1956,7 @@
         <v>45</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0003226108771942737</v>
+        <v>-0.0003226108771941294</v>
       </c>
       <c r="H41" t="n">
         <v>37</v>
@@ -1993,7 +1993,7 @@
         <v>48</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0003445564674893431</v>
+        <v>0.0003445564674893875</v>
       </c>
       <c r="H42" t="n">
         <v>22</v>
@@ -2067,7 +2067,7 @@
         <v>28</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.001835082163533341</v>
+        <v>-0.001835082163533308</v>
       </c>
       <c r="H44" t="n">
         <v>51</v>
@@ -2104,7 +2104,7 @@
         <v>37</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.000697389370586865</v>
+        <v>-0.0006973893705868317</v>
       </c>
       <c r="H45" t="n">
         <v>44</v>
@@ -2141,7 +2141,7 @@
         <v>36</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.0008029358153880173</v>
+        <v>-0.0008029358153879729</v>
       </c>
       <c r="H46" t="n">
         <v>45</v>
@@ -2178,7 +2178,7 @@
         <v>46</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.001400142969639295</v>
+        <v>-0.001400142969639229</v>
       </c>
       <c r="H47" t="n">
         <v>48</v>
@@ -2215,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.0001130712297018111</v>
+        <v>-0.0001130712297018333</v>
       </c>
       <c r="H48" t="n">
         <v>30</v>
@@ -2252,7 +2252,7 @@
         <v>44</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.0001846802514274159</v>
+        <v>-0.0001846802514273937</v>
       </c>
       <c r="H49" t="n">
         <v>34</v>
@@ -2289,7 +2289,7 @@
         <v>53</v>
       </c>
       <c r="G50" t="n">
-        <v>-1.359412867504295e-05</v>
+        <v>-1.359412867499854e-05</v>
       </c>
       <c r="H50" t="n">
         <v>28</v>
@@ -2326,7 +2326,7 @@
         <v>47</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.0005687217856254589</v>
+        <v>-0.0005687217856255034</v>
       </c>
       <c r="H51" t="n">
         <v>42</v>
@@ -2363,7 +2363,7 @@
         <v>52</v>
       </c>
       <c r="G52" t="n">
-        <v>8.437338592059972e-06</v>
+        <v>8.437338592137689e-06</v>
       </c>
       <c r="H52" t="n">
         <v>27</v>
@@ -2400,7 +2400,7 @@
         <v>51</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.000234381195863842</v>
+        <v>-0.0002343811958638753</v>
       </c>
       <c r="H53" t="n">
         <v>35</v>
@@ -2437,7 +2437,7 @@
         <v>50</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.0003381286588022614</v>
+        <v>-0.0003381286588023169</v>
       </c>
       <c r="H54" t="n">
         <v>39</v>
@@ -2545,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5060052298913096</v>
+        <v>0.5060052298913145</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -2582,7 +2582,7 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0338395779654817</v>
+        <v>0.03383957796548175</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2619,7 +2619,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01091706533964594</v>
+        <v>0.01091706533964596</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -2656,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006303376524204596</v>
+        <v>0.006303376524204696</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
@@ -2693,7 +2693,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007697035974072464</v>
+        <v>0.007697035974072531</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008045855817688996</v>
+        <v>0.008045855817689084</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -2767,7 +2767,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005680258449072129</v>
+        <v>0.005680258449072151</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -2804,7 +2804,7 @@
         <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001578014665222949</v>
+        <v>0.001578014665222971</v>
       </c>
       <c r="H9" t="n">
         <v>12</v>
@@ -2841,7 +2841,7 @@
         <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0001168675218212956</v>
+        <v>-0.0001168675218213067</v>
       </c>
       <c r="H10" t="n">
         <v>31</v>
@@ -2878,7 +2878,7 @@
         <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0002662016962840186</v>
+        <v>-0.0002662016962840297</v>
       </c>
       <c r="H11" t="n">
         <v>36</v>
@@ -2915,7 +2915,7 @@
         <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0006447795586071115</v>
+        <v>0.0006447795586070115</v>
       </c>
       <c r="H12" t="n">
         <v>18</v>
@@ -2952,7 +2952,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001983795074001027</v>
+        <v>0.001983795074001071</v>
       </c>
       <c r="H13" t="n">
         <v>9</v>
@@ -2989,7 +2989,7 @@
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.02065342838184092</v>
+        <v>-0.02065342838184094</v>
       </c>
       <c r="H14" t="n">
         <v>53</v>
@@ -3026,7 +3026,7 @@
         <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.00205287097141571</v>
+        <v>0.002052870971415699</v>
       </c>
       <c r="H15" t="n">
         <v>8</v>
@@ -3063,7 +3063,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001779321916018972</v>
+        <v>0.001779321916018906</v>
       </c>
       <c r="H16" t="n">
         <v>11</v>
@@ -3100,7 +3100,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0003553317883045026</v>
+        <v>-0.0003553317883044804</v>
       </c>
       <c r="H17" t="n">
         <v>40</v>
@@ -3137,7 +3137,7 @@
         <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001001010980186467</v>
+        <v>0.001001010980186423</v>
       </c>
       <c r="H18" t="n">
         <v>13</v>
@@ -3174,7 +3174,7 @@
         <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0001324463469226989</v>
+        <v>-0.0001324463469227211</v>
       </c>
       <c r="H19" t="n">
         <v>33</v>
@@ -3211,7 +3211,7 @@
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001844892000747178</v>
+        <v>0.001844892000747145</v>
       </c>
       <c r="H20" t="n">
         <v>10</v>
@@ -3248,7 +3248,7 @@
         <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0005601240915245054</v>
+        <v>-0.0005601240915244388</v>
       </c>
       <c r="H21" t="n">
         <v>41</v>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5060052298913096</v>
+        <v>0.5060052298913145</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01887199810102201</v>
+        <v>0.01887199810101933</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0338395779654817</v>
+        <v>0.03383957796548175</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008895305012611683</v>
+        <v>0.008895305012611716</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.01091706533964594</v>
+        <v>0.01091706533964596</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007702337358314838</v>
+        <v>0.007702337358314855</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.008045855817688996</v>
+        <v>0.008045855817689084</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006414602234832935</v>
+        <v>0.006414602234832971</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.007697035974072464</v>
+        <v>0.007697035974072531</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00810651645131924</v>
+        <v>0.008106516451319325</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.006303376524204596</v>
+        <v>0.006303376524204696</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007871613096928937</v>
+        <v>0.007871613096928905</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.005680258449072129</v>
+        <v>0.005680258449072151</v>
       </c>
       <c r="D8" t="n">
-        <v>0.006256462536271941</v>
+        <v>0.006256462536271897</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.00205287097141571</v>
+        <v>0.002052870971415699</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0010155960695085</v>
+        <v>0.001015596069508517</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001983795074001027</v>
+        <v>0.001983795074001071</v>
       </c>
       <c r="D10" t="n">
-        <v>0.003207552672988284</v>
+        <v>0.003207552672988223</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001844892000747178</v>
+        <v>0.001844892000747145</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001423253453173156</v>
+        <v>0.001423253453173133</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001779321916018972</v>
+        <v>0.001779321916018906</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0008036913823119508</v>
+        <v>0.0008036913823119825</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001578014665222949</v>
+        <v>0.001578014665222971</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0007915481404603266</v>
+        <v>0.0007915481404603698</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001001010980186467</v>
+        <v>0.001001010980186423</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0009487944580273079</v>
+        <v>0.000948794458027348</v>
       </c>
     </row>
     <row r="15">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0009240955433844622</v>
+        <v>0.0009240955433845067</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0003862988151962236</v>
+        <v>0.0003862988151961501</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0009197150622953898</v>
+        <v>0.0009197150622954897</v>
       </c>
       <c r="D16" t="n">
-        <v>0.000897657379254809</v>
+        <v>0.0008976573792548679</v>
       </c>
     </row>
     <row r="17">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0008432482924328521</v>
+        <v>0.0008432482924329409</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0006481511736487669</v>
+        <v>0.0006481511736487971</v>
       </c>
     </row>
     <row r="18">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0007888315273503865</v>
+        <v>0.0007888315273503532</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004382710824525623</v>
+        <v>0.0004382710824526334</v>
       </c>
     </row>
     <row r="19">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0006447795586071115</v>
+        <v>0.0006447795586070115</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0007866134215646046</v>
+        <v>0.0007866134215645868</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0003960994362950831</v>
+        <v>0.000396099436295072</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0005777017136408172</v>
+        <v>0.0005777017136407356</v>
       </c>
     </row>
     <row r="21">
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0003768028270288881</v>
+        <v>0.0003768028270289214</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0007659054584839415</v>
+        <v>0.000765905458483961</v>
       </c>
     </row>
     <row r="22">
@@ -5072,7 +5072,7 @@
         <v>0.0003557141340886805</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0006339294208247931</v>
+        <v>0.0006339294208247303</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0003445564674893431</v>
+        <v>0.0003445564674893875</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0004497170012049657</v>
+        <v>0.0004497170012049798</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0003175231346934093</v>
+        <v>0.0003175231346933871</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0004633366953445097</v>
+        <v>0.0004633366953443995</v>
       </c>
     </row>
     <row r="25">
@@ -5120,7 +5120,7 @@
         <v>0.0001266286008866579</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0004421366487265933</v>
+        <v>0.0004421366487266412</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0001024898684281017</v>
+        <v>0.0001024898684280684</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0003451227360610369</v>
+        <v>0.0003451227360610582</v>
       </c>
     </row>
     <row r="27">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3.235721233372235e-05</v>
+        <v>3.235721233366684e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0007478295686550885</v>
+        <v>0.0007478295686550963</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8.437338592059972e-06</v>
+        <v>8.437338592137689e-06</v>
       </c>
       <c r="D28" t="n">
-        <v>4.050035965240566e-05</v>
+        <v>4.050035965239743e-05</v>
       </c>
     </row>
     <row r="29">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-1.359412867504295e-05</v>
+        <v>-1.359412867499854e-05</v>
       </c>
       <c r="D29" t="n">
-        <v>9.738304911400796e-06</v>
+        <v>9.738304911506822e-06</v>
       </c>
     </row>
     <row r="30">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-7.469104474953082e-05</v>
+        <v>-7.469104474955301e-05</v>
       </c>
       <c r="D30" t="n">
-        <v>2.374961421896184e-05</v>
+        <v>2.374961421904651e-05</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.0001130712297018111</v>
+        <v>-0.0001130712297018333</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0002439198331223938</v>
+        <v>0.0002439198331223678</v>
       </c>
     </row>
     <row r="32">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.0001168675218212956</v>
+        <v>-0.0001168675218213067</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0007925235861204217</v>
+        <v>0.0007925235861204405</v>
       </c>
     </row>
     <row r="33">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.0001176716425592028</v>
+        <v>-0.0001176716425591806</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0004003034082453242</v>
+        <v>0.0004003034082453037</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-0.0001324463469226989</v>
+        <v>-0.0001324463469227211</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0006454520225867181</v>
+        <v>0.000645452022586708</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.0001846802514274159</v>
+        <v>-0.0001846802514273937</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0003716426206432473</v>
+        <v>0.0003716426206431491</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-0.000234381195863842</v>
+        <v>-0.0002343811958638753</v>
       </c>
       <c r="D36" t="n">
-        <v>0.000236980132998242</v>
+        <v>0.0002369801329982591</v>
       </c>
     </row>
     <row r="37">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-0.0002662016962840186</v>
+        <v>-0.0002662016962840297</v>
       </c>
       <c r="D37" t="n">
-        <v>0.001046252188397907</v>
+        <v>0.001046252188397825</v>
       </c>
     </row>
     <row r="38">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.0003226108771942737</v>
+        <v>-0.0003226108771941294</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0005679444414766771</v>
+        <v>0.0005679444414767485</v>
       </c>
     </row>
     <row r="39">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-0.0003362640018051977</v>
+        <v>-0.0003362640018051199</v>
       </c>
       <c r="D39" t="n">
-        <v>0.001038346870652598</v>
+        <v>0.001038346870652625</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.0003381286588022614</v>
+        <v>-0.0003381286588023169</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0001501861388581764</v>
+        <v>0.0001501861388581834</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.0003553317883045026</v>
+        <v>-0.0003553317883044804</v>
       </c>
       <c r="D41" t="n">
-        <v>0.001327973294740724</v>
+        <v>0.001327973294740836</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.0005601240915245054</v>
+        <v>-0.0005601240915244388</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0006924028490437499</v>
+        <v>0.0006924028490437473</v>
       </c>
     </row>
     <row r="43">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.0005687217856254589</v>
+        <v>-0.0005687217856255034</v>
       </c>
       <c r="D43" t="n">
-        <v>0.000368836531241739</v>
+        <v>0.0003688365312417812</v>
       </c>
     </row>
     <row r="44">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.0005821095161208434</v>
+        <v>-0.0005821095161207879</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0003091784580536161</v>
+        <v>0.0003091784580536261</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.000697389370586865</v>
+        <v>-0.0006973893705868317</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0005757197257349418</v>
+        <v>0.0005757197257349445</v>
       </c>
     </row>
     <row r="46">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.0008029358153880173</v>
+        <v>-0.0008029358153879729</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0006061992663920004</v>
+        <v>0.0006061992663920406</v>
       </c>
     </row>
     <row r="47">
@@ -5472,7 +5472,7 @@
         <v>-0.001000268056234965</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0007029745038290113</v>
+        <v>0.0007029745038290387</v>
       </c>
     </row>
     <row r="48">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.001176210536536926</v>
+        <v>-0.001176210536536981</v>
       </c>
       <c r="D48" t="n">
-        <v>0.001130222240312276</v>
+        <v>0.001130222240312283</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.001400142969639295</v>
+        <v>-0.001400142969639229</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0007410231991515997</v>
+        <v>0.0007410231991514725</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.00159413418785822</v>
+        <v>-0.001594134187858109</v>
       </c>
       <c r="D50" t="n">
-        <v>0.002652903816507177</v>
+        <v>0.002652903816507151</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.001754181676085709</v>
+        <v>-0.001754181676085664</v>
       </c>
       <c r="D51" t="n">
-        <v>0.001477833540605643</v>
+        <v>0.001477833540605673</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.001835082163533341</v>
+        <v>-0.001835082163533308</v>
       </c>
       <c r="D52" t="n">
-        <v>0.001875595212132226</v>
+        <v>0.001875595212132218</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.002288258689627743</v>
+        <v>-0.00228825868962772</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0007930398669021704</v>
+        <v>0.0007930398669021713</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.02065342838184092</v>
+        <v>-0.02065342838184094</v>
       </c>
       <c r="D54" t="n">
-        <v>0.01710128647155753</v>
+        <v>0.0171012864715575</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:03:17 UTC</t>
+          <t>2026-06-16 19:27:58 UTC</t>
         </is>
       </c>
     </row>
